--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R37" t="n">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI66"/>
+  <dimension ref="A1:BI72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46148.5625</v>
+        <v>46148.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46148.5625</v>
+        <v>46148.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46148.5625</v>
+        <v>46148.54166666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,27 +6067,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46148.57291666666</v>
+        <v>46148.54166666666</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46148.57291666666</v>
+        <v>46148.5625</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46148.57291666666</v>
+        <v>46148.5625</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46148.58333333334</v>
+        <v>46148.5625</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46148.58333333334</v>
+        <v>46148.57291666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46148.58333333334</v>
+        <v>46148.57291666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46148.58333333334</v>
+        <v>46148.57291666666</v>
       </c>
     </row>
     <row r="36">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46148.60416666666</v>
+        <v>46148.58333333334</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46148.60416666666</v>
+        <v>46148.58333333334</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46148.60416666666</v>
+        <v>46148.58333333334</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46148.60416666666</v>
+        <v>46148.58333333334</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46148.625</v>
+        <v>46148.60416666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,137 +8677,137 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46148.65625</v>
+        <v>46148.60416666666</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8929,10 +8929,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46148.66666666666</v>
+        <v>46148.60416666666</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.60416666666</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.625</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.625</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,137 +9662,137 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.65625</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9914,10 +9914,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.66666666666</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46148.72916666666</v>
+        <v>46148.70833333334</v>
       </c>
     </row>
     <row r="50">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="54">
@@ -10992,12 +10992,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="55">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="56">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46148.875</v>
+        <v>46148.72916666666</v>
       </c>
     </row>
     <row r="57">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13159,27 +13159,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46148.91666666666</v>
+        <v>46148.875</v>
       </c>
     </row>
     <row r="66">
@@ -13356,27 +13356,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,6 +13544,1188 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
+        <v>46148.875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ES Sétif</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI67" s="3" t="n">
+        <v>46148.875</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>USM Khenchela</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>El Bayadh</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI68" s="3" t="n">
+        <v>46148.875</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="3" t="n">
+        <v>46148.875</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ES Mostaganem</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JS Saoura</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="3" t="n">
+        <v>46148.875</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R71" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI71" s="3" t="n">
+        <v>46148.91666666666</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="3" t="n">
         <v>46148.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R44" t="n">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -292,15 +292,15 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,12 +355,12 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
@@ -376,60 +376,60 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
+    <t>Dila</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Egersund</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
@@ -442,45 +442,45 @@
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Al Wihdat</t>
   </si>
   <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,12 +568,12 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -589,60 +589,60 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
+    <t>Saburtalo</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
@@ -655,45 +655,45 @@
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Al Nasr</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Nasr</t>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
+    <t>Al Fateh</t>
   </si>
   <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>109</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -4107,10 +4107,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>108</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,13 +8401,13 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R44">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12062,16 +12062,16 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E60" t="s">
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,16 +12432,16 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,36 +268,36 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,27 +349,27 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
@@ -379,55 +379,58 @@
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
+    <t>Žalgiris</t>
   </si>
   <si>
     <t>Häcken W</t>
@@ -436,7 +439,7 @@
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
-    <t>Žalgiris</t>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
@@ -445,42 +448,39 @@
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Barcelona W</t>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Gagra</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,13 +490,19 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
   </si>
   <si>
     <t>Mount Pleasant Academy FC</t>
@@ -505,54 +511,48 @@
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
   </si>
   <si>
     <t>MC Alger</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,27 +562,27 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Bahardar</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
@@ -592,55 +592,58 @@
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>Apollon</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Djurgården W</t>
@@ -649,7 +652,7 @@
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
@@ -658,42 +661,39 @@
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,13 +703,19 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Racing United</t>
   </si>
   <si>
     <t>Montego Bay United</t>
@@ -718,49 +724,43 @@
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Racing United</t>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>MB Rouisset</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
     <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3370,7 +3370,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3555,7 +3555,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>109</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,10 +6142,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6181,133 +6181,133 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6882,10 +6882,10 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12432,10 +12432,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12617,16 +12617,16 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>154</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -295,12 +295,12 @@
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,21 +349,21 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
@@ -376,81 +376,84 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
+    <t>FS Jelgava</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Líšeň</t>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
   </si>
   <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Egersund</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
@@ -460,7 +463,7 @@
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
+    <t>Marumo Gallants</t>
   </si>
   <si>
     <t>AmaZulu</t>
@@ -469,18 +472,15 @@
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,34 +490,58 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
     <t>Portmore United</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
     <t>Cavalier</t>
   </si>
   <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>Al Hussein</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
   </si>
   <si>
     <t>Paradou AC</t>
@@ -529,30 +553,6 @@
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,21 +562,21 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>Bahardar</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
@@ -589,81 +589,84 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
+    <t>Super Nova</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Příbram</t>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
   </si>
   <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Al Nasr</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Al Nasr</t>
-  </si>
-  <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
@@ -673,7 +676,7 @@
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
+    <t>TS Galaxy</t>
   </si>
   <si>
     <t>Golden Arrows</t>
@@ -682,18 +685,15 @@
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,34 +703,55 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
     <t>Harbour View</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>CS Constantine</t>
@@ -740,27 +761,6 @@
   </si>
   <si>
     <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -3182,10 +3182,10 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6512,7 +6512,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,13 +8401,13 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,12 +280,12 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
@@ -295,12 +295,12 @@
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -376,111 +376,111 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Egersund</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Gagra</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -496,63 +496,63 @@
     <t>Waterhouse</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Portmore United</t>
   </si>
   <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Cavalier</t>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
   </si>
   <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -589,111 +589,111 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Al Nasr</t>
-  </si>
-  <si>
-    <t>Levante W</t>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -709,58 +709,58 @@
     <t>Dunbeholden</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Harbour View</t>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
   </si>
   <si>
     <t>USM Alger</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3740,7 +3740,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4480,7 +4480,7 @@
         <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6145,7 +6145,7 @@
         <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6181,133 +6181,133 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6882,10 +6882,10 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12617,10 +12617,10 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>154</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,16 +13172,16 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E66" t="s">
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -283,30 +283,30 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -376,69 +376,69 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
+    <t>FS Jelgava</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
+    <t>Dila</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
+    <t>Žalgiris</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Žalgiris</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
@@ -457,21 +457,21 @@
     <t>Hammarby</t>
   </si>
   <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -589,69 +589,69 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
+    <t>Super Nova</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Super Nova</t>
+    <t>Saburtalo</t>
   </si>
   <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Apollon</t>
+    <t>FA Šiauliai</t>
+  </si>
+  <si>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>FA Šiauliai</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
@@ -670,21 +670,21 @@
     <t>Uppsala W</t>
   </si>
   <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Sūduva</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Racing United</t>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
   </si>
   <si>
     <t>El Bayadh</t>
   </si>
   <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
     <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>108</v>
@@ -4107,10 +4107,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,10 +5032,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>130</v>
@@ -5071,133 +5071,133 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6145,7 +6145,7 @@
         <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6181,133 +6181,133 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6512,7 +6512,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
         <v>109</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,16 +11877,16 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,10 +13172,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E66" t="s">
         <v>174</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -283,24 +283,24 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -358,123 +358,123 @@
     <t>Fasil Ketema</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Hanácká</t>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
   </si>
   <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Gagra</t>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
@@ -496,63 +496,63 @@
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
+    <t>Paradou AC</t>
   </si>
   <si>
     <t>JS Kabylie</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -571,123 +571,123 @@
     <t>Bahardar</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
   </si>
   <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Příbram</t>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
@@ -709,58 +709,58 @@
     <t>Racing United</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
+    <t>CS Constantine</t>
   </si>
   <si>
     <t>ES Sétif</t>
   </si>
   <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
     <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,10 +4107,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,10 +5032,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>130</v>
@@ -5071,133 +5071,133 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR22">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU22">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV22">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY22">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ22">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA22">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD22">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE22">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R44">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,16 +11877,16 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13727,10 +13727,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E69" t="s">
         <v>177</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,21 +349,21 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,30 +376,30 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
@@ -409,34 +409,37 @@
     <t>Táborsko</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Líšeň</t>
+    <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>FUS Rabat</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Häcken W</t>
+  </si>
+  <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
@@ -445,30 +448,27 @@
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
   </si>
   <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,21 +562,21 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Bahardar</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,30 +589,30 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
@@ -622,34 +622,37 @@
     <t>Chrudim</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Příbram</t>
+    <t>Opava</t>
   </si>
   <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Djurgården W</t>
+  </si>
+  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
@@ -658,30 +661,27 @@
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Al Ain</t>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Uppsala W</t>
   </si>
   <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>108</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,10 +6142,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6181,133 +6181,133 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>154</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -292,21 +292,21 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -364,12 +364,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Minerva Punjab</t>
+  </si>
+  <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
@@ -391,52 +391,55 @@
     <t>České Budějovice</t>
   </si>
   <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Žalgiris</t>
+  </si>
+  <si>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
-    <t>Häcken W</t>
-  </si>
-  <si>
-    <t>Žalgiris</t>
+    <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Al Sharjah</t>
@@ -445,42 +448,39 @@
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>AmaZulu</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
+    <t>Al Jazeera</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -577,12 +577,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Chennaiyin</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
@@ -604,52 +604,55 @@
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Příbram</t>
   </si>
   <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Apollon</t>
   </si>
   <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
+    <t>FA Šiauliai</t>
+  </si>
+  <si>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>Djurgården W</t>
-  </si>
-  <si>
-    <t>FA Šiauliai</t>
+    <t>Al Nasr</t>
   </si>
   <si>
     <t>Al Ain</t>
@@ -658,42 +661,39 @@
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Nasr</t>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
+    <t>Al Fateh</t>
   </si>
   <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,25 +703,52 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
@@ -730,37 +757,10 @@
     <t>Sama Al Sarhan</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
+    <t>Al Salt</t>
   </si>
   <si>
     <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,10 +6142,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6181,133 +6181,133 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6512,10 +6512,10 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -6882,10 +6882,10 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,16 +12432,16 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>153</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13727,10 +13727,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
         <v>177</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,39 +268,39 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,126 +355,126 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>FS Jelgava</t>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Barcelona W</t>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
   </si>
   <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -490,66 +490,66 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
   </si>
   <si>
     <t>Oued Akbou</t>
   </si>
   <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
@@ -568,126 +568,126 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Super Nova</t>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Opava</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -703,61 +703,61 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>USM Alger</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
   </si>
   <si>
     <t>El Bayadh</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3370,7 +3370,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5775,7 +5775,7 @@
         <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>134</v>
@@ -5811,133 +5811,133 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO26">
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6512,7 +6512,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>153</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,16 +12432,16 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,16 +13172,16 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E66" t="s">
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,33 +280,33 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,21 +349,21 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,58 +376,61 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Häcken W</t>
@@ -436,7 +439,7 @@
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
@@ -445,7 +448,7 @@
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
+    <t>Maccabi Haifa</t>
   </si>
   <si>
     <t>Spartak Varna</t>
@@ -454,33 +457,30 @@
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
+    <t>Gagra</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Gagra</t>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -493,22 +493,43 @@
     <t>Waterhouse</t>
   </si>
   <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Al Jazeera</t>
@@ -517,39 +538,18 @@
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
   </si>
   <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
@@ -562,21 +562,21 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,58 +589,61 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Djurgården W</t>
@@ -649,7 +652,7 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
@@ -658,7 +661,7 @@
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Al Ain</t>
+    <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
@@ -667,33 +670,30 @@
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -706,58 +706,58 @@
     <t>Dunbeholden</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>Al Salt</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
   </si>
   <si>
     <t>El Bayadh</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -3182,10 +3182,10 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -4110,7 +4110,7 @@
         <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4701,13 +4701,13 @@
         <v>251</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,10 +5772,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>134</v>
@@ -5811,133 +5811,133 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR26">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU26">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV26">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA26">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -6882,10 +6882,10 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>153</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,16 +12617,16 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>154</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,10 +13172,10 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E66" t="s">
         <v>174</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -295,12 +295,12 @@
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,126 +355,126 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Dila</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Žalgiris</t>
+  </si>
+  <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Žalgiris</t>
-  </si>
-  <si>
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Hammarby</t>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
@@ -493,66 +493,66 @@
     <t>Waterhouse</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
     <t>Oued Akbou</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,126 +568,126 @@
     <t>Dalian Zhixing</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
     <t>Saburtalo</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>FA Šiauliai</t>
+  </si>
+  <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
-  </si>
-  <si>
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Al Nasr</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Nasr</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Uppsala W</t>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
@@ -706,61 +706,61 @@
     <t>Dunbeholden</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>109</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,10 +5772,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>134</v>
@@ -5811,133 +5811,133 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO26">
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -6736,13 +6736,13 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,16 +12617,16 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13542,10 +13542,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E68" t="s">
         <v>176</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -283,12 +283,12 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -349,12 +349,12 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
@@ -364,70 +364,73 @@
     <t>Sidama Bunna</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Hapoel Tel Aviv</t>
@@ -436,51 +439,48 @@
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
     <t>Hammarby</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>AmaZulu</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,13 +490,16 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
+    <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
     <t>Chapelton</t>
@@ -505,51 +508,48 @@
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -577,70 +577,73 @@
     <t>Ethiopian Medhin</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
@@ -649,51 +652,48 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Al Nasr</t>
-  </si>
-  <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
     <t>Uppsala W</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,13 +703,16 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Molynes United</t>
+    <t>Montego Bay United</t>
   </si>
   <si>
     <t>Arnett Gardens</t>
@@ -718,46 +721,43 @@
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>El Bayadh</t>
   </si>
   <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,13 +6736,13 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -11510,13 +11510,13 @@
         <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E57" t="s">
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13545,13 +13545,13 @@
         <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E68" t="s">
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -283,24 +283,24 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
@@ -358,12 +358,12 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,58 +376,61 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Egersund</t>
+    <t>Paphos</t>
   </si>
   <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Žalgiris</t>
   </si>
   <si>
     <t>Häcken W</t>
@@ -436,51 +439,48 @@
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
-    <t>Žalgiris</t>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Hammarby</t>
+    <t>Gagra</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -493,60 +493,60 @@
     <t>Treasure Beach</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
+    <t>Spanish Town Police FC</t>
   </si>
   <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
   </si>
   <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>MC Oran</t>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
     <t>Al Jazeera</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
@@ -571,12 +571,12 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,58 +589,61 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
     <t>Apollon</t>
   </si>
   <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Raufoss</t>
+    <t>Omonia Nicosia</t>
   </si>
   <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Djurgården W</t>
@@ -649,51 +652,48 @@
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Uppsala W</t>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -706,58 +706,58 @@
     <t>Molynes United</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
+    <t>Racing United</t>
   </si>
   <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Racing United</t>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
   </si>
   <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
-    <t>ASO Chlef</t>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
     <t>Al Salt</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5772,10 +5772,10 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E26" t="s">
         <v>134</v>
@@ -5811,133 +5811,133 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR26">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU26">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV26">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW26">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA26">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6512,7 +6512,7 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
         <v>108</v>
@@ -6551,13 +6551,13 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6882,10 +6882,10 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8401,13 +8401,13 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q43">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R43">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11510,7 +11510,7 @@
         <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E57" t="s">
         <v>165</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12250,7 +12250,7 @@
         <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61" t="s">
         <v>169</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G69">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -295,18 +295,18 @@
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -355,88 +355,91 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
+    <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Barcelona W</t>
@@ -445,42 +448,39 @@
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Portmore United</t>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
   </si>
   <si>
     <t>Chapelton</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Cavalier</t>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
   </si>
   <si>
     <t>MC Alger</t>
   </si>
   <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
   </si>
   <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
+    <t>USM Khenchela</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,88 +568,91 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
     <t>Opava</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
+    <t>Al Nasr</t>
   </si>
   <si>
     <t>Levante W</t>
@@ -658,42 +661,39 @@
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Al Nasr</t>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Sūduva</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
+    <t>Al Fateh</t>
   </si>
   <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
   </si>
   <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Harbour View</t>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
   </si>
   <si>
     <t>MB Rouisset</t>
   </si>
   <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>ASO Chlef</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
+    <t>El Bayadh</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,10 +4107,10 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4710,19 +4710,19 @@
         <v>3.15</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -4740,40 +4740,40 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO20">
         <v>0</v>
@@ -4818,13 +4818,13 @@
         <v>0</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD20">
         <v>0</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF20">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,10 +5587,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>133</v>
@@ -5626,133 +5626,133 @@
         <v>251</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM25">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO25">
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA25">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6700,7 +6700,7 @@
         <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6885,7 +6885,7 @@
         <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" t="s">
         <v>140</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8401,13 +8401,13 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q42">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R42">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12250,13 +12250,13 @@
         <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E61" t="s">
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,16 +12802,16 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E64" t="s">
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -292,12 +292,12 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
@@ -376,91 +376,97 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
+    <t>Sparta Praha II</t>
   </si>
   <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Paphos</t>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Gagra</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Gagra</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
   </si>
   <si>
     <t>AmaZulu</t>
@@ -469,12 +475,6 @@
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,15 +568,15 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
@@ -589,91 +589,97 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
+    <t>Prostějov</t>
   </si>
   <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
+    <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Golden Arrows</t>
@@ -682,12 +688,6 @@
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,13 +1926,13 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -3036,133 +3036,133 @@
         <v>251</v>
       </c>
       <c r="P11">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="R11">
-        <v>3.73</v>
+        <v>3.05</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,10 +5587,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
         <v>133</v>
@@ -5626,133 +5626,133 @@
         <v>251</v>
       </c>
       <c r="P25">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR25">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU25">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV25">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW25">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX25">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY25">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ25">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA25">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC25">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD25">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF25">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,22 +6551,22 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="R30">
-        <v>7.38</v>
+        <v>2.33</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -6575,10 +6575,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -6590,28 +6590,28 @@
         <v>0</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6668,13 +6668,13 @@
         <v>0</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD30">
         <v>0</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,13 +6736,13 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R36">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,13 +7846,13 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA43">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC43">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9186,10 +9186,10 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,16 +12802,16 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E64" t="s">
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,10 +13727,10 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E69" t="s">
         <v>177</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,36 +268,36 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>Algeria Ligue 1</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -349,87 +349,87 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
+    <t>Kaisar</t>
   </si>
   <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
     <t>Táborsko</t>
   </si>
   <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
@@ -448,33 +448,33 @@
     <t>Barcelona W</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,87 +562,87 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
     <t>Chrudim</t>
   </si>
   <si>
     <t>Příbram</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
@@ -661,33 +661,33 @@
     <t>Levante W</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
     <t>Uppsala W</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Racing United</t>
-  </si>
-  <si>
     <t>El Bayadh</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
     <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,13 +1926,13 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA27">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -7622,10 +7622,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
+        <v>3.05</v>
+      </c>
+      <c r="R37">
+        <v>2.4</v>
+      </c>
+      <c r="S37">
+        <v>4.03</v>
+      </c>
+      <c r="T37">
+        <v>2.11</v>
+      </c>
+      <c r="U37">
+        <v>2.87</v>
+      </c>
+      <c r="V37">
+        <v>1.41</v>
+      </c>
+      <c r="W37">
+        <v>2.7</v>
+      </c>
+      <c r="X37">
+        <v>2.9</v>
+      </c>
+      <c r="Y37">
+        <v>1.33</v>
+      </c>
+      <c r="Z37">
+        <v>7.8</v>
+      </c>
+      <c r="AA37">
+        <v>1.04</v>
+      </c>
+      <c r="AB37">
+        <v>1.04</v>
+      </c>
+      <c r="AC37">
+        <v>1.35</v>
+      </c>
+      <c r="AD37">
+        <v>2.9</v>
+      </c>
+      <c r="AE37">
+        <v>2.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.66</v>
+      </c>
+      <c r="AG37">
+        <v>3.7</v>
+      </c>
+      <c r="AH37">
+        <v>1.22</v>
+      </c>
+      <c r="AI37">
+        <v>7.8</v>
+      </c>
+      <c r="AJ37">
+        <v>1.04</v>
+      </c>
+      <c r="AK37">
+        <v>1.9</v>
+      </c>
+      <c r="AL37">
+        <v>1.81</v>
+      </c>
+      <c r="AM37">
+        <v>1.32</v>
+      </c>
+      <c r="AN37">
+        <v>1.28</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.34</v>
+      </c>
+      <c r="AQ37">
+        <v>1.58</v>
+      </c>
+      <c r="AR37">
+        <v>1.96</v>
+      </c>
+      <c r="AS37">
+        <v>2.5</v>
+      </c>
+      <c r="AT37">
         <v>3.25</v>
       </c>
-      <c r="R37">
-        <v>2.49</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
-      <c r="U37">
-        <v>0</v>
-      </c>
-      <c r="V37">
-        <v>0</v>
-      </c>
-      <c r="W37">
-        <v>0</v>
-      </c>
-      <c r="X37">
-        <v>0</v>
-      </c>
-      <c r="Y37">
-        <v>0</v>
-      </c>
-      <c r="Z37">
-        <v>0</v>
-      </c>
-      <c r="AA37">
-        <v>0</v>
-      </c>
-      <c r="AB37">
-        <v>0</v>
-      </c>
-      <c r="AC37">
-        <v>0</v>
-      </c>
-      <c r="AD37">
-        <v>0</v>
-      </c>
-      <c r="AE37">
-        <v>0</v>
-      </c>
-      <c r="AF37">
-        <v>0</v>
-      </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
-      <c r="AH37">
-        <v>0</v>
-      </c>
-      <c r="AI37">
-        <v>0</v>
-      </c>
-      <c r="AJ37">
-        <v>0</v>
-      </c>
-      <c r="AK37">
-        <v>0</v>
-      </c>
-      <c r="AL37">
-        <v>0</v>
-      </c>
-      <c r="AM37">
-        <v>0</v>
-      </c>
-      <c r="AN37">
-        <v>0</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
       <c r="AU37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -8771,133 +8771,133 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN42">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO42">
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU42">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV42">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX42">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD42">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL43">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM43">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN43">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR43">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT43">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV43">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW43">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX43">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY43">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ43">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA43">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB43">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC43">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD43">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF43">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -9186,10 +9186,10 @@
         <v>0</v>
       </c>
       <c r="AE44">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG44">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9881,133 +9881,133 @@
         <v>251</v>
       </c>
       <c r="P48">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="Q48">
-        <v>4.73</v>
+        <v>4.55</v>
       </c>
       <c r="R48">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AG48">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH48">
+        <v>2.46</v>
+      </c>
+      <c r="AI48">
+        <v>2.25</v>
+      </c>
+      <c r="AJ48">
+        <v>1.72</v>
+      </c>
+      <c r="AK48">
+        <v>1.22</v>
+      </c>
+      <c r="AL48">
+        <v>3.91</v>
+      </c>
+      <c r="AM48">
+        <v>1.2</v>
+      </c>
+      <c r="AN48">
+        <v>2.33</v>
+      </c>
+      <c r="AO48">
+        <v>0</v>
+      </c>
+      <c r="AP48">
+        <v>1.13</v>
+      </c>
+      <c r="AQ48">
+        <v>1.25</v>
+      </c>
+      <c r="AR48">
+        <v>1.43</v>
+      </c>
+      <c r="AS48">
+        <v>1.71</v>
+      </c>
+      <c r="AT48">
+        <v>2.08</v>
+      </c>
+      <c r="AU48">
+        <v>4.8</v>
+      </c>
+      <c r="AV48">
+        <v>3.45</v>
+      </c>
+      <c r="AW48">
+        <v>2.55</v>
+      </c>
+      <c r="AX48">
         <v>2</v>
       </c>
-      <c r="AI48">
-        <v>0</v>
-      </c>
-      <c r="AJ48">
-        <v>0</v>
-      </c>
-      <c r="AK48">
-        <v>0</v>
-      </c>
-      <c r="AL48">
-        <v>0</v>
-      </c>
-      <c r="AM48">
-        <v>0</v>
-      </c>
-      <c r="AN48">
-        <v>0</v>
-      </c>
-      <c r="AO48">
-        <v>0</v>
-      </c>
-      <c r="AP48">
-        <v>0</v>
-      </c>
-      <c r="AQ48">
-        <v>0</v>
-      </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-      <c r="AS48">
-        <v>0</v>
-      </c>
-      <c r="AT48">
-        <v>0</v>
-      </c>
-      <c r="AU48">
-        <v>0</v>
-      </c>
-      <c r="AV48">
-        <v>0</v>
-      </c>
-      <c r="AW48">
-        <v>0</v>
-      </c>
-      <c r="AX48">
-        <v>0</v>
-      </c>
       <c r="AY48">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AZ48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BA48">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BC48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BD48">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BE48">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BF48">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BG48">
         <v>0</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -12435,7 +12435,7 @@
         <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>153</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13730,7 +13730,7 @@
         <v>105</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E69" t="s">
         <v>177</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -283,24 +283,24 @@
     <t>Latvia Virsliga</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -349,27 +349,27 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
@@ -379,64 +379,67 @@
     <t>FS Jelgava</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
+    <t>Häcken W</t>
+  </si>
+  <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
@@ -445,30 +448,27 @@
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Barcelona W</t>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
     <t>Hammarby</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
+    <t>Al Ramtha</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
     <t>JS Kabylie</t>
   </si>
   <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,27 +562,27 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
-  </si>
-  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
@@ -592,64 +592,67 @@
     <t>Super Nova</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
+    <t>Djurgården W</t>
+  </si>
+  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
@@ -658,30 +661,27 @@
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Levante W</t>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
     <t>Uppsala W</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
+    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>El Bayadh</t>
   </si>
   <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
     <t>ASO Chlef</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
     <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2111,13 +2111,13 @@
         <v>251</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -3370,7 +3370,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>109</v>
@@ -3925,7 +3925,7 @@
         <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,10 +5957,10 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
         <v>135</v>
@@ -5996,133 +5996,133 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6697,7 +6697,7 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
         <v>108</v>
@@ -6736,13 +6736,13 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>3.06</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8586,133 +8586,133 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>3.01</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE41">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8771,133 +8771,133 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q42">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R42">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S42">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF42">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL42">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM42">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN42">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO42">
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ42">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR42">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS42">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT42">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU42">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV42">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW42">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX42">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY42">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ42">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA42">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB42">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC42">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD42">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE42">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF42">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
         <v>108</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,33 +280,33 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Sweden Damallsvenskan</t>
+  </si>
+  <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
@@ -376,105 +376,105 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
     <t>Vlašim</t>
   </si>
   <si>
+    <t>Häcken W</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
-    <t>Häcken W</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Maccabi Haifa</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
     <t>Al Hussein</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
     <t>MC Alger</t>
   </si>
   <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,15 +568,15 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
@@ -589,105 +589,105 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
+    <t>Djurgården W</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
-    <t>Djurgården W</t>
-  </si>
-  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Al Nasr</t>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>El Bayadh</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
     <t>USM Alger</t>
   </si>
   <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
     <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2111,13 +2111,13 @@
         <v>251</v>
       </c>
       <c r="P6">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -2481,79 +2481,79 @@
         <v>251</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -2595,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3555,7 +3555,7 @@
         <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3740,7 +3740,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4340,19 +4340,19 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -4370,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -4394,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4448,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD18">
         <v>0</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4850,7 +4850,7 @@
         <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -4886,133 +4886,133 @@
         <v>251</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,22 +6551,22 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V30">
         <v>0</v>
@@ -6575,10 +6575,10 @@
         <v>0</v>
       </c>
       <c r="X30">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -6590,28 +6590,28 @@
         <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -6620,10 +6620,10 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6668,13 +6668,13 @@
         <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD30">
         <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BF30">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,22 +6736,22 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
         <v>0</v>
@@ -6760,10 +6760,10 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -6775,28 +6775,28 @@
         <v>0</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
         <v>0</v>
@@ -6805,10 +6805,10 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -6853,13 +6853,13 @@
         <v>0</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD31">
         <v>0</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF31">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7661,13 +7661,13 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S37">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV37">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW37">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ37">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD37">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF37">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8180,7 +8180,7 @@
         <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,133 +8401,133 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8586,133 +8586,133 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="R41">
-        <v>3.01</v>
+        <v>3.29</v>
       </c>
       <c r="S41">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF41">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL41">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ41">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR41">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS41">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT41">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV41">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW41">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX41">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY41">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ41">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA41">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC41">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD41">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE41">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF41">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8816,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -12432,10 +12432,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12617,16 +12617,16 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -283,12 +283,12 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
@@ -355,21 +355,21 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
@@ -382,27 +382,30 @@
     <t>Hanácká</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
     <t>Samgurali</t>
   </si>
   <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>Egersund</t>
   </si>
   <si>
@@ -412,24 +415,21 @@
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
@@ -439,13 +439,19 @@
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>Gagra</t>
@@ -457,30 +463,24 @@
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>AmaZulu</t>
   </si>
   <si>
+    <t>Wydad Casablanca</t>
+  </si>
+  <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
     <t>Waterhouse</t>
   </si>
   <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,21 +568,21 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
@@ -595,27 +595,30 @@
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
     <t>Meshakhte</t>
   </si>
   <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Raufoss</t>
   </si>
   <si>
@@ -625,24 +628,21 @@
     <t>Opava</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
@@ -652,13 +652,19 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Levante W</t>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Dinamo Batumi</t>
@@ -670,30 +676,24 @@
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
+    <t>CODM Meknès</t>
+  </si>
+  <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
     <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1750,103 +1750,103 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1855,19 +1855,19 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -2296,112 +2296,112 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="R7">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2410,19 +2410,19 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2481,79 +2481,79 @@
         <v>251</v>
       </c>
       <c r="P8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -2595,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -2666,79 +2666,79 @@
         <v>251</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -2780,19 +2780,19 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4340,19 +4340,19 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -4370,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -4394,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4448,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="BC18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD18">
         <v>0</v>
       </c>
       <c r="BE18">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,10 +4847,10 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -4886,133 +4886,133 @@
         <v>251</v>
       </c>
       <c r="P21">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5032,10 +5032,10 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
         <v>130</v>
@@ -5071,133 +5071,133 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6736,16 +6736,16 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q31">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="T31">
         <v>2.43</v>
@@ -6754,34 +6754,34 @@
         <v>2.7</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="Y31">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AD31">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AE31">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AF31">
         <v>2.35</v>
@@ -6790,25 +6790,25 @@
         <v>2.23</v>
       </c>
       <c r="AH31">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AI31">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM31">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -6850,19 +6850,19 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE31">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>108</v>
@@ -7807,7 +7807,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>109</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,79 +8216,79 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8330,19 +8330,19 @@
         <v>0</v>
       </c>
       <c r="BB39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD39">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,133 +8401,133 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="Q40">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="S40">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>1.23</v>
+      </c>
+      <c r="AD40">
+        <v>3.45</v>
+      </c>
+      <c r="AE40">
+        <v>1.77</v>
+      </c>
+      <c r="AF40">
+        <v>1.87</v>
+      </c>
+      <c r="AG40">
         <v>2.9</v>
       </c>
-      <c r="Y40">
-        <v>1.33</v>
-      </c>
-      <c r="Z40">
-        <v>7.8</v>
-      </c>
-      <c r="AA40">
-        <v>1.04</v>
-      </c>
-      <c r="AB40">
-        <v>1.04</v>
-      </c>
-      <c r="AC40">
-        <v>1.35</v>
-      </c>
-      <c r="AD40">
-        <v>2.9</v>
-      </c>
-      <c r="AE40">
-        <v>2.14</v>
-      </c>
-      <c r="AF40">
-        <v>1.66</v>
-      </c>
-      <c r="AG40">
-        <v>3.7</v>
-      </c>
       <c r="AH40">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AI40">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AJ40">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK40">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AL40">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AM40">
+        <v>1.23</v>
+      </c>
+      <c r="AN40">
         <v>1.32</v>
       </c>
-      <c r="AN40">
-        <v>1.28</v>
-      </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR40">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU40">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX40">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ40">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF40">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -8956,13 +8956,13 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -9001,10 +9001,10 @@
         <v>0</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
         <v>0</v>
@@ -9141,13 +9141,13 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="R44">
-        <v>3.01</v>
+        <v>3.6</v>
       </c>
       <c r="S44">
         <v>2.7</v>
@@ -9156,7 +9156,7 @@
         <v>1.88</v>
       </c>
       <c r="U44">
-        <v>4.92</v>
+        <v>4</v>
       </c>
       <c r="V44">
         <v>1.48</v>
@@ -9165,10 +9165,10 @@
         <v>2.38</v>
       </c>
       <c r="X44">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="Y44">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
         <v>9</v>
@@ -9177,10 +9177,10 @@
         <v>1</v>
       </c>
       <c r="AB44">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AC44">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AD44">
         <v>2.66</v>
@@ -9192,10 +9192,10 @@
         <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AH44">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI44">
         <v>8.800000000000001</v>
@@ -9204,13 +9204,13 @@
         <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL44">
         <v>1.73</v>
       </c>
       <c r="AM44">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN44">
         <v>1.68</v>
@@ -9258,7 +9258,7 @@
         <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="BD44">
         <v>3.18</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9696,79 +9696,79 @@
         <v>252</v>
       </c>
       <c r="P47">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Q47">
-        <v>4.65</v>
+        <v>5.2</v>
       </c>
       <c r="R47">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S47">
         <v>6.5</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U47">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="W47">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="X47">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="Y47">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AB47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC47">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AD47">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="AE47">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AF47">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH47">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AI47">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL47">
-        <v>2.19</v>
+        <v>2.03</v>
       </c>
       <c r="AM47">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="AN47">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AO47">
         <v>0</v>
@@ -9777,52 +9777,52 @@
         <v>1.25</v>
       </c>
       <c r="AQ47">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AR47">
-        <v>1.62</v>
+        <v>2.14</v>
       </c>
       <c r="AS47">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AT47">
-        <v>3.18</v>
+        <v>3.23</v>
       </c>
       <c r="AU47">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="AV47">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AW47">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AX47">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AY47">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AZ47">
-        <v>5.25</v>
+        <v>7.6</v>
       </c>
       <c r="BA47">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BB47">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BC47">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="BD47">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE47">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="BF47">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BG47">
         <v>0</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12432,10 +12432,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12617,10 +12617,10 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>154</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14136,79 +14136,79 @@
         <v>251</v>
       </c>
       <c r="P71">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q71">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="R71">
-        <v>3.12</v>
+        <v>2.79</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH71">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI71">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM71">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN71">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO71">
         <v>0</v>
@@ -14250,19 +14250,19 @@
         <v>0</v>
       </c>
       <c r="BB71">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC71">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD71">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE71">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF71">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG71">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -292,21 +292,21 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,12 +349,12 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
-  </si>
-  <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
@@ -376,111 +376,111 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
   </si>
   <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Žalgiris</t>
   </si>
   <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Žalgiris</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Gagra</t>
   </si>
   <si>
     <t>Hammarby</t>
   </si>
   <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
     <t>Cavalier</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
   </si>
   <si>
     <t>MC Oran</t>
   </si>
   <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
+    <t>Ben Aknoun</t>
   </si>
   <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,12 +562,12 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
@@ -589,111 +589,111 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
   </si>
   <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
     <t>Opava</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>FA Šiauliai</t>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Al Nasr</t>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Uppsala W</t>
   </si>
   <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
+    <t>Al Fateh</t>
   </si>
   <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
     <t>Harbour View</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
   </si>
   <si>
     <t>ASO Chlef</t>
   </si>
   <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Al Buqa'a</t>
   </si>
   <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
+    <t>USM Alger</t>
   </si>
   <si>
     <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1565,103 +1565,103 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1670,19 +1670,19 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1750,103 +1750,103 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS4">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT4">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU4">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV4">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY4">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1855,19 +1855,19 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD4">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE4">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -3036,79 +3036,79 @@
         <v>251</v>
       </c>
       <c r="P11">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="Q11">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>3.01</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="U11">
-        <v>3.91</v>
+        <v>3.63</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="X11">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>6.95</v>
       </c>
       <c r="AA11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB11">
         <v>1.02</v>
       </c>
       <c r="AC11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AD11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AE11">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AF11">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="AH11">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AI11">
         <v>6</v>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK11">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL11">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AM11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN11">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3123,10 +3123,10 @@
         <v>1.87</v>
       </c>
       <c r="AS11">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AT11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AU11">
         <v>3.1</v>
@@ -3144,25 +3144,25 @@
         <v>1.3</v>
       </c>
       <c r="AZ11">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="BA11">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="BB11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC11">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="BD11">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="BE11">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BF11">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -5035,7 +5035,7 @@
         <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>130</v>
@@ -5071,133 +5071,133 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ22">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR22">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT22">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU22">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV22">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW22">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AX22">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY22">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ22">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA22">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD22">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE22">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF22">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,79 +6551,79 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6665,19 +6665,19 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,79 +6736,79 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>7.38</v>
       </c>
       <c r="S31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -6850,19 +6850,19 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7625,7 +7625,7 @@
         <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,79 +7661,79 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -7775,19 +7775,19 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD36">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV37">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW37">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ37">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD37">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF37">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,79 +8216,79 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
         <v>1.23</v>
       </c>
-      <c r="W39">
-        <v>3.52</v>
-      </c>
-      <c r="X39">
-        <v>2.12</v>
-      </c>
-      <c r="Y39">
-        <v>1.56</v>
-      </c>
-      <c r="Z39">
-        <v>4.8</v>
-      </c>
-      <c r="AA39">
-        <v>1.13</v>
-      </c>
-      <c r="AB39">
-        <v>1.01</v>
-      </c>
-      <c r="AC39">
-        <v>1.12</v>
-      </c>
       <c r="AD39">
-        <v>4.95</v>
+        <v>3.45</v>
       </c>
       <c r="AE39">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AF39">
-        <v>2.41</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AH39">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AI39">
-        <v>3.68</v>
+        <v>5.1</v>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AL39">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="AM39">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AN39">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8330,19 +8330,19 @@
         <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC39">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD39">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,76 +8401,76 @@
         <v>251</v>
       </c>
       <c r="P40">
+        <v>2.94</v>
+      </c>
+      <c r="Q40">
+        <v>3.05</v>
+      </c>
+      <c r="R40">
+        <v>2.4</v>
+      </c>
+      <c r="S40">
+        <v>3.8</v>
+      </c>
+      <c r="T40">
+        <v>2</v>
+      </c>
+      <c r="U40">
+        <v>2.92</v>
+      </c>
+      <c r="V40">
+        <v>1.42</v>
+      </c>
+      <c r="W40">
         <v>2.55</v>
       </c>
-      <c r="Q40">
-        <v>3.25</v>
-      </c>
-      <c r="R40">
-        <v>2.49</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
       <c r="X40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC40">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AD40">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="AE40">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AF40">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AH40">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AI40">
-        <v>5.1</v>
+        <v>7.9</v>
       </c>
       <c r="AJ40">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK40">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AM40">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AN40">
         <v>1.32</v>
@@ -8479,55 +8479,55 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8816,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q43">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="R43">
+        <v>3.6</v>
+      </c>
+      <c r="S43">
+        <v>2.7</v>
+      </c>
+      <c r="T43">
+        <v>1.88</v>
+      </c>
+      <c r="U43">
+        <v>4</v>
+      </c>
+      <c r="V43">
+        <v>1.48</v>
+      </c>
+      <c r="W43">
+        <v>2.38</v>
+      </c>
+      <c r="X43">
+        <v>3.3</v>
+      </c>
+      <c r="Y43">
+        <v>1.27</v>
+      </c>
+      <c r="Z43">
+        <v>9</v>
+      </c>
+      <c r="AA43">
+        <v>1</v>
+      </c>
+      <c r="AB43">
+        <v>1.09</v>
+      </c>
+      <c r="AC43">
+        <v>1.37</v>
+      </c>
+      <c r="AD43">
+        <v>2.66</v>
+      </c>
+      <c r="AE43">
+        <v>2.27</v>
+      </c>
+      <c r="AF43">
+        <v>1.56</v>
+      </c>
+      <c r="AG43">
+        <v>4.2</v>
+      </c>
+      <c r="AH43">
+        <v>1.2</v>
+      </c>
+      <c r="AI43">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ43">
+        <v>1.01</v>
+      </c>
+      <c r="AK43">
+        <v>1.97</v>
+      </c>
+      <c r="AL43">
+        <v>1.73</v>
+      </c>
+      <c r="AM43">
+        <v>1.25</v>
+      </c>
+      <c r="AN43">
+        <v>1.68</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>1.27</v>
+      </c>
+      <c r="AQ43">
+        <v>1.47</v>
+      </c>
+      <c r="AR43">
+        <v>1.77</v>
+      </c>
+      <c r="AS43">
+        <v>2.2</v>
+      </c>
+      <c r="AT43">
         <v>2.85</v>
       </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
-      <c r="V43">
-        <v>0</v>
-      </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
-      <c r="X43">
-        <v>0</v>
-      </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
-      <c r="Z43">
-        <v>0</v>
-      </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
-      <c r="AB43">
-        <v>0</v>
-      </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
-      <c r="AD43">
-        <v>0</v>
-      </c>
-      <c r="AE43">
-        <v>2.62</v>
-      </c>
-      <c r="AF43">
-        <v>1.44</v>
-      </c>
-      <c r="AG43">
-        <v>0</v>
-      </c>
-      <c r="AH43">
-        <v>0</v>
-      </c>
-      <c r="AI43">
-        <v>0</v>
-      </c>
-      <c r="AJ43">
-        <v>0</v>
-      </c>
-      <c r="AK43">
-        <v>0</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>0</v>
-      </c>
-      <c r="AN43">
-        <v>0</v>
-      </c>
-      <c r="AO43">
-        <v>0</v>
-      </c>
-      <c r="AP43">
-        <v>0</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
-      <c r="AS43">
-        <v>0</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
       <c r="AU43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA43">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL44">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN44">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS44">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT44">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV44">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW44">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX44">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC44">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD44">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9887,64 +9887,64 @@
         <v>4.55</v>
       </c>
       <c r="R48">
-        <v>4.24</v>
+        <v>4.16</v>
       </c>
       <c r="S48">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="T48">
         <v>3.1</v>
       </c>
       <c r="U48">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="V48">
         <v>1.09</v>
       </c>
       <c r="W48">
-        <v>6.7</v>
+        <v>6.65</v>
       </c>
       <c r="X48">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Y48">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Z48">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA48">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB48">
         <v>1.01</v>
       </c>
       <c r="AC48">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AD48">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE48">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AG48">
         <v>1.54</v>
       </c>
       <c r="AH48">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="AI48">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AJ48">
         <v>1.72</v>
       </c>
       <c r="AK48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL48">
         <v>3.91</v>
@@ -9953,7 +9953,7 @@
         <v>1.2</v>
       </c>
       <c r="AN48">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AO48">
         <v>0</v>
@@ -9995,13 +9995,13 @@
         <v>4.8</v>
       </c>
       <c r="BB48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BC48">
         <v>1.42</v>
       </c>
       <c r="BD48">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BE48">
         <v>2.85</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12432,10 +12432,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>153</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>154</v>
+        <v>247</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,10 +13912,10 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E70" t="s">
         <v>178</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -283,30 +283,30 @@
     <t>Czech Republic FNL</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
+    <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,10 +349,13 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
+    <t>Yunnan Yukun</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
@@ -361,9 +364,6 @@
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,58 +376,61 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Hanácká</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Paphos</t>
   </si>
   <si>
+    <t>Aris</t>
+  </si>
+  <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Hapoel Tel Aviv</t>
@@ -436,51 +439,48 @@
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Gagra</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
+    <t>Marumo Gallants</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
+    <t>Richards Bay</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Richards Bay</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
   </si>
   <si>
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
     <t>MC Alger</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
     <t>Al Hussein</t>
   </si>
   <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,10 +562,13 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
+    <t>Zhejiang FC</t>
   </si>
   <si>
     <t>Ethiopian Medhin</t>
@@ -574,9 +577,6 @@
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,58 +589,61 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
     <t>Meshakhte</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
@@ -649,51 +652,48 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
+    <t>TS Galaxy</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
+    <t>Polokwane City</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Polokwane City</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>Al Salt</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>MB Rouisset</t>
   </si>
   <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
     <t>ASO Chlef</t>
   </si>
   <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
     <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1380,103 +1380,103 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1485,19 +1485,19 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1565,124 +1565,124 @@
         <v>0</v>
       </c>
       <c r="S3">
+        <v>2.13</v>
+      </c>
+      <c r="T3">
+        <v>2.43</v>
+      </c>
+      <c r="U3">
+        <v>4.45</v>
+      </c>
+      <c r="V3">
+        <v>1.22</v>
+      </c>
+      <c r="W3">
+        <v>3.6</v>
+      </c>
+      <c r="X3">
+        <v>2.2</v>
+      </c>
+      <c r="Y3">
+        <v>1.62</v>
+      </c>
+      <c r="Z3">
+        <v>4.75</v>
+      </c>
+      <c r="AA3">
+        <v>1.13</v>
+      </c>
+      <c r="AB3">
+        <v>1.01</v>
+      </c>
+      <c r="AC3">
+        <v>1.11</v>
+      </c>
+      <c r="AD3">
+        <v>4.85</v>
+      </c>
+      <c r="AE3">
+        <v>1.47</v>
+      </c>
+      <c r="AF3">
+        <v>2.35</v>
+      </c>
+      <c r="AG3">
+        <v>2.4</v>
+      </c>
+      <c r="AH3">
+        <v>1.62</v>
+      </c>
+      <c r="AI3">
+        <v>3.78</v>
+      </c>
+      <c r="AJ3">
+        <v>1.19</v>
+      </c>
+      <c r="AK3">
+        <v>1.53</v>
+      </c>
+      <c r="AL3">
+        <v>2.35</v>
+      </c>
+      <c r="AM3">
+        <v>1.22</v>
+      </c>
+      <c r="AN3">
+        <v>2.17</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1.17</v>
+      </c>
+      <c r="AQ3">
+        <v>1.38</v>
+      </c>
+      <c r="AR3">
+        <v>1.68</v>
+      </c>
+      <c r="AS3">
+        <v>2.09</v>
+      </c>
+      <c r="AT3">
+        <v>2.7</v>
+      </c>
+      <c r="AU3">
+        <v>3.92</v>
+      </c>
+      <c r="AV3">
+        <v>2.7</v>
+      </c>
+      <c r="AW3">
         <v>2.05</v>
       </c>
-      <c r="T3">
-        <v>2.41</v>
-      </c>
-      <c r="U3">
-        <v>5</v>
-      </c>
-      <c r="V3">
+      <c r="AX3">
+        <v>1.66</v>
+      </c>
+      <c r="AY3">
+        <v>1.38</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>1.12</v>
+      </c>
+      <c r="BC3">
+        <v>1.75</v>
+      </c>
+      <c r="BD3">
+        <v>4.95</v>
+      </c>
+      <c r="BE3">
+        <v>1.99</v>
+      </c>
+      <c r="BF3">
         <v>1.27</v>
-      </c>
-      <c r="W3">
-        <v>3.35</v>
-      </c>
-      <c r="X3">
-        <v>2.44</v>
-      </c>
-      <c r="Y3">
-        <v>1.48</v>
-      </c>
-      <c r="Z3">
-        <v>5.85</v>
-      </c>
-      <c r="AA3">
-        <v>1.07</v>
-      </c>
-      <c r="AB3">
-        <v>1.02</v>
-      </c>
-      <c r="AC3">
-        <v>1.17</v>
-      </c>
-      <c r="AD3">
-        <v>4.05</v>
-      </c>
-      <c r="AE3">
-        <v>1.73</v>
-      </c>
-      <c r="AF3">
-        <v>2.13</v>
-      </c>
-      <c r="AG3">
-        <v>2.71</v>
-      </c>
-      <c r="AH3">
-        <v>1.36</v>
-      </c>
-      <c r="AI3">
-        <v>4.91</v>
-      </c>
-      <c r="AJ3">
-        <v>1.17</v>
-      </c>
-      <c r="AK3">
-        <v>1.77</v>
-      </c>
-      <c r="AL3">
-        <v>1.94</v>
-      </c>
-      <c r="AM3">
-        <v>1.2</v>
-      </c>
-      <c r="AN3">
-        <v>2.52</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>1.19</v>
-      </c>
-      <c r="AQ3">
-        <v>1.42</v>
-      </c>
-      <c r="AR3">
-        <v>1.95</v>
-      </c>
-      <c r="AS3">
-        <v>2.17</v>
-      </c>
-      <c r="AT3">
-        <v>2.86</v>
-      </c>
-      <c r="AU3">
-        <v>3.68</v>
-      </c>
-      <c r="AV3">
-        <v>2.57</v>
-      </c>
-      <c r="AW3">
-        <v>1.97</v>
-      </c>
-      <c r="AX3">
-        <v>1.6</v>
-      </c>
-      <c r="AY3">
-        <v>1.34</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.16</v>
-      </c>
-      <c r="BC3">
-        <v>1.95</v>
-      </c>
-      <c r="BD3">
-        <v>4.33</v>
-      </c>
-      <c r="BE3">
-        <v>1.78</v>
-      </c>
-      <c r="BF3">
-        <v>1.18</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1750,103 +1750,103 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1855,19 +1855,19 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,112 +1926,112 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,112 +2296,112 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR7">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT7">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU7">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV7">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW7">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX7">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2410,19 +2410,19 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BD7">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -3045,10 +3045,10 @@
         <v>2.8</v>
       </c>
       <c r="S11">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="T11">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
         <v>3.63</v>
@@ -3060,10 +3060,10 @@
         <v>2.66</v>
       </c>
       <c r="X11">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z11">
         <v>6.95</v>
@@ -3081,13 +3081,13 @@
         <v>3.3</v>
       </c>
       <c r="AE11">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AF11">
         <v>1.73</v>
       </c>
       <c r="AG11">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="AH11">
         <v>1.23</v>
@@ -3099,7 +3099,7 @@
         <v>1.05</v>
       </c>
       <c r="AK11">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL11">
         <v>1.96</v>
@@ -3182,7 +3182,7 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>109</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>109</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -5217,10 +5217,10 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
         <v>131</v>
@@ -5256,133 +5256,133 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA23">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,79 +6551,79 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6665,19 +6665,19 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD30">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,79 +6736,79 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q31">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>7.38</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -6850,19 +6850,19 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,13 +6921,13 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8070,40 +8070,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8255,40 +8255,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,133 +8401,133 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR40">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU40">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX40">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ40">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BD40">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8816,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R43">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL43">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM43">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN43">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR43">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT43">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV43">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW43">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX43">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY43">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ43">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA43">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB43">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD43">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF43">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12802,10 +12802,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E64" t="s">
         <v>172</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>153</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,16 +13912,16 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E70" t="s">
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="G70">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,24 +268,24 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
@@ -301,12 +301,12 @@
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Israel Israeli Premier League</t>
+  </si>
+  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -355,132 +355,132 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Dila</t>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
   </si>
   <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Samgurali</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Aris</t>
   </si>
   <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
     <t>Egersund</t>
   </si>
   <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Žalgiris</t>
+  </si>
+  <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Žalgiris</t>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>Gagra</t>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>AmaZulu</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
+    <t>Al Ahli</t>
   </si>
   <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,25 +490,28 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
+    <t>Al Jazeera</t>
   </si>
   <si>
     <t>ES Mostaganem</t>
@@ -517,42 +520,39 @@
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>Al Jazeera</t>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
   </si>
   <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>Sporting KC II</t>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
   </si>
   <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,132 +568,132 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
   </si>
   <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
     <t>Meshakhte</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
+    <t>APOEL</t>
   </si>
   <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
     <t>Raufoss</t>
   </si>
   <si>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>FA Šiauliai</t>
+  </si>
+  <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>FA Šiauliai</t>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Dinamo Batumi</t>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>Golden Arrows</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
+    <t>Al Fateh</t>
   </si>
   <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,25 +703,28 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Racing United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
+    <t>Al Salt</t>
   </si>
   <si>
     <t>JS Saoura</t>
@@ -730,37 +733,34 @@
     <t>Al Buqa'a</t>
   </si>
   <si>
-    <t>Al Salt</t>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
   </si>
   <si>
     <t>El Bayadh</t>
   </si>
   <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
-    <t>LA Galaxy II</t>
+    <t>MB Rouisset</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1410,7 +1410,7 @@
         <v>1.04</v>
       </c>
       <c r="AC2">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD2">
         <v>3.72</v>
@@ -1425,7 +1425,7 @@
         <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AI2">
         <v>5.4</v>
@@ -1437,7 +1437,7 @@
         <v>1.64</v>
       </c>
       <c r="AL2">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AM2">
         <v>1.29</v>
@@ -1470,7 +1470,7 @@
         <v>2.57</v>
       </c>
       <c r="AW2">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="AX2">
         <v>1.6</v>
@@ -1485,16 +1485,16 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC2">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="BD2">
         <v>4.1</v>
       </c>
       <c r="BE2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF2">
         <v>1.16</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T3">
         <v>2.43</v>
@@ -1601,7 +1601,7 @@
         <v>4.85</v>
       </c>
       <c r="AE3">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AF3">
         <v>2.35</v>
@@ -1640,7 +1640,7 @@
         <v>1.38</v>
       </c>
       <c r="AR3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AS3">
         <v>2.09</v>
@@ -1759,25 +1759,25 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X4">
         <v>2.44</v>
       </c>
       <c r="Y4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z4">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="AA4">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC4">
         <v>1.23</v>
@@ -1792,16 +1792,16 @@
         <v>2.13</v>
       </c>
       <c r="AG4">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AH4">
         <v>1.36</v>
       </c>
       <c r="AI4">
-        <v>4.91</v>
+        <v>5.05</v>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
         <v>1.77</v>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,112 +1926,112 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -2040,19 +2040,19 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BD5">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,112 +2296,112 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2410,19 +2410,19 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2481,79 +2481,79 @@
         <v>251</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -2595,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -2666,79 +2666,79 @@
         <v>251</v>
       </c>
       <c r="P9">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -2780,19 +2780,19 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3045,13 +3045,13 @@
         <v>2.8</v>
       </c>
       <c r="S11">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="T11">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="U11">
-        <v>3.63</v>
+        <v>3.52</v>
       </c>
       <c r="V11">
         <v>1.41</v>
@@ -3108,7 +3108,7 @@
         <v>1.29</v>
       </c>
       <c r="AN11">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>1.58</v>
       </c>
       <c r="BF11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3182,10 +3182,10 @@
         <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>109</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -3970,19 +3970,19 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X16">
         <v>0</v>
@@ -4000,22 +4000,22 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI16">
         <v>0</v>
@@ -4024,16 +4024,16 @@
         <v>0</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,79 +6551,79 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO30">
         <v>0</v>
@@ -6665,19 +6665,19 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,79 +6736,79 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>7.38</v>
       </c>
       <c r="S31">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
@@ -6850,19 +6850,19 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,22 +6921,22 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6945,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6960,40 +6960,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV37">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW37">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ37">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BD37">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8070,40 +8070,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8255,40 +8255,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,133 +8401,133 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -8631,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="AE41">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG41">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU43">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ43">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA43">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R44">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="S44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AL44">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN44">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS44">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT44">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV44">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW44">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX44">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC44">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD44">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9696,13 +9696,13 @@
         <v>252</v>
       </c>
       <c r="P47">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q47">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="R47">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S47">
         <v>6.5</v>
@@ -9714,25 +9714,25 @@
         <v>1.75</v>
       </c>
       <c r="V47">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W47">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="X47">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Y47">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z47">
         <v>4.5</v>
       </c>
       <c r="AA47">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AB47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC47">
         <v>1.13</v>
@@ -9768,7 +9768,7 @@
         <v>3.05</v>
       </c>
       <c r="AN47">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AO47">
         <v>0</v>
@@ -9810,16 +9810,16 @@
         <v>1.27</v>
       </c>
       <c r="BB47">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BC47">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BD47">
         <v>5.5</v>
       </c>
       <c r="BE47">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="BF47">
         <v>1.35</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12432,10 +12432,10 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12802,10 +12802,10 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E64" t="s">
         <v>172</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>
@@ -13921,7 +13921,7 @@
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="G70">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -268,45 +268,45 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>India Indian Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
+    <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -364,70 +364,73 @@
     <t>Yunnan Yukun</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Hanácká</t>
+    <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Egersund</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Hapoel Tel Aviv</t>
@@ -436,16 +439,22 @@
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
-    <t>Shabab Al Ahli Dubai</t>
+    <t>Hammarby</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
@@ -454,33 +463,24 @@
     <t>Gagra</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
   </si>
   <si>
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -577,70 +577,73 @@
     <t>Zhejiang FC</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
@@ -649,16 +652,22 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
-    <t>Al Nasr</t>
+    <t>Uppsala W</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
@@ -667,33 +676,24 @@
     <t>Dinamo Batumi</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Polokwane City</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
   </si>
   <si>
     <t>Al Salt</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
     <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1383,22 +1383,22 @@
         <v>2.64</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
         <v>3.88</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="X2">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="Y2">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z2">
         <v>6.35</v>
@@ -1407,43 +1407,43 @@
         <v>1.06</v>
       </c>
       <c r="AB2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC2">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AD2">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AE2">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF2">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AG2">
         <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AI2">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AJ2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL2">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AM2">
         <v>1.29</v>
       </c>
       <c r="AN2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AO2">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>1.19</v>
       </c>
       <c r="AQ2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AR2">
         <v>1.75</v>
       </c>
       <c r="AS2">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AT2">
         <v>2.86</v>
@@ -1467,34 +1467,34 @@
         <v>3.68</v>
       </c>
       <c r="AV2">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AW2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AX2">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AY2">
         <v>1.34</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB2">
         <v>1.17</v>
       </c>
       <c r="BC2">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="BD2">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="BE2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BF2">
         <v>1.16</v>
@@ -1568,37 +1568,37 @@
         <v>2.15</v>
       </c>
       <c r="T3">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
         <v>4.45</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="X3">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Y3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z3">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AB3">
         <v>1.01</v>
       </c>
       <c r="AC3">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AD3">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AE3">
         <v>1.55</v>
@@ -1607,16 +1607,16 @@
         <v>2.35</v>
       </c>
       <c r="AG3">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AI3">
         <v>3.78</v>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
         <v>1.53</v>
@@ -1625,10 +1625,10 @@
         <v>2.35</v>
       </c>
       <c r="AM3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN3">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AO3">
         <v>0</v>
@@ -1637,16 +1637,16 @@
         <v>1.17</v>
       </c>
       <c r="AQ3">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AR3">
         <v>1.67</v>
       </c>
       <c r="AS3">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AT3">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AU3">
         <v>3.92</v>
@@ -1655,19 +1655,19 @@
         <v>2.7</v>
       </c>
       <c r="AW3">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AX3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AY3">
         <v>1.38</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB3">
         <v>1.12</v>
@@ -1750,31 +1750,31 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="T4">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="Y4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA4">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB4">
         <v>1.03</v>
@@ -1783,37 +1783,37 @@
         <v>1.23</v>
       </c>
       <c r="AD4">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="AE4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF4">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AG4">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AH4">
         <v>1.36</v>
       </c>
       <c r="AI4">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="AJ4">
         <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="AL4">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AM4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN4">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="AO4">
         <v>0</v>
@@ -1822,22 +1822,22 @@
         <v>1.19</v>
       </c>
       <c r="AQ4">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AR4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AS4">
         <v>2.17</v>
       </c>
       <c r="AT4">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="AU4">
         <v>3.68</v>
       </c>
       <c r="AV4">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AW4">
         <v>1.97</v>
@@ -1849,25 +1849,25 @@
         <v>1.34</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB4">
         <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BD4">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="BE4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BF4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -2296,10 +2296,10 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="R7">
         <v>2.72</v>
@@ -2308,67 +2308,67 @@
         <v>2.5</v>
       </c>
       <c r="T7">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="U7">
+        <v>3.44</v>
+      </c>
+      <c r="V7">
+        <v>1.22</v>
+      </c>
+      <c r="W7">
         <v>3.52</v>
       </c>
-      <c r="V7">
-        <v>1.25</v>
-      </c>
-      <c r="W7">
-        <v>3.36</v>
-      </c>
       <c r="X7">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Y7">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Z7">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB7">
         <v>1.01</v>
       </c>
       <c r="AC7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AD7">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="AE7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="AH7">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AI7">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AM7">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN7">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2383,10 +2383,10 @@
         <v>1.79</v>
       </c>
       <c r="AS7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AT7">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AU7">
         <v>4.19</v>
@@ -2401,25 +2401,25 @@
         <v>1.72</v>
       </c>
       <c r="AY7">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BC7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="BD7">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE7">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BF7">
         <v>1.29</v>
@@ -2445,7 +2445,7 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
@@ -2481,79 +2481,79 @@
         <v>251</v>
       </c>
       <c r="P8">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL8">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -2595,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE8">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF8">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
@@ -2666,79 +2666,79 @@
         <v>251</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -2780,19 +2780,19 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3051,7 +3051,7 @@
         <v>2.03</v>
       </c>
       <c r="U11">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="V11">
         <v>1.41</v>
@@ -3090,7 +3090,7 @@
         <v>3.2</v>
       </c>
       <c r="AH11">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AI11">
         <v>6</v>
@@ -3105,10 +3105,10 @@
         <v>1.96</v>
       </c>
       <c r="AM11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AN11">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>1.58</v>
       </c>
       <c r="BF11">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG11">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3230,13 +3230,13 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3245,10 +3245,10 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3260,40 +3260,40 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3591,28 +3591,28 @@
         <v>251</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X14">
         <v>0</v>
@@ -3630,22 +3630,22 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14">
         <v>0</v>
@@ -3654,16 +3654,16 @@
         <v>0</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>109</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3815,40 +3815,40 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD15">
         <v>0</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -3970,25 +3970,25 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="T16">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="V16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4000,40 +4000,40 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AD16">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AE16">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AF16">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH16">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL16">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AM16">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AN16">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>109</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4847,10 +4847,10 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -4886,133 +4886,133 @@
         <v>251</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5626,13 +5626,13 @@
         <v>251</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S25">
         <v>0</v>
@@ -5671,10 +5671,10 @@
         <v>0</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG25">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5996,13 +5996,13 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6181,13 +6181,13 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6327,10 +6327,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,133 +6366,133 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH29">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL29">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM29">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN29">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ29">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR29">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS29">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU29">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV29">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW29">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AX29">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY29">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ29">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA29">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC29">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD29">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE29">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF29">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,80 +6551,80 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>1.58</v>
+      </c>
+      <c r="T30">
+        <v>2.88</v>
+      </c>
+      <c r="U30">
+        <v>7.5</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>1.98</v>
+      </c>
+      <c r="Y30">
+        <v>1.64</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>1.11</v>
+      </c>
+      <c r="AD30">
+        <v>5</v>
+      </c>
+      <c r="AE30">
+        <v>1.42</v>
+      </c>
+      <c r="AF30">
+        <v>2.55</v>
+      </c>
+      <c r="AG30">
+        <v>2.08</v>
+      </c>
+      <c r="AH30">
+        <v>1.62</v>
+      </c>
+      <c r="AI30">
+        <v>3.35</v>
+      </c>
+      <c r="AJ30">
+        <v>1.25</v>
+      </c>
+      <c r="AK30">
+        <v>1.84</v>
+      </c>
+      <c r="AL30">
+        <v>1.8</v>
+      </c>
+      <c r="AM30">
+        <v>1.08</v>
+      </c>
+      <c r="AN30">
         <v>3.3</v>
       </c>
-      <c r="R30">
-        <v>2.3</v>
-      </c>
-      <c r="S30">
-        <v>3.3</v>
-      </c>
-      <c r="T30">
-        <v>2.43</v>
-      </c>
-      <c r="U30">
-        <v>2.7</v>
-      </c>
-      <c r="V30">
-        <v>1.31</v>
-      </c>
-      <c r="W30">
-        <v>3.1</v>
-      </c>
-      <c r="X30">
-        <v>2.41</v>
-      </c>
-      <c r="Y30">
-        <v>1.49</v>
-      </c>
-      <c r="Z30">
-        <v>5.75</v>
-      </c>
-      <c r="AA30">
-        <v>1.07</v>
-      </c>
-      <c r="AB30">
-        <v>1.01</v>
-      </c>
-      <c r="AC30">
-        <v>1.15</v>
-      </c>
-      <c r="AD30">
-        <v>4.25</v>
-      </c>
-      <c r="AE30">
-        <v>1.65</v>
-      </c>
-      <c r="AF30">
-        <v>2.35</v>
-      </c>
-      <c r="AG30">
-        <v>2.23</v>
-      </c>
-      <c r="AH30">
-        <v>1.42</v>
-      </c>
-      <c r="AI30">
-        <v>4.6</v>
-      </c>
-      <c r="AJ30">
-        <v>1.13</v>
-      </c>
-      <c r="AK30">
-        <v>1.57</v>
-      </c>
-      <c r="AL30">
-        <v>2.39</v>
-      </c>
-      <c r="AM30">
-        <v>1.28</v>
-      </c>
-      <c r="AN30">
-        <v>1.41</v>
-      </c>
       <c r="AO30">
         <v>0</v>
       </c>
@@ -6665,19 +6665,19 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BD30">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BF30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,133 +6736,133 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q31">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>7.38</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,22 +6921,22 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6945,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6960,40 +6960,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7625,7 +7625,7 @@
         <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,79 +7661,79 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL36">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO36">
         <v>0</v>
@@ -7775,19 +7775,19 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC36">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD36">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF36">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV37">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ37">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB37">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC37">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -8031,13 +8031,13 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8070,40 +8070,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,133 +8216,133 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39">
+        <v>1.11</v>
+      </c>
+      <c r="AD39">
+        <v>4.95</v>
+      </c>
+      <c r="AE39">
+        <v>1.5</v>
+      </c>
+      <c r="AF39">
+        <v>2.41</v>
+      </c>
+      <c r="AG39">
+        <v>2.24</v>
+      </c>
+      <c r="AH39">
+        <v>1.61</v>
+      </c>
+      <c r="AI39">
+        <v>3.69</v>
+      </c>
+      <c r="AJ39">
+        <v>1.21</v>
+      </c>
+      <c r="AK39">
+        <v>1.47</v>
+      </c>
+      <c r="AL39">
+        <v>2.48</v>
+      </c>
+      <c r="AM39">
+        <v>1.2</v>
+      </c>
+      <c r="AN39">
+        <v>1.2</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
         <v>1.23</v>
       </c>
-      <c r="AD39">
-        <v>3.45</v>
-      </c>
-      <c r="AE39">
-        <v>1.77</v>
-      </c>
-      <c r="AF39">
-        <v>1.87</v>
-      </c>
-      <c r="AG39">
-        <v>2.9</v>
-      </c>
-      <c r="AH39">
-        <v>1.32</v>
-      </c>
-      <c r="AI39">
-        <v>5.1</v>
-      </c>
-      <c r="AJ39">
+      <c r="AQ39">
+        <v>1.48</v>
+      </c>
+      <c r="AR39">
+        <v>1.82</v>
+      </c>
+      <c r="AS39">
+        <v>2.4</v>
+      </c>
+      <c r="AT39">
+        <v>3.08</v>
+      </c>
+      <c r="AU39">
+        <v>3.4</v>
+      </c>
+      <c r="AV39">
+        <v>2.42</v>
+      </c>
+      <c r="AW39">
+        <v>1.81</v>
+      </c>
+      <c r="AX39">
+        <v>1.53</v>
+      </c>
+      <c r="AY39">
+        <v>1.29</v>
+      </c>
+      <c r="AZ39">
+        <v>2.18</v>
+      </c>
+      <c r="BA39">
+        <v>2.07</v>
+      </c>
+      <c r="BB39">
         <v>1.11</v>
       </c>
-      <c r="AK39">
-        <v>1.63</v>
-      </c>
-      <c r="AL39">
-        <v>2.1</v>
-      </c>
-      <c r="AM39">
-        <v>1.23</v>
-      </c>
-      <c r="AN39">
-        <v>1.32</v>
-      </c>
-      <c r="AO39">
-        <v>0</v>
-      </c>
-      <c r="AP39">
-        <v>0</v>
-      </c>
-      <c r="AQ39">
-        <v>0</v>
-      </c>
-      <c r="AR39">
-        <v>0</v>
-      </c>
-      <c r="AS39">
-        <v>0</v>
-      </c>
-      <c r="AT39">
-        <v>0</v>
-      </c>
-      <c r="AU39">
-        <v>0</v>
-      </c>
-      <c r="AV39">
-        <v>0</v>
-      </c>
-      <c r="AW39">
-        <v>0</v>
-      </c>
-      <c r="AX39">
-        <v>0</v>
-      </c>
-      <c r="AY39">
-        <v>0</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>0</v>
-      </c>
       <c r="BC39">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD39">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8362,10 +8362,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8401,133 +8401,133 @@
         <v>251</v>
       </c>
       <c r="P40">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q40">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AH40">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ40">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR40">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS40">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT40">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU40">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW40">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX40">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY40">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ40">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA40">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB40">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC40">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD40">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE40">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF40">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="Q43">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="R43">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="S43">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL43">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM43">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN43">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR43">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT43">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU43">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV43">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW43">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX43">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY43">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ43">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA43">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB43">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC43">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD43">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF43">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="R44">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE44">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9699,10 +9699,10 @@
         <v>6.5</v>
       </c>
       <c r="Q47">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="R47">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S47">
         <v>6.5</v>
@@ -9711,16 +9711,16 @@
         <v>2.5</v>
       </c>
       <c r="U47">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V47">
         <v>1.2</v>
       </c>
       <c r="W47">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="X47">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Y47">
         <v>1.64</v>
@@ -9735,16 +9735,16 @@
         <v>1.02</v>
       </c>
       <c r="AC47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD47">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AE47">
         <v>1.42</v>
       </c>
       <c r="AF47">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="AG47">
         <v>2.15</v>
@@ -9753,16 +9753,16 @@
         <v>1.65</v>
       </c>
       <c r="AI47">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK47">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL47">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="AM47">
         <v>3.05</v>
@@ -9774,31 +9774,31 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AQ47">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AR47">
+        <v>1.73</v>
+      </c>
+      <c r="AS47">
         <v>2.14</v>
       </c>
-      <c r="AS47">
-        <v>2.39</v>
-      </c>
       <c r="AT47">
-        <v>3.23</v>
+        <v>2.75</v>
       </c>
       <c r="AU47">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AV47">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AW47">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="AX47">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AY47">
         <v>1.38</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11877,10 +11877,10 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12435,7 +12435,7 @@
         <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E62" t="s">
         <v>170</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>
@@ -13921,7 +13921,7 @@
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>248</v>
+        <v>154</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14145,7 +14145,7 @@
         <v>2.79</v>
       </c>
       <c r="S71">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="T71">
         <v>2.19</v>
@@ -14157,7 +14157,7 @@
         <v>1.3</v>
       </c>
       <c r="W71">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="X71">
         <v>2.47</v>
@@ -14175,25 +14175,25 @@
         <v>1.04</v>
       </c>
       <c r="AC71">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD71">
-        <v>3.8</v>
+        <v>3.99</v>
       </c>
       <c r="AE71">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AF71">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG71">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AH71">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI71">
-        <v>5.06</v>
+        <v>4.75</v>
       </c>
       <c r="AJ71">
         <v>1.1</v>
@@ -14253,16 +14253,16 @@
         <v>1.16</v>
       </c>
       <c r="BC71">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="BD71">
         <v>4.1</v>
       </c>
       <c r="BE71">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BF71">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG71">
         <v>0</v>
@@ -14330,70 +14330,70 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI72">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN72">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14435,19 +14435,19 @@
         <v>0</v>
       </c>
       <c r="BB72">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC72">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD72">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG72">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,33 +280,33 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -355,15 +355,15 @@
     <t>Shanghai SIPG</t>
   </si>
   <si>
+    <t>Sidama Bunna</t>
+  </si>
+  <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,111 +376,111 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Hanácká</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Egersund</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
     <t>Vlašim</t>
   </si>
   <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Žalgiris</t>
   </si>
   <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Žalgiris</t>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Al Sharjah</t>
   </si>
   <si>
+    <t>Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>Spartak Varna</t>
+  </si>
+  <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Hammarby</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
-  </si>
-  <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
-    <t>Maccabi Haifa</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>AmaZulu</t>
   </si>
   <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
-    <t>Al Ahli</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Chapelton</t>
   </si>
   <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
   </si>
   <si>
     <t>MC Alger</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
+    <t>Al Hussein</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -568,15 +568,15 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Ethiopian Medhin</t>
+  </si>
+  <si>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,111 +589,111 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Slavia Praha U21</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Raufoss</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
     <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>FA Šiauliai</t>
   </si>
   <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>FA Šiauliai</t>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Al Ain</t>
   </si>
   <si>
+    <t>Hapoel Be'er Sheva</t>
+  </si>
+  <si>
+    <t>Dobrudzha 1919</t>
+  </si>
+  <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Uppsala W</t>
   </si>
   <si>
-    <t>Dobrudzha 1919</t>
-  </si>
-  <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
-    <t>Hapoel Be'er Sheva</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
+    <t>Al Fateh</t>
+  </si>
+  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
-    <t>Al Fateh</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Arnett Gardens</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
   </si>
   <si>
     <t>MB Rouisset</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
+    <t>Al Faisaly</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2111,133 +2111,133 @@
         <v>251</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,133 +2296,133 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR7">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS7">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU7">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV7">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW7">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX7">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY7">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ7">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD7">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -3045,13 +3045,13 @@
         <v>2.8</v>
       </c>
       <c r="S11">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="T11">
-        <v>2.03</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="V11">
         <v>1.41</v>
@@ -3060,10 +3060,10 @@
         <v>2.66</v>
       </c>
       <c r="X11">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="Y11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
         <v>6.95</v>
@@ -3096,7 +3096,7 @@
         <v>6</v>
       </c>
       <c r="AJ11">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
         <v>1.79</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3221,34 +3221,34 @@
         <v>251</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X12">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3260,40 +3260,40 @@
         <v>0</v>
       </c>
       <c r="AC12">
+        <v>1.33</v>
+      </c>
+      <c r="AD12">
+        <v>2.88</v>
+      </c>
+      <c r="AE12">
+        <v>2.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.63</v>
+      </c>
+      <c r="AG12">
+        <v>3.6</v>
+      </c>
+      <c r="AH12">
         <v>1.22</v>
       </c>
-      <c r="AD12">
-        <v>3.6</v>
-      </c>
-      <c r="AE12">
-        <v>1.72</v>
-      </c>
-      <c r="AF12">
-        <v>1.93</v>
-      </c>
-      <c r="AG12">
-        <v>2.8</v>
-      </c>
-      <c r="AH12">
-        <v>1.35</v>
-      </c>
       <c r="AI12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL12">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AM12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN12">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3367,10 +3367,10 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3552,10 +3552,10 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>122</v>
@@ -3591,35 +3591,35 @@
         <v>251</v>
       </c>
       <c r="P14">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T14">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2.55</v>
+      </c>
+      <c r="Y14">
         <v>1.38</v>
       </c>
-      <c r="W14">
-        <v>2.55</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
       <c r="Z14">
         <v>0</v>
       </c>
@@ -3630,91 +3630,91 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD14">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="AE14">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AF14">
+        <v>1.81</v>
+      </c>
+      <c r="AG14">
+        <v>3.05</v>
+      </c>
+      <c r="AH14">
+        <v>1.3</v>
+      </c>
+      <c r="AI14">
+        <v>5.4</v>
+      </c>
+      <c r="AJ14">
+        <v>1.1</v>
+      </c>
+      <c r="AK14">
+        <v>1.68</v>
+      </c>
+      <c r="AL14">
+        <v>2.04</v>
+      </c>
+      <c r="AM14">
+        <v>1.24</v>
+      </c>
+      <c r="AN14">
+        <v>1.56</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>2</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
         <v>1.63</v>
-      </c>
-      <c r="AG14">
-        <v>3.6</v>
-      </c>
-      <c r="AH14">
-        <v>1.22</v>
-      </c>
-      <c r="AI14">
-        <v>0</v>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>1.78</v>
-      </c>
-      <c r="AL14">
-        <v>1.81</v>
-      </c>
-      <c r="AM14">
-        <v>1.25</v>
-      </c>
-      <c r="AN14">
-        <v>1.49</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>0</v>
-      </c>
-      <c r="BC14">
-        <v>2.2</v>
-      </c>
-      <c r="BD14">
-        <v>0</v>
-      </c>
-      <c r="BE14">
-        <v>1.52</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3737,10 +3737,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3815,40 +3815,40 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="BC15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD15">
         <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3970,13 +3970,13 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T16">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U16">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4012,16 +4012,16 @@
         <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH16">
         <v>1.35</v>
       </c>
       <c r="AI16">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AJ16">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
         <v>1.58</v>
@@ -4033,7 +4033,7 @@
         <v>1.23</v>
       </c>
       <c r="AN16">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -4292,7 +4292,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>109</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4525,13 +4525,13 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -4540,10 +4540,10 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4555,40 +4555,40 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF19">
         <v>0</v>
@@ -4847,10 +4847,10 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -4886,133 +4886,133 @@
         <v>251</v>
       </c>
       <c r="P21">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC21">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD21">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF21">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5071,79 +5071,79 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO22">
         <v>0</v>
@@ -5185,19 +5185,19 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5256,79 +5256,79 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5370,19 +5370,19 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5441,79 +5441,79 @@
         <v>251</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5555,19 +5555,19 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24">
         <v>0</v>
@@ -5587,10 +5587,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E25" t="s">
         <v>133</v>
@@ -5626,133 +5626,133 @@
         <v>251</v>
       </c>
       <c r="P25">
-        <v>2.77</v>
+        <v>1.59</v>
       </c>
       <c r="Q25">
-        <v>3.29</v>
+        <v>4.1</v>
       </c>
       <c r="R25">
-        <v>2.43</v>
+        <v>4.99</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE25">
+        <v>1.67</v>
+      </c>
+      <c r="AF25">
+        <v>2.35</v>
+      </c>
+      <c r="AG25">
+        <v>2.31</v>
+      </c>
+      <c r="AH25">
+        <v>1.58</v>
+      </c>
+      <c r="AI25">
+        <v>3.74</v>
+      </c>
+      <c r="AJ25">
+        <v>1.23</v>
+      </c>
+      <c r="AK25">
+        <v>1.71</v>
+      </c>
+      <c r="AL25">
+        <v>2.18</v>
+      </c>
+      <c r="AM25">
+        <v>1.17</v>
+      </c>
+      <c r="AN25">
+        <v>2.27</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>1.08</v>
+      </c>
+      <c r="AQ25">
+        <v>1.23</v>
+      </c>
+      <c r="AR25">
+        <v>1.46</v>
+      </c>
+      <c r="AS25">
         <v>1.78</v>
       </c>
-      <c r="AF25">
+      <c r="AT25">
+        <v>2.2</v>
+      </c>
+      <c r="AU25">
+        <v>5.27</v>
+      </c>
+      <c r="AV25">
+        <v>3.42</v>
+      </c>
+      <c r="AW25">
+        <v>2.46</v>
+      </c>
+      <c r="AX25">
+        <v>1.93</v>
+      </c>
+      <c r="AY25">
+        <v>1.58</v>
+      </c>
+      <c r="AZ25">
+        <v>1.24</v>
+      </c>
+      <c r="BA25">
+        <v>2.88</v>
+      </c>
+      <c r="BB25">
+        <v>1.13</v>
+      </c>
+      <c r="BC25">
+        <v>1.73</v>
+      </c>
+      <c r="BD25">
+        <v>4.75</v>
+      </c>
+      <c r="BE25">
         <v>1.97</v>
       </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AI25">
-        <v>0</v>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>0</v>
-      </c>
-      <c r="AN25">
-        <v>0</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
-      <c r="BC25">
-        <v>0</v>
-      </c>
-      <c r="BD25">
-        <v>0</v>
-      </c>
-      <c r="BE25">
-        <v>0</v>
-      </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5996,13 +5996,13 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,133 +6551,133 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.58</v>
+        <v>3.44</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="U30">
-        <v>7.5</v>
+        <v>2.7</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="Y30">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AE30">
+        <v>1.72</v>
+      </c>
+      <c r="AF30">
+        <v>2.35</v>
+      </c>
+      <c r="AG30">
+        <v>2.23</v>
+      </c>
+      <c r="AH30">
+        <v>1.54</v>
+      </c>
+      <c r="AI30">
+        <v>4.65</v>
+      </c>
+      <c r="AJ30">
+        <v>1.12</v>
+      </c>
+      <c r="AK30">
+        <v>1.57</v>
+      </c>
+      <c r="AL30">
+        <v>2.37</v>
+      </c>
+      <c r="AM30">
+        <v>1.28</v>
+      </c>
+      <c r="AN30">
+        <v>1.4</v>
+      </c>
+      <c r="AO30">
+        <v>0</v>
+      </c>
+      <c r="AP30">
+        <v>1.3</v>
+      </c>
+      <c r="AQ30">
+        <v>1.67</v>
+      </c>
+      <c r="AR30">
+        <v>2.29</v>
+      </c>
+      <c r="AS30">
+        <v>2.56</v>
+      </c>
+      <c r="AT30">
+        <v>3.54</v>
+      </c>
+      <c r="AU30">
+        <v>3</v>
+      </c>
+      <c r="AV30">
+        <v>2.19</v>
+      </c>
+      <c r="AW30">
+        <v>1.74</v>
+      </c>
+      <c r="AX30">
         <v>1.42</v>
       </c>
-      <c r="AF30">
-        <v>2.55</v>
-      </c>
-      <c r="AG30">
-        <v>2.08</v>
-      </c>
-      <c r="AH30">
-        <v>1.62</v>
-      </c>
-      <c r="AI30">
-        <v>3.35</v>
-      </c>
-      <c r="AJ30">
+      <c r="AY30">
+        <v>1.21</v>
+      </c>
+      <c r="AZ30">
+        <v>2.13</v>
+      </c>
+      <c r="BA30">
+        <v>2.13</v>
+      </c>
+      <c r="BB30">
+        <v>1.14</v>
+      </c>
+      <c r="BC30">
+        <v>1.86</v>
+      </c>
+      <c r="BD30">
+        <v>4.6</v>
+      </c>
+      <c r="BE30">
+        <v>1.87</v>
+      </c>
+      <c r="BF30">
         <v>1.25</v>
-      </c>
-      <c r="AK30">
-        <v>1.84</v>
-      </c>
-      <c r="AL30">
-        <v>1.8</v>
-      </c>
-      <c r="AM30">
-        <v>1.08</v>
-      </c>
-      <c r="AN30">
-        <v>3.3</v>
-      </c>
-      <c r="AO30">
-        <v>0</v>
-      </c>
-      <c r="AP30">
-        <v>0</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30">
-        <v>0</v>
-      </c>
-      <c r="AV30">
-        <v>0</v>
-      </c>
-      <c r="AW30">
-        <v>0</v>
-      </c>
-      <c r="AX30">
-        <v>0</v>
-      </c>
-      <c r="AY30">
-        <v>0</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>0</v>
-      </c>
-      <c r="BC30">
-        <v>1.63</v>
-      </c>
-      <c r="BD30">
-        <v>0</v>
-      </c>
-      <c r="BE30">
-        <v>2</v>
-      </c>
-      <c r="BF30">
-        <v>0</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,133 +6736,133 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>2.65</v>
+        <v>1.33</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>7.38</v>
       </c>
       <c r="S31">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,22 +6921,22 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6945,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6960,40 +6960,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7252,7 +7252,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7625,7 +7625,7 @@
         <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7661,133 +7661,133 @@
         <v>251</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AM36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AU36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV36">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AW36">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ36">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA36">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD36">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7855,13 +7855,13 @@
         <v>2.4</v>
       </c>
       <c r="S37">
-        <v>3.87</v>
+        <v>4.04</v>
       </c>
       <c r="T37">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="U37">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="V37">
         <v>1.46</v>
@@ -7903,7 +7903,7 @@
         <v>1.18</v>
       </c>
       <c r="AI37">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AJ37">
         <v>1.02</v>
@@ -8180,7 +8180,7 @@
         <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8216,133 +8216,133 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AR39">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AS39">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AT39">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AU39">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV39">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AW39">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AX39">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ39">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BA39">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC39">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD39">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,133 +8586,133 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT41">
         <v>0</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY41">
         <v>0</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8771,13 +8771,13 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -8816,10 +8816,10 @@
         <v>0</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="Q43">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R43">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE43">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU43">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW43">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX43">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BA43">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD43">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9144,10 +9144,10 @@
         <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="R44">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="S44">
         <v>2.7</v>
@@ -9177,7 +9177,7 @@
         <v>1</v>
       </c>
       <c r="AB44">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AC44">
         <v>1.37</v>
@@ -9192,13 +9192,13 @@
         <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AH44">
         <v>1.16</v>
       </c>
       <c r="AI44">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44">
         <v>1.01</v>
@@ -9207,7 +9207,7 @@
         <v>1.88</v>
       </c>
       <c r="AL44">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AM44">
         <v>1.3</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9326,13 +9326,13 @@
         <v>251</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9881,40 +9881,40 @@
         <v>251</v>
       </c>
       <c r="P48">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q48">
-        <v>4.55</v>
+        <v>5.05</v>
       </c>
       <c r="R48">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="S48">
         <v>2.09</v>
       </c>
       <c r="T48">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U48">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="V48">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W48">
-        <v>6.65</v>
+        <v>6.4</v>
       </c>
       <c r="X48">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Y48">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="Z48">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AA48">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AB48">
         <v>1.01</v>
@@ -9926,88 +9926,88 @@
         <v>11</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AG48">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AH48">
-        <v>2.48</v>
+        <v>2.57</v>
       </c>
       <c r="AI48">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ48">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AK48">
         <v>1.25</v>
       </c>
       <c r="AL48">
-        <v>3.91</v>
+        <v>4.01</v>
       </c>
       <c r="AM48">
         <v>1.2</v>
       </c>
       <c r="AN48">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AO48">
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AQ48">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR48">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS48">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AT48">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AU48">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV48">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AW48">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AX48">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AY48">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AZ48">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BA48">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BC48">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="BD48">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BE48">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="BF48">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BG48">
         <v>0</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11877,10 +11877,10 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
@@ -12062,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12247,10 +12247,10 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E61" t="s">
         <v>169</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>153</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13357,7 +13357,7 @@
         <v>79</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D67" t="s">
         <v>109</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>79</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D70" t="s">
         <v>109</v>
@@ -13921,7 +13921,7 @@
         <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -14345,7 +14345,7 @@
         <v>2.88</v>
       </c>
       <c r="X72">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="Y72">
         <v>1.39</v>
@@ -14375,7 +14375,7 @@
         <v>3.08</v>
       </c>
       <c r="AH72">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AI72">
         <v>6</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,33 +280,33 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Morocco Botola Pro</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Morocco Botola Pro</t>
+    <t>Sweden Damallsvenskan</t>
   </si>
   <si>
     <t>Israel Israeli Premier League</t>
   </si>
   <si>
-    <t>Sweden Damallsvenskan</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,18 +349,18 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
+    <t>Yunnan Yukun</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
@@ -376,58 +376,61 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
     <t>Baník Ostrava U21</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Egersund</t>
+  </si>
+  <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Paphos</t>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Egersund</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Ústí nad Labem</t>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Hapoel Tel Aviv</t>
@@ -436,18 +439,15 @@
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Häcken W</t>
+    <t>Shabab Al Ahli Dubai</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Shabab Al Ahli Dubai</t>
-  </si>
-  <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
@@ -463,18 +463,18 @@
     <t>Gagra</t>
   </si>
   <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -490,69 +490,69 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
-    <t>Waterhouse</t>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
   </si>
   <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Cavalier</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
   </si>
   <si>
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
   </si>
   <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
     <t>JS Kabylie</t>
   </si>
   <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,18 +562,18 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Zhejiang FC</t>
   </si>
   <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Zhejiang FC</t>
-  </si>
-  <si>
     <t>Bahardar</t>
   </si>
   <si>
@@ -589,58 +589,61 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
     <t>Zbrojovka Brno</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
     <t>Příbram</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Opava</t>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>Beitar Jerusalem</t>
@@ -649,18 +652,15 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Djurgården W</t>
+    <t>Al Nasr</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Nasr</t>
-  </si>
-  <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
@@ -676,18 +676,18 @@
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -703,64 +703,64 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Harbour View</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
     <t>Montego Bay United</t>
   </si>
   <si>
-    <t>Dunbeholden</t>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
   </si>
   <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Harbour View</t>
-  </si>
-  <si>
-    <t>Racing United</t>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>Al Salt</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
     <t>ASO Chlef</t>
   </si>
   <si>
-    <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
   </si>
   <si>
     <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1380,124 +1380,124 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ2">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR2">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS2">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AT2">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="AU2">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV2">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW2">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX2">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY2">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ2">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA2">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BB2">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC2">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD2">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE2">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF2">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1565,124 +1565,124 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T3">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U3">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="V3">
+        <v>1.27</v>
+      </c>
+      <c r="W3">
+        <v>3.35</v>
+      </c>
+      <c r="X3">
+        <v>2.47</v>
+      </c>
+      <c r="Y3">
+        <v>1.47</v>
+      </c>
+      <c r="Z3">
+        <v>5.9</v>
+      </c>
+      <c r="AA3">
+        <v>1.07</v>
+      </c>
+      <c r="AB3">
+        <v>1.03</v>
+      </c>
+      <c r="AC3">
         <v>1.23</v>
       </c>
-      <c r="W3">
-        <v>3.52</v>
-      </c>
-      <c r="X3">
-        <v>2.21</v>
-      </c>
-      <c r="Y3">
-        <v>1.61</v>
-      </c>
-      <c r="Z3">
-        <v>4.8</v>
-      </c>
-      <c r="AA3">
-        <v>1.14</v>
-      </c>
-      <c r="AB3">
-        <v>1.01</v>
-      </c>
-      <c r="AC3">
-        <v>1.15</v>
-      </c>
       <c r="AD3">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="AE3">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AF3">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AH3">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AI3">
-        <v>3.78</v>
+        <v>4.7</v>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AK3">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL3">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AM3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN3">
-        <v>2.02</v>
+        <v>2.41</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AR3">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AS3">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AT3">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AU3">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="AV3">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="AW3">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AX3">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AY3">
         <v>1.38</v>
       </c>
       <c r="AZ3">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="BA3">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="BB3">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BC3">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="BD3">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="BF3">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1750,124 +1750,124 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ4">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR4">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AS4">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT4">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU4">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV4">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY4">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ4">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA4">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC4">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD4">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE4">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF4">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,133 +1926,133 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2072,10 +2072,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2111,133 +2111,133 @@
         <v>251</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL6">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD6">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE6">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF6">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3221,35 +3221,35 @@
         <v>251</v>
       </c>
       <c r="P12">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>2.55</v>
+      </c>
+      <c r="Y12">
         <v>1.38</v>
       </c>
-      <c r="W12">
-        <v>2.55</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
       <c r="Z12">
         <v>0</v>
       </c>
@@ -3260,91 +3260,91 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD12">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="AE12">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AF12">
+        <v>1.81</v>
+      </c>
+      <c r="AG12">
+        <v>3.05</v>
+      </c>
+      <c r="AH12">
+        <v>1.3</v>
+      </c>
+      <c r="AI12">
+        <v>5.4</v>
+      </c>
+      <c r="AJ12">
+        <v>1.1</v>
+      </c>
+      <c r="AK12">
+        <v>1.68</v>
+      </c>
+      <c r="AL12">
+        <v>2.04</v>
+      </c>
+      <c r="AM12">
+        <v>1.24</v>
+      </c>
+      <c r="AN12">
+        <v>1.56</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>2</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
         <v>1.63</v>
-      </c>
-      <c r="AG12">
-        <v>3.6</v>
-      </c>
-      <c r="AH12">
-        <v>1.22</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>1.78</v>
-      </c>
-      <c r="AL12">
-        <v>1.81</v>
-      </c>
-      <c r="AM12">
-        <v>1.25</v>
-      </c>
-      <c r="AN12">
-        <v>1.49</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>2.2</v>
-      </c>
-      <c r="BD12">
-        <v>0</v>
-      </c>
-      <c r="BE12">
-        <v>1.52</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3430,10 +3430,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3445,40 +3445,40 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3523,13 +3523,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3600,70 +3600,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U14">
+        <v>2.95</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2.43</v>
+      </c>
+      <c r="Y14">
+        <v>1.43</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>1.22</v>
+      </c>
+      <c r="AD14">
         <v>3.6</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>2.55</v>
-      </c>
-      <c r="Y14">
-        <v>1.38</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>1.25</v>
-      </c>
-      <c r="AD14">
-        <v>3.35</v>
-      </c>
       <c r="AE14">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF14">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG14">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AH14">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI14">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL14">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AM14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN14">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -3922,7 +3922,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3970,13 +3970,13 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -3985,10 +3985,10 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4000,40 +4000,40 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4078,13 +4078,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
         <v>108</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4331,28 +4331,28 @@
         <v>251</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -4370,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -4394,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4448,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD18">
         <v>0</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4525,13 +4525,13 @@
         <v>0</v>
       </c>
       <c r="S19">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V19">
         <v>0</v>
@@ -4540,10 +4540,10 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -4555,40 +4555,40 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH19">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL19">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="BC19">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF19">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5071,79 +5071,79 @@
         <v>251</v>
       </c>
       <c r="P22">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH22">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL22">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN22">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <v>0</v>
@@ -5185,19 +5185,19 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC22">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD22">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE22">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF22">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5256,79 +5256,79 @@
         <v>251</v>
       </c>
       <c r="P23">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R23">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S23">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="V23">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W23">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X23">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z23">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5370,19 +5370,19 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD23">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF23">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG23">
         <v>0</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5441,76 +5441,76 @@
         <v>251</v>
       </c>
       <c r="P24">
-        <v>2.03</v>
+        <v>2.77</v>
       </c>
       <c r="Q24">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="R24">
-        <v>3.45</v>
+        <v>2.43</v>
       </c>
       <c r="S24">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="T24">
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="U24">
-        <v>4.57</v>
+        <v>3.69</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>1.31</v>
       </c>
       <c r="W24">
-        <v>2.39</v>
+        <v>3.1</v>
       </c>
       <c r="X24">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="Z24">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB24">
         <v>1.04</v>
       </c>
       <c r="AC24">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AD24">
-        <v>2.74</v>
+        <v>3.95</v>
       </c>
       <c r="AE24">
-        <v>2.28</v>
+        <v>1.78</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AG24">
-        <v>4.01</v>
+        <v>2.69</v>
       </c>
       <c r="AH24">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI24">
-        <v>7.7</v>
+        <v>5.05</v>
       </c>
       <c r="AJ24">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK24">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="AM24">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN24">
         <v>1.64</v>
@@ -5555,19 +5555,19 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC24">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="BD24">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BE24">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="BF24">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG24">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
         <v>108</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5811,79 +5811,79 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5925,19 +5925,19 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6366,79 +6366,79 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -6480,19 +6480,19 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,133 +6551,133 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>1.58</v>
+      </c>
+      <c r="T30">
+        <v>2.88</v>
+      </c>
+      <c r="U30">
+        <v>7.5</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>1.98</v>
+      </c>
+      <c r="Y30">
+        <v>1.64</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>1.11</v>
+      </c>
+      <c r="AD30">
+        <v>5</v>
+      </c>
+      <c r="AE30">
+        <v>1.42</v>
+      </c>
+      <c r="AF30">
+        <v>2.55</v>
+      </c>
+      <c r="AG30">
+        <v>2.08</v>
+      </c>
+      <c r="AH30">
+        <v>1.62</v>
+      </c>
+      <c r="AI30">
+        <v>3.35</v>
+      </c>
+      <c r="AJ30">
+        <v>1.25</v>
+      </c>
+      <c r="AK30">
+        <v>1.84</v>
+      </c>
+      <c r="AL30">
+        <v>1.8</v>
+      </c>
+      <c r="AM30">
+        <v>1.08</v>
+      </c>
+      <c r="AN30">
         <v>3.3</v>
       </c>
-      <c r="R30">
-        <v>2.3</v>
-      </c>
-      <c r="S30">
-        <v>3.44</v>
-      </c>
-      <c r="T30">
-        <v>2.43</v>
-      </c>
-      <c r="U30">
-        <v>2.7</v>
-      </c>
-      <c r="V30">
-        <v>1.31</v>
-      </c>
-      <c r="W30">
-        <v>3.1</v>
-      </c>
-      <c r="X30">
-        <v>2.44</v>
-      </c>
-      <c r="Y30">
-        <v>1.48</v>
-      </c>
-      <c r="Z30">
-        <v>5.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.07</v>
-      </c>
-      <c r="AB30">
-        <v>1.01</v>
-      </c>
-      <c r="AC30">
-        <v>1.15</v>
-      </c>
-      <c r="AD30">
-        <v>4.2</v>
-      </c>
-      <c r="AE30">
-        <v>1.72</v>
-      </c>
-      <c r="AF30">
-        <v>2.35</v>
-      </c>
-      <c r="AG30">
-        <v>2.23</v>
-      </c>
-      <c r="AH30">
-        <v>1.54</v>
-      </c>
-      <c r="AI30">
-        <v>4.65</v>
-      </c>
-      <c r="AJ30">
-        <v>1.12</v>
-      </c>
-      <c r="AK30">
-        <v>1.57</v>
-      </c>
-      <c r="AL30">
-        <v>2.37</v>
-      </c>
-      <c r="AM30">
-        <v>1.28</v>
-      </c>
-      <c r="AN30">
-        <v>1.4</v>
-      </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="BD30">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="BF30">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,10 +6697,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,133 +6736,133 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>1.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q31">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="R31">
-        <v>7.38</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE31">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6921,22 +6921,22 @@
         <v>251</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6945,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6960,40 +6960,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7038,13 +7038,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,133 +8586,133 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q41">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="R41">
-        <v>7</v>
+        <v>3.17</v>
       </c>
       <c r="S41">
-        <v>2.01</v>
+        <v>3.16</v>
       </c>
       <c r="T41">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="U41">
-        <v>7.8</v>
+        <v>4.39</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W41">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="X41">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z41">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA41">
         <v>1.01</v>
       </c>
       <c r="AB41">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC41">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AD41">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="AE41">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AG41">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="AH41">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AI41">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AJ41">
+        <v>1.02</v>
+      </c>
+      <c r="AK41">
+        <v>2.4</v>
+      </c>
+      <c r="AL41">
+        <v>1.5</v>
+      </c>
+      <c r="AM41">
+        <v>1.33</v>
+      </c>
+      <c r="AN41">
+        <v>1.5</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>1.34</v>
+      </c>
+      <c r="AQ41">
+        <v>1.58</v>
+      </c>
+      <c r="AR41">
+        <v>1.94</v>
+      </c>
+      <c r="AS41">
+        <v>2.48</v>
+      </c>
+      <c r="AT41">
+        <v>3.25</v>
+      </c>
+      <c r="AU41">
+        <v>2.95</v>
+      </c>
+      <c r="AV41">
+        <v>2.2</v>
+      </c>
+      <c r="AW41">
+        <v>1.75</v>
+      </c>
+      <c r="AX41">
+        <v>1.47</v>
+      </c>
+      <c r="AY41">
+        <v>1.29</v>
+      </c>
+      <c r="AZ41">
+        <v>1.8</v>
+      </c>
+      <c r="BA41">
+        <v>2.18</v>
+      </c>
+      <c r="BB41">
+        <v>1.43</v>
+      </c>
+      <c r="BC41">
+        <v>3.18</v>
+      </c>
+      <c r="BD41">
+        <v>2.53</v>
+      </c>
+      <c r="BE41">
+        <v>1.28</v>
+      </c>
+      <c r="BF41">
         <v>1.01</v>
-      </c>
-      <c r="AK41">
-        <v>2.45</v>
-      </c>
-      <c r="AL41">
-        <v>1.48</v>
-      </c>
-      <c r="AM41">
-        <v>1.19</v>
-      </c>
-      <c r="AN41">
-        <v>2.5</v>
-      </c>
-      <c r="AO41">
-        <v>0</v>
-      </c>
-      <c r="AP41">
-        <v>1.5</v>
-      </c>
-      <c r="AQ41">
-        <v>1.89</v>
-      </c>
-      <c r="AR41">
-        <v>2.4</v>
-      </c>
-      <c r="AS41">
-        <v>3.15</v>
-      </c>
-      <c r="AT41">
-        <v>0</v>
-      </c>
-      <c r="AU41">
-        <v>2.33</v>
-      </c>
-      <c r="AV41">
-        <v>1.8</v>
-      </c>
-      <c r="AW41">
-        <v>1.49</v>
-      </c>
-      <c r="AX41">
-        <v>1.3</v>
-      </c>
-      <c r="AY41">
-        <v>0</v>
-      </c>
-      <c r="AZ41">
-        <v>1.28</v>
-      </c>
-      <c r="BA41">
-        <v>3.95</v>
-      </c>
-      <c r="BB41">
-        <v>1.29</v>
-      </c>
-      <c r="BC41">
-        <v>2.44</v>
-      </c>
-      <c r="BD41">
-        <v>3.12</v>
-      </c>
-      <c r="BE41">
-        <v>1.46</v>
-      </c>
-      <c r="BF41">
-        <v>1.08</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8771,133 +8771,133 @@
         <v>251</v>
       </c>
       <c r="P42">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q42">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="R42">
-        <v>2.77</v>
+        <v>7</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE42">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO42">
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT42">
         <v>0</v>
       </c>
       <c r="AU42">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW42">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY42">
         <v>0</v>
       </c>
       <c r="AZ42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA42">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC42">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD42">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q43">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="R43">
-        <v>3.17</v>
+        <v>3.92</v>
       </c>
       <c r="S43">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="T43">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="U43">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W43">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="X43">
+        <v>3.3</v>
+      </c>
+      <c r="Y43">
+        <v>1.27</v>
+      </c>
+      <c r="Z43">
+        <v>9</v>
+      </c>
+      <c r="AA43">
+        <v>1</v>
+      </c>
+      <c r="AB43">
+        <v>1.04</v>
+      </c>
+      <c r="AC43">
+        <v>1.37</v>
+      </c>
+      <c r="AD43">
+        <v>2.66</v>
+      </c>
+      <c r="AE43">
+        <v>2.27</v>
+      </c>
+      <c r="AF43">
+        <v>1.56</v>
+      </c>
+      <c r="AG43">
         <v>4.2</v>
       </c>
-      <c r="Y43">
-        <v>1.15</v>
-      </c>
-      <c r="Z43">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA43">
+      <c r="AH43">
+        <v>1.16</v>
+      </c>
+      <c r="AI43">
+        <v>8.5</v>
+      </c>
+      <c r="AJ43">
         <v>1.01</v>
       </c>
-      <c r="AB43">
-        <v>1.08</v>
-      </c>
-      <c r="AC43">
-        <v>1.66</v>
-      </c>
-      <c r="AD43">
-        <v>2.09</v>
-      </c>
-      <c r="AE43">
-        <v>3.04</v>
-      </c>
-      <c r="AF43">
-        <v>1.29</v>
-      </c>
-      <c r="AG43">
-        <v>5.25</v>
-      </c>
-      <c r="AH43">
-        <v>1.12</v>
-      </c>
-      <c r="AI43">
-        <v>11</v>
-      </c>
-      <c r="AJ43">
-        <v>1.02</v>
-      </c>
       <c r="AK43">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AL43">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AM43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN43">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
+        <v>1.47</v>
+      </c>
+      <c r="AR43">
+        <v>1.77</v>
+      </c>
+      <c r="AS43">
+        <v>2.2</v>
+      </c>
+      <c r="AT43">
+        <v>2.85</v>
+      </c>
+      <c r="AU43">
+        <v>3.3</v>
+      </c>
+      <c r="AV43">
+        <v>2.45</v>
+      </c>
+      <c r="AW43">
+        <v>1.92</v>
+      </c>
+      <c r="AX43">
         <v>1.58</v>
       </c>
-      <c r="AR43">
-        <v>1.94</v>
-      </c>
-      <c r="AS43">
-        <v>2.48</v>
-      </c>
-      <c r="AT43">
-        <v>3.25</v>
-      </c>
-      <c r="AU43">
-        <v>2.95</v>
-      </c>
-      <c r="AV43">
-        <v>2.2</v>
-      </c>
-      <c r="AW43">
-        <v>1.75</v>
-      </c>
-      <c r="AX43">
+      <c r="AY43">
+        <v>1.36</v>
+      </c>
+      <c r="AZ43">
+        <v>1.84</v>
+      </c>
+      <c r="BA43">
+        <v>2.08</v>
+      </c>
+      <c r="BB43">
+        <v>1.28</v>
+      </c>
+      <c r="BC43">
+        <v>2.5</v>
+      </c>
+      <c r="BD43">
+        <v>3.18</v>
+      </c>
+      <c r="BE43">
         <v>1.47</v>
       </c>
-      <c r="AY43">
-        <v>1.29</v>
-      </c>
-      <c r="AZ43">
-        <v>1.8</v>
-      </c>
-      <c r="BA43">
-        <v>2.18</v>
-      </c>
-      <c r="BB43">
-        <v>1.43</v>
-      </c>
-      <c r="BC43">
-        <v>3.18</v>
-      </c>
-      <c r="BD43">
-        <v>2.53</v>
-      </c>
-      <c r="BE43">
-        <v>1.28</v>
-      </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="Q44">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="R44">
-        <v>3.92</v>
+        <v>2.77</v>
       </c>
       <c r="S44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL44">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN44">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS44">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT44">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV44">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW44">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX44">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC44">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD44">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -10027,7 +10027,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>153</v>
+        <v>242</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12802,7 +12802,7 @@
         <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
         <v>109</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,7 +13542,7 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
         <v>109</v>
@@ -13551,7 +13551,7 @@
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13727,7 +13727,7 @@
         <v>79</v>
       </c>
       <c r="C69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D69" t="s">
         <v>109</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14136,13 +14136,13 @@
         <v>251</v>
       </c>
       <c r="P71">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q71">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="R71">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="S71">
         <v>2.78</v>
@@ -14178,13 +14178,13 @@
         <v>1.18</v>
       </c>
       <c r="AD71">
-        <v>3.99</v>
+        <v>3.82</v>
       </c>
       <c r="AE71">
         <v>1.71</v>
       </c>
       <c r="AF71">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AG71">
         <v>2.7</v>
@@ -14259,7 +14259,7 @@
         <v>4.1</v>
       </c>
       <c r="BE71">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BF71">
         <v>1.18</v>
@@ -14330,70 +14330,70 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z72">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD72">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG72">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH72">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI72">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ72">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK72">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL72">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM72">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN72">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14435,19 +14435,19 @@
         <v>0</v>
       </c>
       <c r="BB72">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC72">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD72">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE72">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF72">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG72">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,27 +280,27 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Latvia Virsliga</t>
+  </si>
+  <si>
     <t>Czech Republic FNL</t>
   </si>
   <si>
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
-    <t>Latvia Virsliga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Cyprus First Division</t>
   </si>
   <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
@@ -325,12 +325,12 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Jordan Jordanian Pro League</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Jordan Jordanian Pro League</t>
-  </si>
-  <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
@@ -349,21 +349,21 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
+    <t>Fasil Ketema</t>
+  </si>
+  <si>
+    <t>Sidama Bunna</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
     <t>Kaisar</t>
   </si>
   <si>
@@ -376,13 +376,22 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
   </si>
   <si>
     <t>Samgurali</t>
@@ -391,45 +400,36 @@
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>FUS Rabat</t>
+  </si>
+  <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
-    <t>FUS Rabat</t>
-  </si>
-  <si>
-    <t>Táborsko</t>
+    <t>Egersund</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Egersund</t>
+    <t>AEK Larnaca</t>
   </si>
   <si>
     <t>Aris</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
     <t>Häcken W</t>
   </si>
   <si>
@@ -439,15 +439,15 @@
     <t>Žalgiris</t>
   </si>
   <si>
+    <t>Barcelona W</t>
+  </si>
+  <si>
+    <t>Al Sharjah</t>
+  </si>
+  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
@@ -466,15 +466,15 @@
     <t>Richards Bay</t>
   </si>
   <si>
+    <t>Marumo Gallants</t>
+  </si>
+  <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Al Ahli</t>
   </si>
   <si>
@@ -496,24 +496,36 @@
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Waterhouse</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
+    <t>Al Wihdat</t>
   </si>
   <si>
     <t>Oued Akbou</t>
   </si>
   <si>
+    <t>Al Hussein</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
@@ -523,6 +535,15 @@
     <t>Al Jazeera</t>
   </si>
   <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
     <t>Sporting KC II</t>
   </si>
   <si>
@@ -532,27 +553,6 @@
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,21 +562,21 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
+    <t>Bahardar</t>
+  </si>
+  <si>
+    <t>Ethiopian Medhin</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
     <t>Kairat</t>
   </si>
   <si>
@@ -589,13 +589,22 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
   </si>
   <si>
     <t>Meshakhte</t>
@@ -604,45 +613,36 @@
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Ittihad Tanger</t>
+  </si>
+  <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Příbram</t>
   </si>
   <si>
-    <t>Ittihad Tanger</t>
-  </si>
-  <si>
-    <t>Chrudim</t>
+    <t>Raufoss</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Raufoss</t>
+    <t>Apollon</t>
   </si>
   <si>
     <t>APOEL</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
     <t>Djurgården W</t>
   </si>
   <si>
@@ -652,15 +652,15 @@
     <t>FA Šiauliai</t>
   </si>
   <si>
+    <t>Levante W</t>
+  </si>
+  <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
     <t>Al Nasr</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
@@ -679,15 +679,15 @@
     <t>Polokwane City</t>
   </si>
   <si>
+    <t>TS Galaxy</t>
+  </si>
+  <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>Al Fateh</t>
   </si>
   <si>
@@ -709,24 +709,33 @@
     <t>Racing United</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Dunbeholden</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
+    <t>MB Rouisset</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
     <t>USM Alger</t>
   </si>
   <si>
@@ -736,6 +745,15 @@
     <t>Al Salt</t>
   </si>
   <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
   </si>
   <si>
@@ -743,24 +761,6 @@
   </si>
   <si>
     <t>Sama Al Sarhan</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1565,124 +1565,124 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR3">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS3">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU3">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AV3">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AW3">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX3">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ3">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BA3">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB3">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC3">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD3">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE3">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1750,124 +1750,124 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AO4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1887,10 +1887,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1926,133 +1926,133 @@
         <v>251</v>
       </c>
       <c r="P5">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
@@ -2296,133 +2296,133 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3221,130 +3221,130 @@
         <v>251</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S12">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="T12">
+        <v>2.1</v>
+      </c>
+      <c r="U12">
+        <v>3.5</v>
+      </c>
+      <c r="V12">
+        <v>1.38</v>
+      </c>
+      <c r="W12">
+        <v>2.55</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>1.33</v>
+      </c>
+      <c r="AD12">
+        <v>2.88</v>
+      </c>
+      <c r="AE12">
+        <v>2.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.63</v>
+      </c>
+      <c r="AG12">
+        <v>3.6</v>
+      </c>
+      <c r="AH12">
+        <v>1.22</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>1.78</v>
+      </c>
+      <c r="AL12">
+        <v>1.81</v>
+      </c>
+      <c r="AM12">
+        <v>1.25</v>
+      </c>
+      <c r="AN12">
+        <v>1.49</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
         <v>2.2</v>
       </c>
-      <c r="U12">
-        <v>3.6</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>2.55</v>
-      </c>
-      <c r="Y12">
-        <v>1.38</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>1.25</v>
-      </c>
-      <c r="AD12">
-        <v>3.35</v>
-      </c>
-      <c r="AE12">
-        <v>1.83</v>
-      </c>
-      <c r="AF12">
-        <v>1.81</v>
-      </c>
-      <c r="AG12">
-        <v>3.05</v>
-      </c>
-      <c r="AH12">
-        <v>1.3</v>
-      </c>
-      <c r="AI12">
-        <v>5.4</v>
-      </c>
-      <c r="AJ12">
-        <v>1.1</v>
-      </c>
-      <c r="AK12">
-        <v>1.68</v>
-      </c>
-      <c r="AL12">
-        <v>2.04</v>
-      </c>
-      <c r="AM12">
-        <v>1.24</v>
-      </c>
-      <c r="AN12">
-        <v>1.56</v>
-      </c>
-      <c r="AO12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>2</v>
-      </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3367,7 +3367,7 @@
         <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>109</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T13">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U13">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3457,16 +3457,16 @@
         <v>1.93</v>
       </c>
       <c r="AG13">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH13">
         <v>1.35</v>
       </c>
       <c r="AI13">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AJ13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK13">
         <v>1.58</v>
@@ -3478,7 +3478,7 @@
         <v>1.23</v>
       </c>
       <c r="AN13">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3523,13 +3523,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3600,13 +3600,13 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="U14">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3642,16 +3642,16 @@
         <v>1.93</v>
       </c>
       <c r="AG14">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH14">
         <v>1.35</v>
       </c>
       <c r="AI14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
         <v>1.58</v>
@@ -3663,7 +3663,7 @@
         <v>1.23</v>
       </c>
       <c r="AN14">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3815,40 +3815,40 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD15">
         <v>0</v>
       </c>
       <c r="BE15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4110,7 +4110,7 @@
         <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>125</v>
@@ -4331,28 +4331,28 @@
         <v>251</v>
       </c>
       <c r="P18">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -4370,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -4394,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL18">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4448,13 +4448,13 @@
         <v>0</v>
       </c>
       <c r="BC18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD18">
         <v>0</v>
       </c>
       <c r="BE18">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4477,7 +4477,7 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
         <v>109</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5441,79 +5441,79 @@
         <v>251</v>
       </c>
       <c r="P24">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL24">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5555,19 +5555,19 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD24">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE24">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF24">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG24">
         <v>0</v>
@@ -5587,7 +5587,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" t="s">
         <v>108</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5811,79 +5811,79 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5925,19 +5925,19 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5996,79 +5996,79 @@
         <v>251</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -6110,19 +6110,19 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6181,79 +6181,79 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -6295,19 +6295,19 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>109</v>
@@ -6366,79 +6366,79 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Q29">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="R29">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="S29">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="U29">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="V29">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W29">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="X29">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="Y29">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z29">
-        <v>7.7</v>
+        <v>6.1</v>
       </c>
       <c r="AA29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AB29">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC29">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AD29">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="AE29">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="AF29">
-        <v>1.61</v>
+        <v>1.97</v>
       </c>
       <c r="AG29">
-        <v>4.01</v>
+        <v>2.7</v>
       </c>
       <c r="AH29">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI29">
-        <v>7.7</v>
+        <v>5.22</v>
       </c>
       <c r="AJ29">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK29">
-        <v>1.89</v>
+        <v>1.63</v>
       </c>
       <c r="AL29">
-        <v>1.81</v>
+        <v>2.14</v>
       </c>
       <c r="AM29">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AN29">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AO29">
         <v>0</v>
@@ -6480,19 +6480,19 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="BC29">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="BD29">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BE29">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="BF29">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7437,7 +7437,7 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
         <v>109</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8771,133 +8771,133 @@
         <v>251</v>
       </c>
       <c r="P42">
+        <v>2.41</v>
+      </c>
+      <c r="Q42">
+        <v>2.9</v>
+      </c>
+      <c r="R42">
+        <v>2.77</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
+        <v>2.62</v>
+      </c>
+      <c r="AF42">
         <v>1.44</v>
       </c>
-      <c r="Q42">
-        <v>3.6</v>
-      </c>
-      <c r="R42">
-        <v>7</v>
-      </c>
-      <c r="S42">
-        <v>2.01</v>
-      </c>
-      <c r="T42">
-        <v>2.06</v>
-      </c>
-      <c r="U42">
-        <v>7.8</v>
-      </c>
-      <c r="V42">
-        <v>1.45</v>
-      </c>
-      <c r="W42">
-        <v>2.47</v>
-      </c>
-      <c r="X42">
-        <v>3.18</v>
-      </c>
-      <c r="Y42">
-        <v>1.28</v>
-      </c>
-      <c r="Z42">
-        <v>8.4</v>
-      </c>
-      <c r="AA42">
-        <v>1.01</v>
-      </c>
-      <c r="AB42">
-        <v>1.03</v>
-      </c>
-      <c r="AC42">
-        <v>1.38</v>
-      </c>
-      <c r="AD42">
-        <v>2.62</v>
-      </c>
-      <c r="AE42">
-        <v>2.25</v>
-      </c>
-      <c r="AF42">
-        <v>1.57</v>
-      </c>
       <c r="AG42">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI42">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AJ42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL42">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AM42">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN42">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO42">
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ42">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AR42">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AS42">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT42">
         <v>0</v>
       </c>
       <c r="AU42">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AW42">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX42">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY42">
         <v>0</v>
       </c>
       <c r="AZ42">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BA42">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BB42">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC42">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD42">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE42">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF42">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="Q43">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="R43">
-        <v>3.92</v>
+        <v>7</v>
       </c>
       <c r="S43">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="T43">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U43">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="X43">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="Y43">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z43">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB43">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC43">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AD43">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AE43">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AH43">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI43">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AJ43">
         <v>1.01</v>
       </c>
       <c r="AK43">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="AL43">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="AM43">
+        <v>1.19</v>
+      </c>
+      <c r="AN43">
+        <v>2.5</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>1.5</v>
+      </c>
+      <c r="AQ43">
+        <v>1.89</v>
+      </c>
+      <c r="AR43">
+        <v>2.4</v>
+      </c>
+      <c r="AS43">
+        <v>3.15</v>
+      </c>
+      <c r="AT43">
+        <v>0</v>
+      </c>
+      <c r="AU43">
+        <v>2.33</v>
+      </c>
+      <c r="AV43">
+        <v>1.8</v>
+      </c>
+      <c r="AW43">
+        <v>1.49</v>
+      </c>
+      <c r="AX43">
         <v>1.3</v>
       </c>
-      <c r="AN43">
-        <v>1.68</v>
-      </c>
-      <c r="AO43">
-        <v>0</v>
-      </c>
-      <c r="AP43">
-        <v>1.27</v>
-      </c>
-      <c r="AQ43">
-        <v>1.47</v>
-      </c>
-      <c r="AR43">
-        <v>1.77</v>
-      </c>
-      <c r="AS43">
-        <v>2.2</v>
-      </c>
-      <c r="AT43">
-        <v>2.85</v>
-      </c>
-      <c r="AU43">
-        <v>3.3</v>
-      </c>
-      <c r="AV43">
-        <v>2.45</v>
-      </c>
-      <c r="AW43">
-        <v>1.92</v>
-      </c>
-      <c r="AX43">
-        <v>1.58</v>
-      </c>
       <c r="AY43">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ43">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="BA43">
-        <v>2.08</v>
+        <v>3.95</v>
       </c>
       <c r="BB43">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC43">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD43">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="BE43">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF43">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q44">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="R44">
-        <v>2.77</v>
+        <v>3.92</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE44">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11692,7 +11692,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E61" t="s">
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12432,7 +12432,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12441,7 +12441,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12468,7 +12468,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12626,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12811,7 +12811,7 @@
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D65" t="s">
         <v>109</v>
@@ -12996,7 +12996,7 @@
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13181,7 +13181,7 @@
         <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -13366,7 +13366,7 @@
         <v>175</v>
       </c>
       <c r="F67" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -13542,16 +13542,16 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E68" t="s">
         <v>176</v>
       </c>
       <c r="F68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -13736,7 +13736,7 @@
         <v>177</v>
       </c>
       <c r="F69" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -14184,7 +14184,7 @@
         <v>1.71</v>
       </c>
       <c r="AF71">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AG71">
         <v>2.7</v>
@@ -14199,7 +14199,7 @@
         <v>1.1</v>
       </c>
       <c r="AK71">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL71">
         <v>2.2</v>
@@ -14259,7 +14259,7 @@
         <v>4.1</v>
       </c>
       <c r="BE71">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BF71">
         <v>1.18</v>
@@ -14330,70 +14330,70 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI72">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM72">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN72">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14435,19 +14435,19 @@
         <v>0</v>
       </c>
       <c r="BB72">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC72">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD72">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE72">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG72">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -280,33 +280,33 @@
     <t>Bulgaria First League</t>
   </si>
   <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
+    <t>Georgia Erovnuli Liga</t>
+  </si>
+  <si>
     <t>Latvia Virsliga</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Georgia Erovnuli Liga</t>
-  </si>
-  <si>
     <t>Lithuania A Lyga</t>
   </si>
   <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
+    <t>Israel Israeli Premier League</t>
   </si>
   <si>
     <t>Sweden Damallsvenskan</t>
   </si>
   <si>
-    <t>Israel Israeli Premier League</t>
-  </si>
-  <si>
     <t>Spain Primera Division Women</t>
   </si>
   <si>
@@ -349,18 +349,18 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
+    <t>Sidama Bunna</t>
   </si>
   <si>
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Yunnan Yukun</t>
   </si>
   <si>
@@ -376,66 +376,66 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
-  </si>
-  <si>
-    <t>Líšeň</t>
+    <t>Paphos</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>AEK Larnaca</t>
-  </si>
-  <si>
-    <t>Aris</t>
+    <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
     <t>Žalgiris</t>
   </si>
   <si>
@@ -451,36 +451,36 @@
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>Hammarby</t>
+  </si>
+  <si>
     <t>Spartak Varna</t>
   </si>
   <si>
     <t>TransINVEST Vilnius</t>
   </si>
   <si>
-    <t>Hammarby</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>Richards Bay</t>
   </si>
   <si>
     <t>Marumo Gallants</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
-    <t>AmaZulu</t>
+    <t>Wydad Casablanca</t>
   </si>
   <si>
     <t>Al Ahli</t>
   </si>
   <si>
-    <t>Wydad Casablanca</t>
-  </si>
-  <si>
     <t>Brighton &amp; Hove Albion Women</t>
   </si>
   <si>
@@ -493,28 +493,49 @@
     <t>Cavalier</t>
   </si>
   <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
     <t>Treasure Beach</t>
   </si>
   <si>
-    <t>Portmore United</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
+    <t>Al Ramtha</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
   </si>
   <si>
     <t>Al Wihdat</t>
   </si>
   <si>
-    <t>Oued Akbou</t>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
   </si>
   <si>
     <t>Al Hussein</t>
@@ -523,33 +544,12 @@
     <t>MC Alger</t>
   </si>
   <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
     <t>Ben Aknoun</t>
   </si>
   <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
     <t>USM Khenchela</t>
   </si>
   <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
@@ -562,18 +562,18 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Ethiopian Medhin</t>
   </si>
   <si>
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Zhejiang FC</t>
   </si>
   <si>
@@ -589,66 +589,66 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Vysočina Jihlava</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
     <t>Super Nova</t>
   </si>
   <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Vysočina Jihlava</t>
-  </si>
-  <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Příbram</t>
+  </si>
+  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Příbram</t>
+    <t>Omonia Nicosia</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Raufoss</t>
   </si>
   <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>Apollon</t>
-  </si>
-  <si>
-    <t>APOEL</t>
+    <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
@@ -664,36 +664,36 @@
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Uppsala W</t>
+  </si>
+  <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
     <t>Sūduva</t>
   </si>
   <si>
-    <t>Uppsala W</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
     <t>Polokwane City</t>
   </si>
   <si>
     <t>TS Galaxy</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
-    <t>Golden Arrows</t>
+    <t>CODM Meknès</t>
   </si>
   <si>
     <t>Al Fateh</t>
   </si>
   <si>
-    <t>CODM Meknès</t>
-  </si>
-  <si>
     <t>Arsenal Women</t>
   </si>
   <si>
@@ -706,58 +706,58 @@
     <t>Harbour View</t>
   </si>
   <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
     <t>Molynes United</t>
   </si>
   <si>
-    <t>Tivoli Gardens</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
+    <t>Al Buqa'a</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
   </si>
   <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>JS Saoura</t>
+  </si>
+  <si>
     <t>Al Faisaly</t>
   </si>
   <si>
     <t>MB Rouisset</t>
   </si>
   <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
     <t>USM Alger</t>
   </si>
   <si>
-    <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
     <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
@@ -1380,124 +1380,124 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ2">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD2">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE2">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG2">
         <v>0</v>
@@ -1565,124 +1565,124 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AO3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1750,124 +1750,124 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="T4">
         <v>2.39</v>
       </c>
       <c r="U4">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="V4">
+        <v>1.23</v>
+      </c>
+      <c r="W4">
+        <v>3.52</v>
+      </c>
+      <c r="X4">
+        <v>2.21</v>
+      </c>
+      <c r="Y4">
+        <v>1.61</v>
+      </c>
+      <c r="Z4">
+        <v>4.8</v>
+      </c>
+      <c r="AA4">
+        <v>1.12</v>
+      </c>
+      <c r="AB4">
+        <v>1.01</v>
+      </c>
+      <c r="AC4">
+        <v>1.15</v>
+      </c>
+      <c r="AD4">
+        <v>4.8</v>
+      </c>
+      <c r="AE4">
+        <v>1.52</v>
+      </c>
+      <c r="AF4">
+        <v>2.35</v>
+      </c>
+      <c r="AG4">
+        <v>2.3</v>
+      </c>
+      <c r="AH4">
+        <v>1.61</v>
+      </c>
+      <c r="AI4">
+        <v>3.8</v>
+      </c>
+      <c r="AJ4">
+        <v>1.19</v>
+      </c>
+      <c r="AK4">
+        <v>1.52</v>
+      </c>
+      <c r="AL4">
+        <v>2.37</v>
+      </c>
+      <c r="AM4">
+        <v>1.23</v>
+      </c>
+      <c r="AN4">
+        <v>2.14</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.17</v>
+      </c>
+      <c r="AQ4">
+        <v>1.38</v>
+      </c>
+      <c r="AR4">
+        <v>1.68</v>
+      </c>
+      <c r="AS4">
+        <v>2.09</v>
+      </c>
+      <c r="AT4">
+        <v>2.6</v>
+      </c>
+      <c r="AU4">
+        <v>3.92</v>
+      </c>
+      <c r="AV4">
+        <v>2.7</v>
+      </c>
+      <c r="AW4">
+        <v>2.05</v>
+      </c>
+      <c r="AX4">
+        <v>1.67</v>
+      </c>
+      <c r="AY4">
+        <v>1.42</v>
+      </c>
+      <c r="AZ4">
+        <v>1.47</v>
+      </c>
+      <c r="BA4">
+        <v>2.85</v>
+      </c>
+      <c r="BB4">
+        <v>1.12</v>
+      </c>
+      <c r="BC4">
+        <v>1.73</v>
+      </c>
+      <c r="BD4">
+        <v>4.95</v>
+      </c>
+      <c r="BE4">
+        <v>1.99</v>
+      </c>
+      <c r="BF4">
         <v>1.27</v>
-      </c>
-      <c r="W4">
-        <v>3.35</v>
-      </c>
-      <c r="X4">
-        <v>2.47</v>
-      </c>
-      <c r="Y4">
-        <v>1.47</v>
-      </c>
-      <c r="Z4">
-        <v>5.9</v>
-      </c>
-      <c r="AA4">
-        <v>1.07</v>
-      </c>
-      <c r="AB4">
-        <v>1.03</v>
-      </c>
-      <c r="AC4">
-        <v>1.23</v>
-      </c>
-      <c r="AD4">
-        <v>3.98</v>
-      </c>
-      <c r="AE4">
-        <v>1.74</v>
-      </c>
-      <c r="AF4">
-        <v>2.12</v>
-      </c>
-      <c r="AG4">
-        <v>2.65</v>
-      </c>
-      <c r="AH4">
-        <v>1.36</v>
-      </c>
-      <c r="AI4">
-        <v>4.7</v>
-      </c>
-      <c r="AJ4">
-        <v>1.1</v>
-      </c>
-      <c r="AK4">
-        <v>1.71</v>
-      </c>
-      <c r="AL4">
-        <v>1.97</v>
-      </c>
-      <c r="AM4">
-        <v>1.21</v>
-      </c>
-      <c r="AN4">
-        <v>2.41</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4">
-        <v>1.42</v>
-      </c>
-      <c r="AR4">
-        <v>1.74</v>
-      </c>
-      <c r="AS4">
-        <v>2.17</v>
-      </c>
-      <c r="AT4">
-        <v>2.7</v>
-      </c>
-      <c r="AU4">
-        <v>3.68</v>
-      </c>
-      <c r="AV4">
-        <v>2.57</v>
-      </c>
-      <c r="AW4">
-        <v>1.97</v>
-      </c>
-      <c r="AX4">
-        <v>1.6</v>
-      </c>
-      <c r="AY4">
-        <v>1.38</v>
-      </c>
-      <c r="AZ4">
-        <v>1.32</v>
-      </c>
-      <c r="BA4">
-        <v>3.6</v>
-      </c>
-      <c r="BB4">
-        <v>1.16</v>
-      </c>
-      <c r="BC4">
-        <v>1.97</v>
-      </c>
-      <c r="BD4">
-        <v>4.3</v>
-      </c>
-      <c r="BE4">
-        <v>1.77</v>
-      </c>
-      <c r="BF4">
-        <v>1.17</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -2296,13 +2296,13 @@
         <v>251</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="R7">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>2.5</v>
@@ -2320,7 +2320,7 @@
         <v>3.52</v>
       </c>
       <c r="X7">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="Y7">
         <v>1.64</v>
@@ -2329,7 +2329,7 @@
         <v>4.7</v>
       </c>
       <c r="AA7">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB7">
         <v>1.01</v>
@@ -2368,7 +2368,7 @@
         <v>1.27</v>
       </c>
       <c r="AN7">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AO7">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         <v>4.19</v>
       </c>
       <c r="AV7">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AW7">
         <v>2.14</v>
@@ -2666,28 +2666,28 @@
         <v>251</v>
       </c>
       <c r="P9">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q9">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="R9">
-        <v>5.8</v>
+        <v>4.67</v>
       </c>
       <c r="S9">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="T9">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="U9">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="V9">
         <v>1.33</v>
       </c>
       <c r="W9">
-        <v>2.91</v>
+        <v>3.17</v>
       </c>
       <c r="X9">
         <v>2.59</v>
@@ -2711,7 +2711,7 @@
         <v>3.58</v>
       </c>
       <c r="AE9">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF9">
         <v>1.94</v>
@@ -2720,25 +2720,25 @@
         <v>2.83</v>
       </c>
       <c r="AH9">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI9">
         <v>5.3</v>
       </c>
       <c r="AJ9">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK9">
         <v>1.85</v>
       </c>
       <c r="AL9">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AM9">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AN9">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>120</v>
@@ -3221,34 +3221,34 @@
         <v>251</v>
       </c>
       <c r="P12">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U12">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3260,40 +3260,40 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AD12">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AE12">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AH12">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK12">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL12">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AM12">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AN12">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
         <v>121</v>
@@ -3415,13 +3415,13 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3430,10 +3430,10 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3445,40 +3445,40 @@
         <v>0</v>
       </c>
       <c r="AC13">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <v>0</v>
@@ -3523,13 +3523,13 @@
         <v>0</v>
       </c>
       <c r="BC13">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD13">
         <v>0</v>
       </c>
       <c r="BE13">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF13">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>109</v>
@@ -3600,13 +3600,13 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3615,10 +3615,10 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y14">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3630,40 +3630,40 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD14">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AE14">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AF14">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG14">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AH14">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI14">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK14">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AM14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN14">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3708,13 +3708,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3740,7 +3740,7 @@
         <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V15">
         <v>0</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3815,40 +3815,40 @@
         <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="BC15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD15">
         <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF15">
         <v>0</v>
@@ -3922,10 +3922,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -4107,7 +4107,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4155,13 +4155,13 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4170,10 +4170,10 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4185,40 +4185,40 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4263,13 +4263,13 @@
         <v>0</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD17">
         <v>0</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF17">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4477,10 +4477,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4516,28 +4516,28 @@
         <v>251</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -4555,22 +4555,22 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -4579,16 +4579,16 @@
         <v>0</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF19">
         <v>0</v>
@@ -4847,7 +4847,7 @@
         <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
         <v>109</v>
@@ -4895,13 +4895,13 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -4910,10 +4910,10 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4925,40 +4925,40 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5003,13 +5003,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5217,7 +5217,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5402,7 +5402,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5441,79 +5441,79 @@
         <v>251</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5555,19 +5555,19 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24">
         <v>0</v>
@@ -5587,10 +5587,10 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
         <v>133</v>
@@ -5626,133 +5626,133 @@
         <v>251</v>
       </c>
       <c r="P25">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="U25">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="V25">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Y25">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z25">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AD25">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="AE25">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AF25">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG25">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AH25">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AI25">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="AM25">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AN25">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="AO25">
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR25">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AU25">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV25">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AW25">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AX25">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY25">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ25">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA25">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC25">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BD25">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="BF25">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5811,79 +5811,79 @@
         <v>251</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5925,19 +5925,19 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,7 +5957,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5996,79 +5996,79 @@
         <v>251</v>
       </c>
       <c r="P27">
+        <v>1.92</v>
+      </c>
+      <c r="Q27">
+        <v>3.62</v>
+      </c>
+      <c r="R27">
+        <v>3.62</v>
+      </c>
+      <c r="S27">
+        <v>2.6</v>
+      </c>
+      <c r="T27">
+        <v>2.05</v>
+      </c>
+      <c r="U27">
+        <v>4.4</v>
+      </c>
+      <c r="V27">
+        <v>1.38</v>
+      </c>
+      <c r="W27">
         <v>2.77</v>
       </c>
-      <c r="Q27">
-        <v>3.29</v>
-      </c>
-      <c r="R27">
-        <v>2.43</v>
-      </c>
-      <c r="S27">
-        <v>2.7</v>
-      </c>
-      <c r="T27">
-        <v>2.17</v>
-      </c>
-      <c r="U27">
-        <v>3.69</v>
-      </c>
-      <c r="V27">
-        <v>1.31</v>
-      </c>
-      <c r="W27">
-        <v>3.1</v>
-      </c>
       <c r="X27">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="Y27">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="Z27">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AA27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC27">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD27">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AE27">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF27">
         <v>1.97</v>
       </c>
       <c r="AG27">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH27">
         <v>1.36</v>
       </c>
       <c r="AI27">
-        <v>5.05</v>
+        <v>5.22</v>
       </c>
       <c r="AJ27">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK27">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="AM27">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AN27">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -6110,16 +6110,16 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC27">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BD27">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BE27">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BF27">
         <v>1.2</v>
@@ -6142,7 +6142,7 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -6181,79 +6181,79 @@
         <v>251</v>
       </c>
       <c r="P28">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AD28">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AE28">
-        <v>2.28</v>
+        <v>1.81</v>
       </c>
       <c r="AF28">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AG28">
-        <v>4.01</v>
+        <v>3</v>
       </c>
       <c r="AH28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI28">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="AJ28">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AK28">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AL28">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AM28">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AN28">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -6295,19 +6295,19 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6330,7 +6330,7 @@
         <v>94</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6366,67 +6366,67 @@
         <v>251</v>
       </c>
       <c r="P29">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="Q29">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="R29">
-        <v>3.62</v>
+        <v>4.99</v>
       </c>
       <c r="S29">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="T29">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="U29">
-        <v>4.4</v>
+        <v>5.47</v>
       </c>
       <c r="V29">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="W29">
-        <v>2.77</v>
+        <v>3.44</v>
       </c>
       <c r="X29">
-        <v>2.54</v>
+        <v>2.21</v>
       </c>
       <c r="Y29">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="Z29">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA29">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AB29">
         <v>1.01</v>
       </c>
       <c r="AC29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD29">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="AE29">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="AF29">
-        <v>1.97</v>
+        <v>2.33</v>
       </c>
       <c r="AG29">
-        <v>2.7</v>
+        <v>2.31</v>
       </c>
       <c r="AH29">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AI29">
-        <v>5.22</v>
+        <v>3.74</v>
       </c>
       <c r="AJ29">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK29">
         <v>1.63</v>
@@ -6435,64 +6435,64 @@
         <v>2.14</v>
       </c>
       <c r="AM29">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AN29">
-        <v>1.72</v>
+        <v>2.49</v>
       </c>
       <c r="AO29">
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB29">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BC29">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="BD29">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="BE29">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="BF29">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6551,133 +6551,133 @@
         <v>251</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>1.58</v>
+        <v>3.44</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="U30">
-        <v>7.5</v>
+        <v>2.85</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="Y30">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC30">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AE30">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF30">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AG30">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AH30">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI30">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK30">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AM30">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AN30">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC30">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE30">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6700,7 +6700,7 @@
         <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6736,133 +6736,133 @@
         <v>251</v>
       </c>
       <c r="P31">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>1.58</v>
+      </c>
+      <c r="T31">
+        <v>2.88</v>
+      </c>
+      <c r="U31">
+        <v>7.5</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>1.98</v>
+      </c>
+      <c r="Y31">
+        <v>1.64</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>1.11</v>
+      </c>
+      <c r="AD31">
+        <v>5</v>
+      </c>
+      <c r="AE31">
+        <v>1.42</v>
+      </c>
+      <c r="AF31">
+        <v>2.55</v>
+      </c>
+      <c r="AG31">
+        <v>2.08</v>
+      </c>
+      <c r="AH31">
+        <v>1.62</v>
+      </c>
+      <c r="AI31">
+        <v>3.35</v>
+      </c>
+      <c r="AJ31">
+        <v>1.25</v>
+      </c>
+      <c r="AK31">
+        <v>1.84</v>
+      </c>
+      <c r="AL31">
+        <v>1.8</v>
+      </c>
+      <c r="AM31">
+        <v>1.08</v>
+      </c>
+      <c r="AN31">
         <v>3.3</v>
       </c>
-      <c r="R31">
-        <v>2.3</v>
-      </c>
-      <c r="S31">
-        <v>3.44</v>
-      </c>
-      <c r="T31">
-        <v>2.43</v>
-      </c>
-      <c r="U31">
-        <v>2.7</v>
-      </c>
-      <c r="V31">
-        <v>1.31</v>
-      </c>
-      <c r="W31">
-        <v>3.1</v>
-      </c>
-      <c r="X31">
-        <v>2.44</v>
-      </c>
-      <c r="Y31">
-        <v>1.48</v>
-      </c>
-      <c r="Z31">
-        <v>5.5</v>
-      </c>
-      <c r="AA31">
-        <v>1.07</v>
-      </c>
-      <c r="AB31">
-        <v>1.01</v>
-      </c>
-      <c r="AC31">
-        <v>1.15</v>
-      </c>
-      <c r="AD31">
-        <v>4.2</v>
-      </c>
-      <c r="AE31">
-        <v>1.72</v>
-      </c>
-      <c r="AF31">
-        <v>2.35</v>
-      </c>
-      <c r="AG31">
-        <v>2.23</v>
-      </c>
-      <c r="AH31">
-        <v>1.54</v>
-      </c>
-      <c r="AI31">
-        <v>4.65</v>
-      </c>
-      <c r="AJ31">
-        <v>1.12</v>
-      </c>
-      <c r="AK31">
-        <v>1.57</v>
-      </c>
-      <c r="AL31">
-        <v>2.37</v>
-      </c>
-      <c r="AM31">
-        <v>1.28</v>
-      </c>
-      <c r="AN31">
-        <v>1.4</v>
-      </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="BD31">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="BF31">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -7622,7 +7622,7 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
         <v>109</v>
@@ -7670,13 +7670,13 @@
         <v>1.75</v>
       </c>
       <c r="S36">
-        <v>3.96</v>
+        <v>4.17</v>
       </c>
       <c r="T36">
         <v>2.38</v>
       </c>
       <c r="U36">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V36">
         <v>1.23</v>
@@ -7691,7 +7691,7 @@
         <v>1.62</v>
       </c>
       <c r="Z36">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA36">
         <v>1.13</v>
@@ -7712,7 +7712,7 @@
         <v>2.41</v>
       </c>
       <c r="AG36">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AH36">
         <v>1.61</v>
@@ -7730,49 +7730,49 @@
         <v>2.48</v>
       </c>
       <c r="AM36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN36">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AQ36">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR36">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AS36">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AT36">
-        <v>3.08</v>
+        <v>3.33</v>
       </c>
       <c r="AU36">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="AV36">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AW36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AX36">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AY36">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AZ36">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BA36">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="BB36">
         <v>1.11</v>
@@ -7807,10 +7807,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7846,133 +7846,133 @@
         <v>251</v>
       </c>
       <c r="P37">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO37">
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT37">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV37">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW37">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ37">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC37">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD37">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF37">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7992,10 +7992,10 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
@@ -8031,76 +8031,76 @@
         <v>251</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R38">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AD38">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="AE38">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AF38">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>3.86</v>
       </c>
       <c r="AH38">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AI38">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AJ38">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK38">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AM38">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AN38">
         <v>1.32</v>
@@ -8109,55 +8109,55 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV38">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ38">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC38">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD38">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE38">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF38">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8177,7 +8177,7 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -8216,13 +8216,13 @@
         <v>251</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -8255,40 +8255,40 @@
         <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI39">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM39">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO39">
         <v>0</v>
@@ -8362,7 +8362,7 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
         <v>108</v>
@@ -8586,133 +8586,133 @@
         <v>251</v>
       </c>
       <c r="P41">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="Q41">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>3.17</v>
+        <v>3.7</v>
       </c>
       <c r="S41">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="T41">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="U41">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="V41">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="X41">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y41">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA41">
+        <v>1</v>
+      </c>
+      <c r="AB41">
+        <v>1.04</v>
+      </c>
+      <c r="AC41">
+        <v>1.42</v>
+      </c>
+      <c r="AD41">
+        <v>2.66</v>
+      </c>
+      <c r="AE41">
+        <v>2.27</v>
+      </c>
+      <c r="AF41">
+        <v>1.56</v>
+      </c>
+      <c r="AG41">
+        <v>4.15</v>
+      </c>
+      <c r="AH41">
+        <v>1.16</v>
+      </c>
+      <c r="AI41">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AJ41">
         <v>1.01</v>
       </c>
-      <c r="AB41">
-        <v>1.08</v>
-      </c>
-      <c r="AC41">
-        <v>1.66</v>
-      </c>
-      <c r="AD41">
-        <v>2.09</v>
-      </c>
-      <c r="AE41">
-        <v>3.04</v>
-      </c>
-      <c r="AF41">
-        <v>1.29</v>
-      </c>
-      <c r="AG41">
-        <v>5.25</v>
-      </c>
-      <c r="AH41">
-        <v>1.12</v>
-      </c>
-      <c r="AI41">
-        <v>11</v>
-      </c>
-      <c r="AJ41">
-        <v>1.02</v>
-      </c>
       <c r="AK41">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL41">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AM41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AN41">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
+        <v>1.47</v>
+      </c>
+      <c r="AR41">
+        <v>1.77</v>
+      </c>
+      <c r="AS41">
+        <v>2.2</v>
+      </c>
+      <c r="AT41">
+        <v>2.85</v>
+      </c>
+      <c r="AU41">
+        <v>3.3</v>
+      </c>
+      <c r="AV41">
+        <v>2.45</v>
+      </c>
+      <c r="AW41">
+        <v>1.92</v>
+      </c>
+      <c r="AX41">
         <v>1.58</v>
       </c>
-      <c r="AR41">
-        <v>1.94</v>
-      </c>
-      <c r="AS41">
-        <v>2.48</v>
-      </c>
-      <c r="AT41">
-        <v>3.25</v>
-      </c>
-      <c r="AU41">
-        <v>2.95</v>
-      </c>
-      <c r="AV41">
-        <v>2.2</v>
-      </c>
-      <c r="AW41">
-        <v>1.75</v>
-      </c>
-      <c r="AX41">
+      <c r="AY41">
+        <v>1.36</v>
+      </c>
+      <c r="AZ41">
+        <v>1.79</v>
+      </c>
+      <c r="BA41">
+        <v>2.16</v>
+      </c>
+      <c r="BB41">
+        <v>1.28</v>
+      </c>
+      <c r="BC41">
+        <v>2.41</v>
+      </c>
+      <c r="BD41">
+        <v>3.18</v>
+      </c>
+      <c r="BE41">
         <v>1.47</v>
       </c>
-      <c r="AY41">
-        <v>1.29</v>
-      </c>
-      <c r="AZ41">
-        <v>1.8</v>
-      </c>
-      <c r="BA41">
-        <v>2.18</v>
-      </c>
-      <c r="BB41">
-        <v>1.43</v>
-      </c>
-      <c r="BC41">
-        <v>3.18</v>
-      </c>
-      <c r="BD41">
-        <v>2.53</v>
-      </c>
-      <c r="BE41">
-        <v>1.28</v>
-      </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8771,133 +8771,133 @@
         <v>251</v>
       </c>
       <c r="P42">
+        <v>1.44</v>
+      </c>
+      <c r="Q42">
+        <v>3.75</v>
+      </c>
+      <c r="R42">
+        <v>7.5</v>
+      </c>
+      <c r="S42">
+        <v>2.04</v>
+      </c>
+      <c r="T42">
+        <v>2.06</v>
+      </c>
+      <c r="U42">
+        <v>7.7</v>
+      </c>
+      <c r="V42">
+        <v>1.45</v>
+      </c>
+      <c r="W42">
+        <v>2.47</v>
+      </c>
+      <c r="X42">
+        <v>3.18</v>
+      </c>
+      <c r="Y42">
+        <v>1.28</v>
+      </c>
+      <c r="Z42">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA42">
+        <v>1.01</v>
+      </c>
+      <c r="AB42">
+        <v>1.03</v>
+      </c>
+      <c r="AC42">
+        <v>1.37</v>
+      </c>
+      <c r="AD42">
+        <v>2.66</v>
+      </c>
+      <c r="AE42">
+        <v>2.1</v>
+      </c>
+      <c r="AF42">
+        <v>1.57</v>
+      </c>
+      <c r="AG42">
+        <v>4.1</v>
+      </c>
+      <c r="AH42">
+        <v>1.16</v>
+      </c>
+      <c r="AI42">
+        <v>8.5</v>
+      </c>
+      <c r="AJ42">
+        <v>1.01</v>
+      </c>
+      <c r="AK42">
+        <v>2.42</v>
+      </c>
+      <c r="AL42">
+        <v>1.49</v>
+      </c>
+      <c r="AM42">
+        <v>1.18</v>
+      </c>
+      <c r="AN42">
+        <v>2.5</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>1.5</v>
+      </c>
+      <c r="AQ42">
+        <v>1.89</v>
+      </c>
+      <c r="AR42">
+        <v>2.4</v>
+      </c>
+      <c r="AS42">
+        <v>3.15</v>
+      </c>
+      <c r="AT42">
+        <v>0</v>
+      </c>
+      <c r="AU42">
+        <v>2.33</v>
+      </c>
+      <c r="AV42">
+        <v>1.8</v>
+      </c>
+      <c r="AW42">
+        <v>1.49</v>
+      </c>
+      <c r="AX42">
+        <v>1.3</v>
+      </c>
+      <c r="AY42">
+        <v>0</v>
+      </c>
+      <c r="AZ42">
+        <v>1.28</v>
+      </c>
+      <c r="BA42">
+        <v>3.95</v>
+      </c>
+      <c r="BB42">
+        <v>1.28</v>
+      </c>
+      <c r="BC42">
         <v>2.41</v>
       </c>
-      <c r="Q42">
-        <v>2.9</v>
-      </c>
-      <c r="R42">
-        <v>2.77</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
-      <c r="AB42">
-        <v>0</v>
-      </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
-      <c r="AD42">
-        <v>0</v>
-      </c>
-      <c r="AE42">
-        <v>2.62</v>
-      </c>
-      <c r="AF42">
-        <v>1.44</v>
-      </c>
-      <c r="AG42">
-        <v>0</v>
-      </c>
-      <c r="AH42">
-        <v>0</v>
-      </c>
-      <c r="AI42">
-        <v>0</v>
-      </c>
-      <c r="AJ42">
-        <v>0</v>
-      </c>
-      <c r="AK42">
-        <v>0</v>
-      </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
-      <c r="AM42">
-        <v>0</v>
-      </c>
-      <c r="AN42">
-        <v>0</v>
-      </c>
-      <c r="AO42">
-        <v>0</v>
-      </c>
-      <c r="AP42">
-        <v>0</v>
-      </c>
-      <c r="AQ42">
-        <v>0</v>
-      </c>
-      <c r="AR42">
-        <v>0</v>
-      </c>
-      <c r="AS42">
-        <v>0</v>
-      </c>
-      <c r="AT42">
-        <v>0</v>
-      </c>
-      <c r="AU42">
-        <v>0</v>
-      </c>
-      <c r="AV42">
-        <v>0</v>
-      </c>
-      <c r="AW42">
-        <v>0</v>
-      </c>
-      <c r="AX42">
-        <v>0</v>
-      </c>
-      <c r="AY42">
-        <v>0</v>
-      </c>
-      <c r="AZ42">
-        <v>0</v>
-      </c>
-      <c r="BA42">
-        <v>0</v>
-      </c>
-      <c r="BB42">
-        <v>0</v>
-      </c>
-      <c r="BC42">
-        <v>0</v>
-      </c>
       <c r="BD42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8956,133 +8956,133 @@
         <v>251</v>
       </c>
       <c r="P43">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q43">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R43">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="S43">
-        <v>2.01</v>
+        <v>3.16</v>
       </c>
       <c r="T43">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="U43">
-        <v>7.8</v>
+        <v>4.39</v>
       </c>
       <c r="V43">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="X43">
-        <v>3.18</v>
+        <v>4.2</v>
       </c>
       <c r="Y43">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
-        <v>8.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA43">
         <v>1.01</v>
       </c>
       <c r="AB43">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AC43">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AD43">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="AE43">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="AF43">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AG43">
-        <v>3.75</v>
+        <v>6.75</v>
       </c>
       <c r="AH43">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AI43">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AJ43">
+        <v>1.02</v>
+      </c>
+      <c r="AK43">
+        <v>2.4</v>
+      </c>
+      <c r="AL43">
+        <v>1.5</v>
+      </c>
+      <c r="AM43">
+        <v>1.33</v>
+      </c>
+      <c r="AN43">
+        <v>1.5</v>
+      </c>
+      <c r="AO43">
+        <v>0</v>
+      </c>
+      <c r="AP43">
+        <v>1.34</v>
+      </c>
+      <c r="AQ43">
+        <v>1.58</v>
+      </c>
+      <c r="AR43">
+        <v>1.94</v>
+      </c>
+      <c r="AS43">
+        <v>2.48</v>
+      </c>
+      <c r="AT43">
+        <v>3.25</v>
+      </c>
+      <c r="AU43">
+        <v>2.95</v>
+      </c>
+      <c r="AV43">
+        <v>2.2</v>
+      </c>
+      <c r="AW43">
+        <v>1.75</v>
+      </c>
+      <c r="AX43">
+        <v>1.47</v>
+      </c>
+      <c r="AY43">
+        <v>1.29</v>
+      </c>
+      <c r="AZ43">
+        <v>1.8</v>
+      </c>
+      <c r="BA43">
+        <v>2.18</v>
+      </c>
+      <c r="BB43">
+        <v>1.43</v>
+      </c>
+      <c r="BC43">
+        <v>3.18</v>
+      </c>
+      <c r="BD43">
+        <v>2.53</v>
+      </c>
+      <c r="BE43">
+        <v>1.28</v>
+      </c>
+      <c r="BF43">
         <v>1.01</v>
-      </c>
-      <c r="AK43">
-        <v>2.45</v>
-      </c>
-      <c r="AL43">
-        <v>1.48</v>
-      </c>
-      <c r="AM43">
-        <v>1.19</v>
-      </c>
-      <c r="AN43">
-        <v>2.5</v>
-      </c>
-      <c r="AO43">
-        <v>0</v>
-      </c>
-      <c r="AP43">
-        <v>1.5</v>
-      </c>
-      <c r="AQ43">
-        <v>1.89</v>
-      </c>
-      <c r="AR43">
-        <v>2.4</v>
-      </c>
-      <c r="AS43">
-        <v>3.15</v>
-      </c>
-      <c r="AT43">
-        <v>0</v>
-      </c>
-      <c r="AU43">
-        <v>2.33</v>
-      </c>
-      <c r="AV43">
-        <v>1.8</v>
-      </c>
-      <c r="AW43">
-        <v>1.49</v>
-      </c>
-      <c r="AX43">
-        <v>1.3</v>
-      </c>
-      <c r="AY43">
-        <v>0</v>
-      </c>
-      <c r="AZ43">
-        <v>1.28</v>
-      </c>
-      <c r="BA43">
-        <v>3.95</v>
-      </c>
-      <c r="BB43">
-        <v>1.29</v>
-      </c>
-      <c r="BC43">
-        <v>2.44</v>
-      </c>
-      <c r="BD43">
-        <v>3.12</v>
-      </c>
-      <c r="BE43">
-        <v>1.46</v>
-      </c>
-      <c r="BF43">
-        <v>1.08</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9141,133 +9141,133 @@
         <v>251</v>
       </c>
       <c r="P44">
-        <v>1.95</v>
+        <v>2.53</v>
       </c>
       <c r="Q44">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="R44">
-        <v>3.92</v>
+        <v>2.75</v>
       </c>
       <c r="S44">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AF44">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH44">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI44">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AL44">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN44">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AR44">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS44">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT44">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU44">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV44">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AW44">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX44">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY44">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA44">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BB44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC44">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD44">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE44">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF44">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9326,13 +9326,13 @@
         <v>251</v>
       </c>
       <c r="P45">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -9472,7 +9472,7 @@
         <v>74</v>
       </c>
       <c r="C46" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
         <v>109</v>
@@ -9511,79 +9511,79 @@
         <v>251</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN46">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AO46">
         <v>0</v>
@@ -9625,19 +9625,19 @@
         <v>0</v>
       </c>
       <c r="BB46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC46">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD46">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="BE46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF46">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG46">
         <v>0</v>
@@ -9699,52 +9699,52 @@
         <v>6.5</v>
       </c>
       <c r="Q47">
-        <v>5.2</v>
+        <v>4.65</v>
       </c>
       <c r="R47">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S47">
-        <v>6.5</v>
+        <v>6.96</v>
       </c>
       <c r="T47">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="V47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W47">
         <v>4</v>
       </c>
       <c r="X47">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Y47">
         <v>1.64</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA47">
         <v>1.17</v>
       </c>
       <c r="AB47">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC47">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD47">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AE47">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AF47">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AG47">
         <v>2.15</v>
@@ -9756,7 +9756,7 @@
         <v>3.42</v>
       </c>
       <c r="AJ47">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
         <v>1.58</v>
@@ -9765,7 +9765,7 @@
         <v>2.18</v>
       </c>
       <c r="AM47">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AN47">
         <v>1.02</v>
@@ -9807,7 +9807,7 @@
         <v>7.6</v>
       </c>
       <c r="BA47">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BB47">
         <v>1.15</v>
@@ -11516,7 +11516,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11701,7 +11701,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11877,7 +11877,7 @@
         <v>79</v>
       </c>
       <c r="C59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D59" t="s">
         <v>109</v>
@@ -11886,7 +11886,7 @@
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12062,16 +12062,16 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E60" t="s">
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12247,7 +12247,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12256,7 +12256,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>239</v>
+        <v>154</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12468,7 +12468,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -12617,7 +12617,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -13172,7 +13172,7 @@
         <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D66" t="s">
         <v>109</v>
@@ -13542,10 +13542,10 @@
         <v>79</v>
       </c>
       <c r="C68" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E68" t="s">
         <v>176</v>
@@ -13578,7 +13578,7 @@
         <v>-1</v>
       </c>
       <c r="O68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P68">
         <v>0</v>
@@ -14199,10 +14199,10 @@
         <v>1.1</v>
       </c>
       <c r="AK71">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL71">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AM71">
         <v>1.23</v>
@@ -14321,79 +14321,79 @@
         <v>251</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S72">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T72">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U72">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="V72">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W72">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X72">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y72">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z72">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC72">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD72">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE72">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AF72">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG72">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH72">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI72">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ72">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK72">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL72">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM72">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN72">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO72">
         <v>0</v>
@@ -14435,19 +14435,19 @@
         <v>0</v>
       </c>
       <c r="BB72">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC72">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD72">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE72">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF72">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG72">
         <v>0</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="239">
   <si>
     <t>Date</t>
   </si>
@@ -268,12 +268,12 @@
     <t>Ethiopia Ethiopia Premier League</t>
   </si>
   <si>
+    <t>India Indian Super League</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>India Indian Super League</t>
-  </si>
-  <si>
     <t>UAE Arabian Gulf League</t>
   </si>
   <si>
@@ -292,12 +292,12 @@
     <t>Lithuania A Lyga</t>
   </si>
   <si>
+    <t>Cyprus First Division</t>
+  </si>
+  <si>
     <t>Morocco Botola Pro</t>
   </si>
   <si>
-    <t>Cyprus First Division</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -328,12 +328,12 @@
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -349,126 +349,126 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Fasil Ketema</t>
   </si>
   <si>
     <t>Sidama Bunna</t>
   </si>
   <si>
-    <t>Fasil Ketema</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
+    <t>Minerva Punjab</t>
   </si>
   <si>
     <t>Kaisar</t>
   </si>
   <si>
-    <t>Minerva Punjab</t>
-  </si>
-  <si>
     <t>Al Wahda</t>
   </si>
   <si>
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Sparta Praha II</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
     <t>České Budějovice</t>
   </si>
   <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Welwalo Adigrat Uni</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Sparta Praha II</t>
-  </si>
-  <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
-    <t>Welwalo Adigrat Uni</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
     <t>FS Jelgava</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Líšeň</t>
+  </si>
+  <si>
+    <t>AEK Larnaca</t>
+  </si>
+  <si>
     <t>Ústí nad Labem</t>
   </si>
   <si>
-    <t>Líšeň</t>
-  </si>
-  <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>AEK Larnaca</t>
+    <t>Aris</t>
+  </si>
+  <si>
+    <t>Vlašim</t>
+  </si>
+  <si>
+    <t>Paphos</t>
   </si>
   <si>
     <t>Táborsko</t>
   </si>
   <si>
-    <t>Paphos</t>
-  </si>
-  <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
-  </si>
-  <si>
     <t>Egersund</t>
   </si>
   <si>
+    <t>Žalgiris</t>
+  </si>
+  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
     <t>Häcken W</t>
   </si>
   <si>
-    <t>Žalgiris</t>
+    <t>Al Sharjah</t>
   </si>
   <si>
     <t>Barcelona W</t>
   </si>
   <si>
-    <t>Al Sharjah</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
+    <t>TransINVEST Vilnius</t>
+  </si>
+  <si>
     <t>Hammarby</t>
   </si>
   <si>
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>TransINVEST Vilnius</t>
-  </si>
-  <si>
     <t>Gagra</t>
   </si>
   <si>
+    <t>Mamelodi Sundowns</t>
+  </si>
+  <si>
     <t>AmaZulu</t>
   </si>
   <si>
-    <t>Mamelodi Sundowns</t>
-  </si>
-  <si>
     <t>Richards Bay</t>
   </si>
   <si>
@@ -490,69 +490,48 @@
     <t>Maghreb Fès</t>
   </si>
   <si>
+    <t>Treasure Beach</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
     <t>Mount Pleasant Academy FC</t>
   </si>
   <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
     <t>Spanish Town Police FC</t>
   </si>
   <si>
-    <t>Chapelton</t>
+    <t>Waterhouse</t>
   </si>
   <si>
     <t>Portmore United</t>
   </si>
   <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Treasure Beach</t>
+    <t>Shabab Al Ordon</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Sporting KC II</t>
+  </si>
+  <si>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Hussein</t>
   </si>
   <si>
     <t>Al Ramtha</t>
   </si>
   <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
-    <t>Sporting KC II</t>
-  </si>
-  <si>
-    <t>Al Wihdat</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>USM Khenchela</t>
-  </si>
-  <si>
-    <t>Shabab Al Ordon</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -562,126 +541,126 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Dalian Zhixing</t>
+  </si>
+  <si>
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
-    <t>Dalian Zhixing</t>
+    <t>Zhejiang FC</t>
+  </si>
+  <si>
+    <t>Bahardar</t>
   </si>
   <si>
     <t>Ethiopian Medhin</t>
   </si>
   <si>
-    <t>Bahardar</t>
-  </si>
-  <si>
-    <t>Zhejiang FC</t>
+    <t>Chennaiyin</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Chennaiyin</t>
-  </si>
-  <si>
     <t>Al Wasl</t>
   </si>
   <si>
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Prostějov</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Negele Arsi Ketema</t>
+  </si>
+  <si>
     <t>Saburtalo</t>
   </si>
   <si>
-    <t>Prostějov</t>
-  </si>
-  <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
-    <t>Negele Arsi Ketema</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
     <t>Super Nova</t>
   </si>
   <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Příbram</t>
+  </si>
+  <si>
+    <t>Apollon</t>
+  </si>
+  <si>
     <t>Opava</t>
   </si>
   <si>
-    <t>Příbram</t>
-  </si>
-  <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>Apollon</t>
+    <t>APOEL</t>
+  </si>
+  <si>
+    <t>Viktoria Žižkov</t>
+  </si>
+  <si>
+    <t>Omonia Nicosia</t>
   </si>
   <si>
     <t>Chrudim</t>
   </si>
   <si>
-    <t>Omonia Nicosia</t>
-  </si>
-  <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
-  </si>
-  <si>
     <t>Raufoss</t>
   </si>
   <si>
+    <t>FA Šiauliai</t>
+  </si>
+  <si>
     <t>Beitar Jerusalem</t>
   </si>
   <si>
     <t>Djurgården W</t>
   </si>
   <si>
-    <t>FA Šiauliai</t>
+    <t>Al Ain</t>
   </si>
   <si>
     <t>Levante W</t>
   </si>
   <si>
-    <t>Al Ain</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
+    <t>Sūduva</t>
+  </si>
+  <si>
     <t>Uppsala W</t>
   </si>
   <si>
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Sūduva</t>
-  </si>
-  <si>
     <t>Dinamo Batumi</t>
   </si>
   <si>
+    <t>Kaizer Chiefs</t>
+  </si>
+  <si>
     <t>Golden Arrows</t>
   </si>
   <si>
-    <t>Kaizer Chiefs</t>
-  </si>
-  <si>
     <t>Polokwane City</t>
   </si>
   <si>
@@ -703,64 +682,43 @@
     <t>Raja Casablanca</t>
   </si>
   <si>
+    <t>Molynes United</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
     <t>Montego Bay United</t>
   </si>
   <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
     <t>Racing United</t>
   </si>
   <si>
-    <t>Arnett Gardens</t>
+    <t>Dunbeholden</t>
   </si>
   <si>
     <t>Tivoli Gardens</t>
   </si>
   <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Molynes United</t>
+    <t>Sama Al Sarhan</t>
+  </si>
+  <si>
+    <t>LA Galaxy II</t>
+  </si>
+  <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Al Faisaly</t>
   </si>
   <si>
     <t>Al Buqa'a</t>
-  </si>
-  <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>JS Saoura</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>MB Rouisset</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
-    <t>Sama Al Sarhan</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1136,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI72"/>
+  <dimension ref="A1:BI65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -1341,7 +1299,7 @@
         <v>110</v>
       </c>
       <c r="F2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1368,7 +1326,7 @@
         <v>-1</v>
       </c>
       <c r="O2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1526,7 +1484,7 @@
         <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1553,7 +1511,7 @@
         <v>-1</v>
       </c>
       <c r="O3" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1565,124 +1523,124 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="T3">
         <v>2.39</v>
       </c>
       <c r="U3">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="V3">
+        <v>1.23</v>
+      </c>
+      <c r="W3">
+        <v>3.52</v>
+      </c>
+      <c r="X3">
+        <v>2.21</v>
+      </c>
+      <c r="Y3">
+        <v>1.61</v>
+      </c>
+      <c r="Z3">
+        <v>4.8</v>
+      </c>
+      <c r="AA3">
+        <v>1.12</v>
+      </c>
+      <c r="AB3">
+        <v>1.01</v>
+      </c>
+      <c r="AC3">
+        <v>1.15</v>
+      </c>
+      <c r="AD3">
+        <v>4.8</v>
+      </c>
+      <c r="AE3">
+        <v>1.52</v>
+      </c>
+      <c r="AF3">
+        <v>2.35</v>
+      </c>
+      <c r="AG3">
+        <v>2.3</v>
+      </c>
+      <c r="AH3">
+        <v>1.61</v>
+      </c>
+      <c r="AI3">
+        <v>3.8</v>
+      </c>
+      <c r="AJ3">
+        <v>1.19</v>
+      </c>
+      <c r="AK3">
+        <v>1.52</v>
+      </c>
+      <c r="AL3">
+        <v>2.37</v>
+      </c>
+      <c r="AM3">
+        <v>1.23</v>
+      </c>
+      <c r="AN3">
+        <v>2.14</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>1.17</v>
+      </c>
+      <c r="AQ3">
+        <v>1.38</v>
+      </c>
+      <c r="AR3">
+        <v>1.68</v>
+      </c>
+      <c r="AS3">
+        <v>2.09</v>
+      </c>
+      <c r="AT3">
+        <v>2.6</v>
+      </c>
+      <c r="AU3">
+        <v>3.92</v>
+      </c>
+      <c r="AV3">
+        <v>2.7</v>
+      </c>
+      <c r="AW3">
+        <v>2.05</v>
+      </c>
+      <c r="AX3">
+        <v>1.67</v>
+      </c>
+      <c r="AY3">
+        <v>1.42</v>
+      </c>
+      <c r="AZ3">
+        <v>1.47</v>
+      </c>
+      <c r="BA3">
+        <v>2.85</v>
+      </c>
+      <c r="BB3">
+        <v>1.12</v>
+      </c>
+      <c r="BC3">
+        <v>1.73</v>
+      </c>
+      <c r="BD3">
+        <v>4.95</v>
+      </c>
+      <c r="BE3">
+        <v>1.99</v>
+      </c>
+      <c r="BF3">
         <v>1.27</v>
-      </c>
-      <c r="W3">
-        <v>3.35</v>
-      </c>
-      <c r="X3">
-        <v>2.47</v>
-      </c>
-      <c r="Y3">
-        <v>1.47</v>
-      </c>
-      <c r="Z3">
-        <v>5.9</v>
-      </c>
-      <c r="AA3">
-        <v>1.07</v>
-      </c>
-      <c r="AB3">
-        <v>1.03</v>
-      </c>
-      <c r="AC3">
-        <v>1.2</v>
-      </c>
-      <c r="AD3">
-        <v>3.98</v>
-      </c>
-      <c r="AE3">
-        <v>1.74</v>
-      </c>
-      <c r="AF3">
-        <v>2.12</v>
-      </c>
-      <c r="AG3">
-        <v>2.7</v>
-      </c>
-      <c r="AH3">
-        <v>1.43</v>
-      </c>
-      <c r="AI3">
-        <v>4.7</v>
-      </c>
-      <c r="AJ3">
-        <v>1.16</v>
-      </c>
-      <c r="AK3">
-        <v>1.75</v>
-      </c>
-      <c r="AL3">
-        <v>1.97</v>
-      </c>
-      <c r="AM3">
-        <v>1.21</v>
-      </c>
-      <c r="AN3">
-        <v>2.41</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>1.19</v>
-      </c>
-      <c r="AQ3">
-        <v>1.44</v>
-      </c>
-      <c r="AR3">
-        <v>1.72</v>
-      </c>
-      <c r="AS3">
-        <v>2.14</v>
-      </c>
-      <c r="AT3">
-        <v>2.86</v>
-      </c>
-      <c r="AU3">
-        <v>3.68</v>
-      </c>
-      <c r="AV3">
-        <v>2.55</v>
-      </c>
-      <c r="AW3">
-        <v>1.97</v>
-      </c>
-      <c r="AX3">
-        <v>1.62</v>
-      </c>
-      <c r="AY3">
-        <v>1.38</v>
-      </c>
-      <c r="AZ3">
-        <v>1.32</v>
-      </c>
-      <c r="BA3">
-        <v>3.6</v>
-      </c>
-      <c r="BB3">
-        <v>1.16</v>
-      </c>
-      <c r="BC3">
-        <v>1.97</v>
-      </c>
-      <c r="BD3">
-        <v>4.3</v>
-      </c>
-      <c r="BE3">
-        <v>1.77</v>
-      </c>
-      <c r="BF3">
-        <v>1.17</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1711,7 +1669,7 @@
         <v>112</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1738,7 +1696,7 @@
         <v>-1</v>
       </c>
       <c r="O4" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1750,124 +1708,124 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="T4">
         <v>2.39</v>
       </c>
       <c r="U4">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="X4">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y4">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Z4">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA4">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC4">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AD4">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="AE4">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AF4">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AG4">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH4">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AI4">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AJ4">
+        <v>1.16</v>
+      </c>
+      <c r="AK4">
+        <v>1.75</v>
+      </c>
+      <c r="AL4">
+        <v>1.97</v>
+      </c>
+      <c r="AM4">
+        <v>1.21</v>
+      </c>
+      <c r="AN4">
+        <v>2.41</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
         <v>1.19</v>
       </c>
-      <c r="AK4">
-        <v>1.52</v>
-      </c>
-      <c r="AL4">
-        <v>2.37</v>
-      </c>
-      <c r="AM4">
-        <v>1.23</v>
-      </c>
-      <c r="AN4">
+      <c r="AQ4">
+        <v>1.44</v>
+      </c>
+      <c r="AR4">
+        <v>1.72</v>
+      </c>
+      <c r="AS4">
         <v>2.14</v>
       </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
+      <c r="AT4">
+        <v>2.86</v>
+      </c>
+      <c r="AU4">
+        <v>3.68</v>
+      </c>
+      <c r="AV4">
+        <v>2.55</v>
+      </c>
+      <c r="AW4">
+        <v>1.97</v>
+      </c>
+      <c r="AX4">
+        <v>1.62</v>
+      </c>
+      <c r="AY4">
+        <v>1.38</v>
+      </c>
+      <c r="AZ4">
+        <v>1.32</v>
+      </c>
+      <c r="BA4">
+        <v>3.6</v>
+      </c>
+      <c r="BB4">
+        <v>1.16</v>
+      </c>
+      <c r="BC4">
+        <v>1.97</v>
+      </c>
+      <c r="BD4">
+        <v>4.3</v>
+      </c>
+      <c r="BE4">
+        <v>1.77</v>
+      </c>
+      <c r="BF4">
         <v>1.17</v>
-      </c>
-      <c r="AQ4">
-        <v>1.38</v>
-      </c>
-      <c r="AR4">
-        <v>1.68</v>
-      </c>
-      <c r="AS4">
-        <v>2.09</v>
-      </c>
-      <c r="AT4">
-        <v>2.6</v>
-      </c>
-      <c r="AU4">
-        <v>3.92</v>
-      </c>
-      <c r="AV4">
-        <v>2.7</v>
-      </c>
-      <c r="AW4">
-        <v>2.05</v>
-      </c>
-      <c r="AX4">
-        <v>1.67</v>
-      </c>
-      <c r="AY4">
-        <v>1.42</v>
-      </c>
-      <c r="AZ4">
-        <v>1.47</v>
-      </c>
-      <c r="BA4">
-        <v>2.85</v>
-      </c>
-      <c r="BB4">
-        <v>1.12</v>
-      </c>
-      <c r="BC4">
-        <v>1.73</v>
-      </c>
-      <c r="BD4">
-        <v>4.95</v>
-      </c>
-      <c r="BE4">
-        <v>1.99</v>
-      </c>
-      <c r="BF4">
-        <v>1.27</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1887,16 +1845,16 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
       </c>
       <c r="F5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1923,136 +1881,136 @@
         <v>-1</v>
       </c>
       <c r="O5" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2081,7 +2039,7 @@
         <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2108,7 +2066,7 @@
         <v>-1</v>
       </c>
       <c r="O6" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -2257,16 +2215,16 @@
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2293,136 +2251,136 @@
         <v>-1</v>
       </c>
       <c r="O7" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AO7">
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ7">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR7">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT7">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU7">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV7">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW7">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX7">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY7">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ7">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA7">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC7">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD7">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE7">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF7">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG7">
         <v>0</v>
@@ -2445,13 +2403,13 @@
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2478,82 +2436,82 @@
         <v>-1</v>
       </c>
       <c r="O8" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AO8">
         <v>0</v>
@@ -2595,19 +2553,19 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG8">
         <v>0</v>
@@ -2630,13 +2588,13 @@
         <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2663,82 +2621,82 @@
         <v>-1</v>
       </c>
       <c r="O9" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -2780,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -2821,7 +2779,7 @@
         <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2848,7 +2806,7 @@
         <v>-1</v>
       </c>
       <c r="O10" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -3006,7 +2964,7 @@
         <v>119</v>
       </c>
       <c r="F11" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -3033,25 +2991,25 @@
         <v>-1</v>
       </c>
       <c r="O11" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P11">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S11">
         <v>2.99</v>
       </c>
       <c r="T11">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U11">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="V11">
         <v>1.41</v>
@@ -3075,28 +3033,28 @@
         <v>1.02</v>
       </c>
       <c r="AC11">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AD11">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="AE11">
         <v>1.9</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG11">
         <v>3.2</v>
       </c>
       <c r="AH11">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI11">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK11">
         <v>1.79</v>
@@ -3144,13 +3102,13 @@
         <v>1.3</v>
       </c>
       <c r="AZ11">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="BA11">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="BB11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC11">
         <v>2.27</v>
@@ -3191,7 +3149,7 @@
         <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -3218,7 +3176,7 @@
         <v>-1</v>
       </c>
       <c r="O12" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -3230,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="T12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="V12">
         <v>0</v>
@@ -3245,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="X12">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y12">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3260,40 +3218,40 @@
         <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD12">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AE12">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AF12">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AG12">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AH12">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI12">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK12">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL12">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AM12">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AN12">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3338,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3376,7 +3334,7 @@
         <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -3403,7 +3361,7 @@
         <v>-1</v>
       </c>
       <c r="O13" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -3561,7 +3519,7 @@
         <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3588,7 +3546,7 @@
         <v>-1</v>
       </c>
       <c r="O14" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -3600,70 +3558,70 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U14">
+        <v>3.1</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>2.43</v>
+      </c>
+      <c r="Y14">
+        <v>1.43</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>1.22</v>
+      </c>
+      <c r="AD14">
         <v>3.6</v>
       </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>2.55</v>
-      </c>
-      <c r="Y14">
-        <v>1.38</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>1.25</v>
-      </c>
-      <c r="AD14">
-        <v>3.35</v>
-      </c>
       <c r="AE14">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF14">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG14">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AH14">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI14">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AJ14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL14">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AM14">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AN14">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3708,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3737,16 +3695,16 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3773,7 +3731,7 @@
         <v>-1</v>
       </c>
       <c r="O15" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -3922,7 +3880,7 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
         <v>109</v>
@@ -3931,7 +3889,7 @@
         <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3958,7 +3916,7 @@
         <v>-1</v>
       </c>
       <c r="O16" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -3970,13 +3928,13 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -3985,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -4000,40 +3958,40 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4078,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4107,7 +4065,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4116,7 +4074,7 @@
         <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4143,7 +4101,7 @@
         <v>-1</v>
       </c>
       <c r="O17" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -4155,13 +4113,13 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4170,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4185,40 +4143,40 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4263,13 +4221,13 @@
         <v>0</v>
       </c>
       <c r="BC17">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD17">
         <v>0</v>
       </c>
       <c r="BE17">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF17">
         <v>0</v>
@@ -4292,16 +4250,16 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
       </c>
       <c r="F18" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -4328,7 +4286,7 @@
         <v>-1</v>
       </c>
       <c r="O18" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -4486,7 +4444,7 @@
         <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -4513,7 +4471,7 @@
         <v>-1</v>
       </c>
       <c r="O19" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P19">
         <v>2.19</v>
@@ -4671,7 +4629,7 @@
         <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4698,7 +4656,7 @@
         <v>-1</v>
       </c>
       <c r="O20" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P20">
         <v>2.19</v>
@@ -4856,7 +4814,7 @@
         <v>129</v>
       </c>
       <c r="F21" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4883,7 +4841,7 @@
         <v>-1</v>
       </c>
       <c r="O21" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -4895,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -4910,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4925,40 +4883,40 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI21">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ21">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL21">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM21">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN21">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -5003,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5032,7 +4990,7 @@
         <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
         <v>109</v>
@@ -5041,7 +4999,7 @@
         <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -5068,82 +5026,82 @@
         <v>-1</v>
       </c>
       <c r="O22" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO22">
         <v>0</v>
@@ -5185,19 +5143,19 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5217,7 +5175,7 @@
         <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>109</v>
@@ -5226,7 +5184,7 @@
         <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -5253,7 +5211,7 @@
         <v>-1</v>
       </c>
       <c r="O23" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -5265,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5280,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -5295,40 +5253,40 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5373,13 +5331,13 @@
         <v>0</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -5411,7 +5369,7 @@
         <v>132</v>
       </c>
       <c r="F24" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -5438,82 +5396,82 @@
         <v>-1</v>
       </c>
       <c r="O24" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P24">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R24">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T24">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U24">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W24">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X24">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC24">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD24">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG24">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="AH24">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ24">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL24">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5555,19 +5513,19 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC24">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD24">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE24">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG24">
         <v>0</v>
@@ -5587,7 +5545,7 @@
         <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>109</v>
@@ -5596,7 +5554,7 @@
         <v>133</v>
       </c>
       <c r="F25" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5623,136 +5581,136 @@
         <v>-1</v>
       </c>
       <c r="O25" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="T25">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="U25">
-        <v>4.8</v>
+        <v>2.99</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X25">
-        <v>2.17</v>
+        <v>2.72</v>
       </c>
       <c r="Y25">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AD25">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="AE25">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="AF25">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AG25">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AH25">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AI25">
-        <v>4</v>
+        <v>5.12</v>
       </c>
       <c r="AJ25">
+        <v>1.11</v>
+      </c>
+      <c r="AK25">
+        <v>1.59</v>
+      </c>
+      <c r="AL25">
+        <v>2.21</v>
+      </c>
+      <c r="AM25">
+        <v>1.27</v>
+      </c>
+      <c r="AN25">
+        <v>1.45</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
         <v>1.18</v>
       </c>
-      <c r="AK25">
-        <v>1.62</v>
-      </c>
-      <c r="AL25">
-        <v>2.12</v>
-      </c>
-      <c r="AM25">
-        <v>1.16</v>
-      </c>
-      <c r="AN25">
-        <v>2.12</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>0</v>
-      </c>
       <c r="BC25">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="BD25">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE25">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="BF25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5772,7 +5730,7 @@
         <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D26" t="s">
         <v>109</v>
@@ -5781,7 +5739,7 @@
         <v>134</v>
       </c>
       <c r="F26" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5808,82 +5766,82 @@
         <v>-1</v>
       </c>
       <c r="O26" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P26">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AD26">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AE26">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF26">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG26">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="AH26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI26">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AJ26">
         <v>1.1</v>
       </c>
       <c r="AK26">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL26">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AM26">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AN26">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AO26">
         <v>0</v>
@@ -5925,19 +5883,19 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG26">
         <v>0</v>
@@ -5957,7 +5915,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5966,7 +5924,7 @@
         <v>135</v>
       </c>
       <c r="F27" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5993,82 +5951,82 @@
         <v>-1</v>
       </c>
       <c r="O27" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P27">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="Q27">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R27">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="S27">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="T27">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="U27">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="V27">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>2.77</v>
+        <v>3.16</v>
       </c>
       <c r="X27">
         <v>2.54</v>
       </c>
       <c r="Y27">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="Z27">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="AA27">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AB27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC27">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AD27">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AE27">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AF27">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AG27">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH27">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI27">
-        <v>5.22</v>
+        <v>4.92</v>
       </c>
       <c r="AJ27">
         <v>1.11</v>
       </c>
       <c r="AK27">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL27">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AM27">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AN27">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -6110,19 +6068,19 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC27">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="BD27">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE27">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="BF27">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6151,7 +6109,7 @@
         <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -6178,7 +6136,7 @@
         <v>-1</v>
       </c>
       <c r="O28" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6190,13 +6148,13 @@
         <v>0</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -6205,10 +6163,10 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -6220,40 +6178,40 @@
         <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AD28">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AE28">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AG28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AH28">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AI28">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AJ28">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AM28">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AN28">
-        <v>1.46</v>
+        <v>2.12</v>
       </c>
       <c r="AO28">
         <v>0</v>
@@ -6298,13 +6256,13 @@
         <v>0</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD28">
         <v>0</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF28">
         <v>0</v>
@@ -6336,7 +6294,7 @@
         <v>137</v>
       </c>
       <c r="F29" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -6363,7 +6321,7 @@
         <v>-1</v>
       </c>
       <c r="O29" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P29">
         <v>1.59</v>
@@ -6512,16 +6470,16 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -6548,136 +6506,136 @@
         <v>-1</v>
       </c>
       <c r="O30" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P30">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="Q30">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="R30">
-        <v>2.2</v>
+        <v>7.38</v>
       </c>
       <c r="S30">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL30">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS30">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT30">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU30">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV30">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY30">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ30">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA30">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD30">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE30">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF30">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6697,16 +6655,16 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
       </c>
       <c r="F31" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -6733,136 +6691,136 @@
         <v>-1</v>
       </c>
       <c r="O31" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.58</v>
+        <v>3.44</v>
       </c>
       <c r="T31">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="U31">
-        <v>7.5</v>
+        <v>2.85</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X31">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="Y31">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC31">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AE31">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AF31">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AG31">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="AH31">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI31">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK31">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="AL31">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AM31">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ31">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA31">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC31">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="BD31">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE31">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="BF31">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6882,7 +6840,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6891,7 +6849,7 @@
         <v>140</v>
       </c>
       <c r="F32" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6918,25 +6876,25 @@
         <v>-1</v>
       </c>
       <c r="O32" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>7.38</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6945,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6960,40 +6918,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -7038,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7067,7 +7025,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7076,7 +7034,7 @@
         <v>141</v>
       </c>
       <c r="F33" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7103,7 +7061,7 @@
         <v>-1</v>
       </c>
       <c r="O33" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -7252,7 +7210,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7261,7 +7219,7 @@
         <v>142</v>
       </c>
       <c r="F34" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7288,7 +7246,7 @@
         <v>-1</v>
       </c>
       <c r="O34" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P34">
         <v>0</v>
@@ -7446,7 +7404,7 @@
         <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7473,7 +7431,7 @@
         <v>-1</v>
       </c>
       <c r="O35" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -7631,7 +7589,7 @@
         <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7658,7 +7616,7 @@
         <v>-1</v>
       </c>
       <c r="O36" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P36">
         <v>3.5</v>
@@ -7807,7 +7765,7 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
         <v>108</v>
@@ -7816,7 +7774,7 @@
         <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7843,16 +7801,16 @@
         <v>-1</v>
       </c>
       <c r="O37" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -7885,40 +7843,40 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI37">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO37">
         <v>0</v>
@@ -7992,16 +7950,16 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
         <v>146</v>
       </c>
       <c r="F38" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -8028,136 +7986,136 @@
         <v>-1</v>
       </c>
       <c r="O38" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P38">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AH38">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ38">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL38">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO38">
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ38">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR38">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS38">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT38">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU38">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV38">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW38">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX38">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY38">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ38">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA38">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB38">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC38">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD38">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE38">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF38">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG38">
         <v>0</v>
@@ -8177,16 +8135,16 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
       </c>
       <c r="F39" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -8213,79 +8171,79 @@
         <v>-1</v>
       </c>
       <c r="O39" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P39">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC39">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AD39">
-        <v>3.45</v>
+        <v>2.93</v>
       </c>
       <c r="AE39">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AF39">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AG39">
-        <v>2.9</v>
+        <v>3.86</v>
       </c>
       <c r="AH39">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AI39">
-        <v>5.1</v>
+        <v>8.1</v>
       </c>
       <c r="AJ39">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK39">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL39">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AM39">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AN39">
         <v>1.32</v>
@@ -8294,55 +8252,55 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV39">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ39">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA39">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC39">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE39">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF39">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8371,7 +8329,7 @@
         <v>148</v>
       </c>
       <c r="F40" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -8398,7 +8356,7 @@
         <v>-1</v>
       </c>
       <c r="O40" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P40">
         <v>0</v>
@@ -8556,7 +8514,7 @@
         <v>149</v>
       </c>
       <c r="F41" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -8583,121 +8541,121 @@
         <v>-1</v>
       </c>
       <c r="O41" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P41">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="Q41">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R41">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="S41">
-        <v>2.7</v>
+        <v>2.04</v>
       </c>
       <c r="T41">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="U41">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="V41">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="X41">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="Y41">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC41">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AD41">
         <v>2.66</v>
       </c>
       <c r="AE41">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="AF41">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG41">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AH41">
         <v>1.16</v>
       </c>
       <c r="AI41">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ41">
         <v>1.01</v>
       </c>
       <c r="AK41">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AL41">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AM41">
+        <v>1.18</v>
+      </c>
+      <c r="AN41">
+        <v>2.5</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>1.5</v>
+      </c>
+      <c r="AQ41">
+        <v>1.89</v>
+      </c>
+      <c r="AR41">
+        <v>2.4</v>
+      </c>
+      <c r="AS41">
+        <v>3.15</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>2.33</v>
+      </c>
+      <c r="AV41">
+        <v>1.8</v>
+      </c>
+      <c r="AW41">
+        <v>1.49</v>
+      </c>
+      <c r="AX41">
         <v>1.3</v>
       </c>
-      <c r="AN41">
-        <v>1.68</v>
-      </c>
-      <c r="AO41">
-        <v>0</v>
-      </c>
-      <c r="AP41">
-        <v>1.27</v>
-      </c>
-      <c r="AQ41">
-        <v>1.47</v>
-      </c>
-      <c r="AR41">
-        <v>1.77</v>
-      </c>
-      <c r="AS41">
-        <v>2.2</v>
-      </c>
-      <c r="AT41">
-        <v>2.85</v>
-      </c>
-      <c r="AU41">
-        <v>3.3</v>
-      </c>
-      <c r="AV41">
-        <v>2.45</v>
-      </c>
-      <c r="AW41">
-        <v>1.92</v>
-      </c>
-      <c r="AX41">
-        <v>1.58</v>
-      </c>
       <c r="AY41">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ41">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="BA41">
-        <v>2.16</v>
+        <v>3.95</v>
       </c>
       <c r="BB41">
         <v>1.28</v>
@@ -8706,13 +8664,13 @@
         <v>2.41</v>
       </c>
       <c r="BD41">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="BE41">
         <v>1.47</v>
       </c>
       <c r="BF41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8741,7 +8699,7 @@
         <v>150</v>
       </c>
       <c r="F42" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -8768,121 +8726,121 @@
         <v>-1</v>
       </c>
       <c r="O42" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P42">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="Q42">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R42">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="S42">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="T42">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U42">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W42">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="X42">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Y42">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z42">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB42">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC42">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AD42">
         <v>2.66</v>
       </c>
       <c r="AE42">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AF42">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AH42">
         <v>1.16</v>
       </c>
       <c r="AI42">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ42">
         <v>1.01</v>
       </c>
       <c r="AK42">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AL42">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AM42">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AN42">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="AO42">
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR42">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AS42">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU42">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AV42">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AW42">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AX42">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AY42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ42">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="BA42">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="BB42">
         <v>1.28</v>
@@ -8891,13 +8849,13 @@
         <v>2.41</v>
       </c>
       <c r="BD42">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="BE42">
         <v>1.47</v>
       </c>
       <c r="BF42">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8926,7 +8884,7 @@
         <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -8953,7 +8911,7 @@
         <v>-1</v>
       </c>
       <c r="O43" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P43">
         <v>2.38</v>
@@ -9111,7 +9069,7 @@
         <v>152</v>
       </c>
       <c r="F44" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -9138,7 +9096,7 @@
         <v>-1</v>
       </c>
       <c r="O44" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P44">
         <v>2.53</v>
@@ -9287,7 +9245,7 @@
         <v>74</v>
       </c>
       <c r="C45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D45" t="s">
         <v>109</v>
@@ -9296,7 +9254,7 @@
         <v>153</v>
       </c>
       <c r="F45" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -9323,7 +9281,7 @@
         <v>-1</v>
       </c>
       <c r="O45" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -9481,7 +9439,7 @@
         <v>154</v>
       </c>
       <c r="F46" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -9508,7 +9466,7 @@
         <v>-1</v>
       </c>
       <c r="O46" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P46">
         <v>1.27</v>
@@ -9666,7 +9624,7 @@
         <v>155</v>
       </c>
       <c r="F47" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -9693,7 +9651,7 @@
         <v>-1</v>
       </c>
       <c r="O47" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="P47">
         <v>6.5</v>
@@ -9851,7 +9809,7 @@
         <v>156</v>
       </c>
       <c r="F48" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -9878,7 +9836,7 @@
         <v>-1</v>
       </c>
       <c r="O48" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P48">
         <v>1.64</v>
@@ -9887,7 +9845,7 @@
         <v>5.05</v>
       </c>
       <c r="R48">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="S48">
         <v>2.09</v>
@@ -9896,7 +9854,7 @@
         <v>3.22</v>
       </c>
       <c r="U48">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="V48">
         <v>1.11</v>
@@ -9920,25 +9878,25 @@
         <v>1.01</v>
       </c>
       <c r="AC48">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD48">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AG48">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AH48">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AI48">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AJ48">
         <v>1.78</v>
@@ -9950,58 +9908,58 @@
         <v>4.01</v>
       </c>
       <c r="AM48">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN48">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AO48">
         <v>0</v>
       </c>
       <c r="AP48">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AQ48">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AR48">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AS48">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AT48">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="AU48">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AV48">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AW48">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AX48">
         <v>1.81</v>
       </c>
       <c r="AY48">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AZ48">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BA48">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BB48">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="BC48">
         <v>1.32</v>
       </c>
       <c r="BD48">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE48">
         <v>2.93</v>
@@ -10027,7 +9985,7 @@
         <v>77</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D49" t="s">
         <v>109</v>
@@ -10036,7 +9994,7 @@
         <v>157</v>
       </c>
       <c r="F49" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -10063,7 +10021,7 @@
         <v>-1</v>
       </c>
       <c r="O49" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -10221,7 +10179,7 @@
         <v>158</v>
       </c>
       <c r="F50" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -10248,7 +10206,7 @@
         <v>-1</v>
       </c>
       <c r="O50" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -10406,7 +10364,7 @@
         <v>159</v>
       </c>
       <c r="F51" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -10433,7 +10391,7 @@
         <v>-1</v>
       </c>
       <c r="O51" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -10591,7 +10549,7 @@
         <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -10618,7 +10576,7 @@
         <v>-1</v>
       </c>
       <c r="O52" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -10776,7 +10734,7 @@
         <v>161</v>
       </c>
       <c r="F53" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -10803,7 +10761,7 @@
         <v>-1</v>
       </c>
       <c r="O53" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -10961,7 +10919,7 @@
         <v>162</v>
       </c>
       <c r="F54" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -10988,7 +10946,7 @@
         <v>-1</v>
       </c>
       <c r="O54" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -11146,7 +11104,7 @@
         <v>163</v>
       </c>
       <c r="F55" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -11173,7 +11131,7 @@
         <v>-1</v>
       </c>
       <c r="O55" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -11331,7 +11289,7 @@
         <v>164</v>
       </c>
       <c r="F56" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -11358,7 +11316,7 @@
         <v>-1</v>
       </c>
       <c r="O56" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P56">
         <v>0</v>
@@ -11516,7 +11474,7 @@
         <v>165</v>
       </c>
       <c r="F57" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -11543,7 +11501,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -11692,7 +11650,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11701,7 +11659,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11728,7 +11686,7 @@
         <v>-1</v>
       </c>
       <c r="O58" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P58">
         <v>0</v>
@@ -11880,13 +11838,13 @@
         <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -11913,7 +11871,7 @@
         <v>-1</v>
       </c>
       <c r="O59" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P59">
         <v>0</v>
@@ -12065,13 +12023,13 @@
         <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E60" t="s">
         <v>168</v>
       </c>
       <c r="F60" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -12098,7 +12056,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12256,7 +12214,7 @@
         <v>169</v>
       </c>
       <c r="F61" t="s">
-        <v>154</v>
+        <v>232</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -12283,7 +12241,7 @@
         <v>-1</v>
       </c>
       <c r="O61" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -12432,7 +12390,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12441,7 +12399,7 @@
         <v>170</v>
       </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -12468,7 +12426,7 @@
         <v>-1</v>
       </c>
       <c r="O62" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P62">
         <v>0</v>
@@ -12617,7 +12575,7 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
         <v>109</v>
@@ -12626,7 +12584,7 @@
         <v>171</v>
       </c>
       <c r="F63" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -12653,7 +12611,7 @@
         <v>-1</v>
       </c>
       <c r="O63" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -12799,19 +12757,19 @@
         <v>46148</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E64" t="s">
         <v>172</v>
       </c>
       <c r="F64" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12838,82 +12796,82 @@
         <v>-1</v>
       </c>
       <c r="O64" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL64">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO64">
         <v>0</v>
@@ -12955,19 +12913,19 @@
         <v>0</v>
       </c>
       <c r="BB64">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC64">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD64">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE64">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG64">
         <v>0</v>
@@ -12976,7 +12934,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3">
-        <v>46148.875</v>
+        <v>46148.91666666666</v>
       </c>
     </row>
     <row r="65" spans="1:61">
@@ -12984,19 +12942,19 @@
         <v>46148</v>
       </c>
       <c r="B65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C65" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D65" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E65" t="s">
         <v>173</v>
       </c>
       <c r="F65" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -13023,16 +12981,16 @@
         <v>-1</v>
       </c>
       <c r="O65" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -13071,10 +13029,10 @@
         <v>0</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG65">
         <v>0</v>
@@ -13161,1301 +13119,6 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="66" spans="1:61">
-      <c r="A66" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" t="s">
-        <v>109</v>
-      </c>
-      <c r="E66" t="s">
-        <v>174</v>
-      </c>
-      <c r="F66" t="s">
-        <v>244</v>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>-1</v>
-      </c>
-      <c r="N66">
-        <v>-1</v>
-      </c>
-      <c r="O66" t="s">
-        <v>251</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>0</v>
-      </c>
-      <c r="AB66">
-        <v>0</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66">
-        <v>0</v>
-      </c>
-      <c r="AI66">
-        <v>0</v>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>0</v>
-      </c>
-      <c r="AN66">
-        <v>0</v>
-      </c>
-      <c r="AO66">
-        <v>0</v>
-      </c>
-      <c r="AP66">
-        <v>0</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66">
-        <v>0</v>
-      </c>
-      <c r="AV66">
-        <v>0</v>
-      </c>
-      <c r="AW66">
-        <v>0</v>
-      </c>
-      <c r="AX66">
-        <v>0</v>
-      </c>
-      <c r="AY66">
-        <v>0</v>
-      </c>
-      <c r="AZ66">
-        <v>0</v>
-      </c>
-      <c r="BA66">
-        <v>0</v>
-      </c>
-      <c r="BB66">
-        <v>0</v>
-      </c>
-      <c r="BC66">
-        <v>0</v>
-      </c>
-      <c r="BD66">
-        <v>0</v>
-      </c>
-      <c r="BE66">
-        <v>0</v>
-      </c>
-      <c r="BF66">
-        <v>0</v>
-      </c>
-      <c r="BG66">
-        <v>0</v>
-      </c>
-      <c r="BH66">
-        <v>0</v>
-      </c>
-      <c r="BI66" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="67" spans="1:61">
-      <c r="A67" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67" t="s">
-        <v>109</v>
-      </c>
-      <c r="E67" t="s">
-        <v>175</v>
-      </c>
-      <c r="F67" t="s">
-        <v>245</v>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>-1</v>
-      </c>
-      <c r="N67">
-        <v>-1</v>
-      </c>
-      <c r="O67" t="s">
-        <v>251</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>0</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67">
-        <v>0</v>
-      </c>
-      <c r="AI67">
-        <v>0</v>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>0</v>
-      </c>
-      <c r="AN67">
-        <v>0</v>
-      </c>
-      <c r="AO67">
-        <v>0</v>
-      </c>
-      <c r="AP67">
-        <v>0</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67">
-        <v>0</v>
-      </c>
-      <c r="AV67">
-        <v>0</v>
-      </c>
-      <c r="AW67">
-        <v>0</v>
-      </c>
-      <c r="AX67">
-        <v>0</v>
-      </c>
-      <c r="AY67">
-        <v>0</v>
-      </c>
-      <c r="AZ67">
-        <v>0</v>
-      </c>
-      <c r="BA67">
-        <v>0</v>
-      </c>
-      <c r="BB67">
-        <v>0</v>
-      </c>
-      <c r="BC67">
-        <v>0</v>
-      </c>
-      <c r="BD67">
-        <v>0</v>
-      </c>
-      <c r="BE67">
-        <v>0</v>
-      </c>
-      <c r="BF67">
-        <v>0</v>
-      </c>
-      <c r="BG67">
-        <v>0</v>
-      </c>
-      <c r="BH67">
-        <v>0</v>
-      </c>
-      <c r="BI67" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="68" spans="1:61">
-      <c r="A68" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B68" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" t="s">
-        <v>104</v>
-      </c>
-      <c r="D68" t="s">
-        <v>109</v>
-      </c>
-      <c r="E68" t="s">
-        <v>176</v>
-      </c>
-      <c r="F68" t="s">
-        <v>246</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>-1</v>
-      </c>
-      <c r="N68">
-        <v>-1</v>
-      </c>
-      <c r="O68" t="s">
-        <v>252</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>0</v>
-      </c>
-      <c r="AB68">
-        <v>0</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68">
-        <v>0</v>
-      </c>
-      <c r="AI68">
-        <v>0</v>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>0</v>
-      </c>
-      <c r="AN68">
-        <v>0</v>
-      </c>
-      <c r="AO68">
-        <v>0</v>
-      </c>
-      <c r="AP68">
-        <v>0</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68">
-        <v>0</v>
-      </c>
-      <c r="AV68">
-        <v>0</v>
-      </c>
-      <c r="AW68">
-        <v>0</v>
-      </c>
-      <c r="AX68">
-        <v>0</v>
-      </c>
-      <c r="AY68">
-        <v>0</v>
-      </c>
-      <c r="AZ68">
-        <v>0</v>
-      </c>
-      <c r="BA68">
-        <v>0</v>
-      </c>
-      <c r="BB68">
-        <v>0</v>
-      </c>
-      <c r="BC68">
-        <v>0</v>
-      </c>
-      <c r="BD68">
-        <v>0</v>
-      </c>
-      <c r="BE68">
-        <v>0</v>
-      </c>
-      <c r="BF68">
-        <v>0</v>
-      </c>
-      <c r="BG68">
-        <v>0</v>
-      </c>
-      <c r="BH68">
-        <v>0</v>
-      </c>
-      <c r="BI68" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="69" spans="1:61">
-      <c r="A69" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
-      <c r="C69" t="s">
-        <v>104</v>
-      </c>
-      <c r="D69" t="s">
-        <v>109</v>
-      </c>
-      <c r="E69" t="s">
-        <v>177</v>
-      </c>
-      <c r="F69" t="s">
-        <v>247</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>-1</v>
-      </c>
-      <c r="N69">
-        <v>-1</v>
-      </c>
-      <c r="O69" t="s">
-        <v>251</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>0</v>
-      </c>
-      <c r="AD69">
-        <v>0</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69">
-        <v>0</v>
-      </c>
-      <c r="AI69">
-        <v>0</v>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>0</v>
-      </c>
-      <c r="AN69">
-        <v>0</v>
-      </c>
-      <c r="AO69">
-        <v>0</v>
-      </c>
-      <c r="AP69">
-        <v>0</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69">
-        <v>0</v>
-      </c>
-      <c r="AV69">
-        <v>0</v>
-      </c>
-      <c r="AW69">
-        <v>0</v>
-      </c>
-      <c r="AX69">
-        <v>0</v>
-      </c>
-      <c r="AY69">
-        <v>0</v>
-      </c>
-      <c r="AZ69">
-        <v>0</v>
-      </c>
-      <c r="BA69">
-        <v>0</v>
-      </c>
-      <c r="BB69">
-        <v>0</v>
-      </c>
-      <c r="BC69">
-        <v>0</v>
-      </c>
-      <c r="BD69">
-        <v>0</v>
-      </c>
-      <c r="BE69">
-        <v>0</v>
-      </c>
-      <c r="BF69">
-        <v>0</v>
-      </c>
-      <c r="BG69">
-        <v>0</v>
-      </c>
-      <c r="BH69">
-        <v>0</v>
-      </c>
-      <c r="BI69" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="70" spans="1:61">
-      <c r="A70" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" t="s">
-        <v>103</v>
-      </c>
-      <c r="D70" t="s">
-        <v>109</v>
-      </c>
-      <c r="E70" t="s">
-        <v>178</v>
-      </c>
-      <c r="F70" t="s">
-        <v>248</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>-1</v>
-      </c>
-      <c r="N70">
-        <v>-1</v>
-      </c>
-      <c r="O70" t="s">
-        <v>251</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
-      <c r="AH70">
-        <v>0</v>
-      </c>
-      <c r="AI70">
-        <v>0</v>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70">
-        <v>0</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>0</v>
-      </c>
-      <c r="AN70">
-        <v>0</v>
-      </c>
-      <c r="AO70">
-        <v>0</v>
-      </c>
-      <c r="AP70">
-        <v>0</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70">
-        <v>0</v>
-      </c>
-      <c r="AV70">
-        <v>0</v>
-      </c>
-      <c r="AW70">
-        <v>0</v>
-      </c>
-      <c r="AX70">
-        <v>0</v>
-      </c>
-      <c r="AY70">
-        <v>0</v>
-      </c>
-      <c r="AZ70">
-        <v>0</v>
-      </c>
-      <c r="BA70">
-        <v>0</v>
-      </c>
-      <c r="BB70">
-        <v>0</v>
-      </c>
-      <c r="BC70">
-        <v>0</v>
-      </c>
-      <c r="BD70">
-        <v>0</v>
-      </c>
-      <c r="BE70">
-        <v>0</v>
-      </c>
-      <c r="BF70">
-        <v>0</v>
-      </c>
-      <c r="BG70">
-        <v>0</v>
-      </c>
-      <c r="BH70">
-        <v>0</v>
-      </c>
-      <c r="BI70" s="3">
-        <v>46148.875</v>
-      </c>
-    </row>
-    <row r="71" spans="1:61">
-      <c r="A71" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B71" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" t="s">
-        <v>106</v>
-      </c>
-      <c r="D71" t="s">
-        <v>108</v>
-      </c>
-      <c r="E71" t="s">
-        <v>179</v>
-      </c>
-      <c r="F71" t="s">
-        <v>249</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>-1</v>
-      </c>
-      <c r="N71">
-        <v>-1</v>
-      </c>
-      <c r="O71" t="s">
-        <v>251</v>
-      </c>
-      <c r="P71">
-        <v>2.14</v>
-      </c>
-      <c r="Q71">
-        <v>3.4</v>
-      </c>
-      <c r="R71">
-        <v>2.8</v>
-      </c>
-      <c r="S71">
-        <v>2.78</v>
-      </c>
-      <c r="T71">
-        <v>2.19</v>
-      </c>
-      <c r="U71">
-        <v>3.47</v>
-      </c>
-      <c r="V71">
-        <v>1.3</v>
-      </c>
-      <c r="W71">
-        <v>3.08</v>
-      </c>
-      <c r="X71">
-        <v>2.47</v>
-      </c>
-      <c r="Y71">
-        <v>1.45</v>
-      </c>
-      <c r="Z71">
-        <v>5.8</v>
-      </c>
-      <c r="AA71">
-        <v>1.07</v>
-      </c>
-      <c r="AB71">
-        <v>1.04</v>
-      </c>
-      <c r="AC71">
-        <v>1.18</v>
-      </c>
-      <c r="AD71">
-        <v>3.82</v>
-      </c>
-      <c r="AE71">
-        <v>1.71</v>
-      </c>
-      <c r="AF71">
-        <v>2.07</v>
-      </c>
-      <c r="AG71">
-        <v>2.7</v>
-      </c>
-      <c r="AH71">
-        <v>1.36</v>
-      </c>
-      <c r="AI71">
-        <v>4.75</v>
-      </c>
-      <c r="AJ71">
-        <v>1.1</v>
-      </c>
-      <c r="AK71">
-        <v>1.58</v>
-      </c>
-      <c r="AL71">
-        <v>2.17</v>
-      </c>
-      <c r="AM71">
-        <v>1.23</v>
-      </c>
-      <c r="AN71">
-        <v>1.53</v>
-      </c>
-      <c r="AO71">
-        <v>0</v>
-      </c>
-      <c r="AP71">
-        <v>0</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71">
-        <v>0</v>
-      </c>
-      <c r="AV71">
-        <v>0</v>
-      </c>
-      <c r="AW71">
-        <v>0</v>
-      </c>
-      <c r="AX71">
-        <v>0</v>
-      </c>
-      <c r="AY71">
-        <v>0</v>
-      </c>
-      <c r="AZ71">
-        <v>0</v>
-      </c>
-      <c r="BA71">
-        <v>0</v>
-      </c>
-      <c r="BB71">
-        <v>1.16</v>
-      </c>
-      <c r="BC71">
-        <v>1.94</v>
-      </c>
-      <c r="BD71">
-        <v>4.1</v>
-      </c>
-      <c r="BE71">
-        <v>1.76</v>
-      </c>
-      <c r="BF71">
-        <v>1.18</v>
-      </c>
-      <c r="BG71">
-        <v>0</v>
-      </c>
-      <c r="BH71">
-        <v>0</v>
-      </c>
-      <c r="BI71" s="3">
-        <v>46148.91666666666</v>
-      </c>
-    </row>
-    <row r="72" spans="1:61">
-      <c r="A72" s="2">
-        <v>46148</v>
-      </c>
-      <c r="B72" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" t="s">
-        <v>107</v>
-      </c>
-      <c r="D72" t="s">
-        <v>108</v>
-      </c>
-      <c r="E72" t="s">
-        <v>180</v>
-      </c>
-      <c r="F72" t="s">
-        <v>250</v>
-      </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
-      <c r="H72">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>0</v>
-      </c>
-      <c r="K72">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>-1</v>
-      </c>
-      <c r="N72">
-        <v>-1</v>
-      </c>
-      <c r="O72" t="s">
-        <v>251</v>
-      </c>
-      <c r="P72">
-        <v>2.02</v>
-      </c>
-      <c r="Q72">
-        <v>3.34</v>
-      </c>
-      <c r="R72">
-        <v>3.27</v>
-      </c>
-      <c r="S72">
-        <v>0</v>
-      </c>
-      <c r="T72">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>0</v>
-      </c>
-      <c r="V72">
-        <v>0</v>
-      </c>
-      <c r="W72">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>0</v>
-      </c>
-      <c r="Y72">
-        <v>0</v>
-      </c>
-      <c r="Z72">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>0</v>
-      </c>
-      <c r="AB72">
-        <v>0</v>
-      </c>
-      <c r="AC72">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>0</v>
-      </c>
-      <c r="AE72">
-        <v>1.88</v>
-      </c>
-      <c r="AF72">
-        <v>1.88</v>
-      </c>
-      <c r="AG72">
-        <v>0</v>
-      </c>
-      <c r="AH72">
-        <v>0</v>
-      </c>
-      <c r="AI72">
-        <v>0</v>
-      </c>
-      <c r="AJ72">
-        <v>0</v>
-      </c>
-      <c r="AK72">
-        <v>0</v>
-      </c>
-      <c r="AL72">
-        <v>0</v>
-      </c>
-      <c r="AM72">
-        <v>0</v>
-      </c>
-      <c r="AN72">
-        <v>0</v>
-      </c>
-      <c r="AO72">
-        <v>0</v>
-      </c>
-      <c r="AP72">
-        <v>0</v>
-      </c>
-      <c r="AQ72">
-        <v>0</v>
-      </c>
-      <c r="AR72">
-        <v>0</v>
-      </c>
-      <c r="AS72">
-        <v>0</v>
-      </c>
-      <c r="AT72">
-        <v>0</v>
-      </c>
-      <c r="AU72">
-        <v>0</v>
-      </c>
-      <c r="AV72">
-        <v>0</v>
-      </c>
-      <c r="AW72">
-        <v>0</v>
-      </c>
-      <c r="AX72">
-        <v>0</v>
-      </c>
-      <c r="AY72">
-        <v>0</v>
-      </c>
-      <c r="AZ72">
-        <v>0</v>
-      </c>
-      <c r="BA72">
-        <v>0</v>
-      </c>
-      <c r="BB72">
-        <v>0</v>
-      </c>
-      <c r="BC72">
-        <v>0</v>
-      </c>
-      <c r="BD72">
-        <v>0</v>
-      </c>
-      <c r="BE72">
-        <v>0</v>
-      </c>
-      <c r="BF72">
-        <v>0</v>
-      </c>
-      <c r="BG72">
-        <v>0</v>
-      </c>
-      <c r="BH72">
-        <v>0</v>
-      </c>
-      <c r="BI72" s="3">
         <v>46148.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -325,15 +325,15 @@
     <t>Jamaica Jamaica National Premier League</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
     <t>USA MLS Next Pro</t>
   </si>
   <si>
-    <t>Algeria Ligue 1</t>
-  </si>
-  <si>
     <t>USA USL Championship</t>
   </si>
   <si>
@@ -349,10 +349,13 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>Shanghai SIPG</t>
+  </si>
+  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>Shanghai SIPG</t>
+    <t>Sidama Bunna</t>
   </si>
   <si>
     <t>Yunnan Yukun</t>
@@ -361,9 +364,6 @@
     <t>Fasil Ketema</t>
   </si>
   <si>
-    <t>Sidama Bunna</t>
-  </si>
-  <si>
     <t>Minerva Punjab</t>
   </si>
   <si>
@@ -376,78 +376,81 @@
     <t>Slavia Sofia</t>
   </si>
   <si>
+    <t>Hanácká</t>
+  </si>
+  <si>
+    <t>Samgurali</t>
+  </si>
+  <si>
+    <t>Baník Ostrava U21</t>
+  </si>
+  <si>
+    <t>Dila</t>
+  </si>
+  <si>
+    <t>FS Jelgava</t>
+  </si>
+  <si>
     <t>Sparta Praha II</t>
   </si>
   <si>
-    <t>Samgurali</t>
-  </si>
-  <si>
     <t>České Budějovice</t>
   </si>
   <si>
-    <t>Baník Ostrava U21</t>
-  </si>
-  <si>
-    <t>Hanácká</t>
-  </si>
-  <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>FS Jelgava</t>
-  </si>
-  <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Táborsko</t>
+  </si>
+  <si>
+    <t>Aris</t>
+  </si>
+  <si>
     <t>Líšeň</t>
   </si>
   <si>
+    <t>Ústí nad Labem</t>
+  </si>
+  <si>
     <t>AEK Larnaca</t>
   </si>
   <si>
-    <t>Ústí nad Labem</t>
+    <t>Vlašim</t>
   </si>
   <si>
     <t>FUS Rabat</t>
   </si>
   <si>
-    <t>Aris</t>
-  </si>
-  <si>
-    <t>Vlašim</t>
+    <t>Egersund</t>
   </si>
   <si>
     <t>Paphos</t>
   </si>
   <si>
-    <t>Táborsko</t>
-  </si>
-  <si>
-    <t>Egersund</t>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Häcken W</t>
   </si>
   <si>
     <t>Žalgiris</t>
   </si>
   <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Häcken W</t>
+    <t>Barcelona W</t>
   </si>
   <si>
     <t>Al Sharjah</t>
   </si>
   <si>
-    <t>Barcelona W</t>
-  </si>
-  <si>
     <t>Shabab Al Ahli Dubai</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
@@ -460,21 +463,18 @@
     <t>Spartak Varna</t>
   </si>
   <si>
-    <t>Gagra</t>
+    <t>AmaZulu</t>
+  </si>
+  <si>
+    <t>Richards Bay</t>
+  </si>
+  <si>
+    <t>Marumo Gallants</t>
   </si>
   <si>
     <t>Mamelodi Sundowns</t>
   </si>
   <si>
-    <t>AmaZulu</t>
-  </si>
-  <si>
-    <t>Richards Bay</t>
-  </si>
-  <si>
-    <t>Marumo Gallants</t>
-  </si>
-  <si>
     <t>Wydad Casablanca</t>
   </si>
   <si>
@@ -493,45 +493,45 @@
     <t>Treasure Beach</t>
   </si>
   <si>
+    <t>Waterhouse</t>
+  </si>
+  <si>
+    <t>Spanish Town Police FC</t>
+  </si>
+  <si>
+    <t>Portmore United</t>
+  </si>
+  <si>
+    <t>Chapelton</t>
+  </si>
+  <si>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
     <t>Cavalier</t>
   </si>
   <si>
-    <t>Mount Pleasant Academy FC</t>
-  </si>
-  <si>
-    <t>Chapelton</t>
-  </si>
-  <si>
-    <t>Spanish Town Police FC</t>
-  </si>
-  <si>
-    <t>Waterhouse</t>
-  </si>
-  <si>
-    <t>Portmore United</t>
+    <t>Ben Aknoun</t>
+  </si>
+  <si>
+    <t>Al Jazeera</t>
+  </si>
+  <si>
+    <t>Al Wihdat</t>
+  </si>
+  <si>
+    <t>Al Ramtha</t>
   </si>
   <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
-    <t>Al Wihdat</t>
+    <t>Al Hussein</t>
   </si>
   <si>
     <t>Sporting KC II</t>
   </si>
   <si>
-    <t>Ben Aknoun</t>
-  </si>
-  <si>
-    <t>Al Jazeera</t>
-  </si>
-  <si>
-    <t>Al Hussein</t>
-  </si>
-  <si>
-    <t>Al Ramtha</t>
-  </si>
-  <si>
     <t>New Mexico United</t>
   </si>
   <si>
@@ -541,10 +541,13 @@
     <t>Qingdao Jonoon</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
     <t>Dalian Zhixing</t>
   </si>
   <si>
-    <t>Sichuan Jiuniu</t>
+    <t>Ethiopian Medhin</t>
   </si>
   <si>
     <t>Zhejiang FC</t>
@@ -553,9 +556,6 @@
     <t>Bahardar</t>
   </si>
   <si>
-    <t>Ethiopian Medhin</t>
-  </si>
-  <si>
     <t>Chennaiyin</t>
   </si>
   <si>
@@ -568,78 +568,81 @@
     <t>Septemvri Sofia</t>
   </si>
   <si>
+    <t>Slavia Praha U21</t>
+  </si>
+  <si>
+    <t>Meshakhte</t>
+  </si>
+  <si>
+    <t>Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
+  </si>
+  <si>
+    <t>Super Nova</t>
+  </si>
+  <si>
     <t>Prostějov</t>
   </si>
   <si>
-    <t>Meshakhte</t>
-  </si>
-  <si>
     <t>Vysočina Jihlava</t>
   </si>
   <si>
-    <t>Zbrojovka Brno</t>
-  </si>
-  <si>
-    <t>Slavia Praha U21</t>
-  </si>
-  <si>
     <t>Negele Arsi Ketema</t>
   </si>
   <si>
-    <t>Saburtalo</t>
-  </si>
-  <si>
-    <t>Super Nova</t>
-  </si>
-  <si>
     <t>Panevėžys</t>
   </si>
   <si>
+    <t>Chrudim</t>
+  </si>
+  <si>
+    <t>APOEL</t>
+  </si>
+  <si>
     <t>Příbram</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
     <t>Apollon</t>
   </si>
   <si>
-    <t>Opava</t>
+    <t>Viktoria Žižkov</t>
   </si>
   <si>
     <t>Ittihad Tanger</t>
   </si>
   <si>
-    <t>APOEL</t>
-  </si>
-  <si>
-    <t>Viktoria Žižkov</t>
+    <t>Raufoss</t>
   </si>
   <si>
     <t>Omonia Nicosia</t>
   </si>
   <si>
-    <t>Chrudim</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
+    <t>Beitar Jerusalem</t>
+  </si>
+  <si>
+    <t>Djurgården W</t>
   </si>
   <si>
     <t>FA Šiauliai</t>
   </si>
   <si>
-    <t>Beitar Jerusalem</t>
-  </si>
-  <si>
-    <t>Djurgården W</t>
+    <t>Levante W</t>
   </si>
   <si>
     <t>Al Ain</t>
   </si>
   <si>
-    <t>Levante W</t>
-  </si>
-  <si>
     <t>Al Nasr</t>
   </si>
   <si>
+    <t>Dinamo Batumi</t>
+  </si>
+  <si>
     <t>Hapoel Be'er Sheva</t>
   </si>
   <si>
@@ -652,21 +655,18 @@
     <t>Dobrudzha 1919</t>
   </si>
   <si>
-    <t>Dinamo Batumi</t>
+    <t>Golden Arrows</t>
+  </si>
+  <si>
+    <t>Polokwane City</t>
+  </si>
+  <si>
+    <t>TS Galaxy</t>
   </si>
   <si>
     <t>Kaizer Chiefs</t>
   </si>
   <si>
-    <t>Golden Arrows</t>
-  </si>
-  <si>
-    <t>Polokwane City</t>
-  </si>
-  <si>
-    <t>TS Galaxy</t>
-  </si>
-  <si>
     <t>CODM Meknès</t>
   </si>
   <si>
@@ -685,40 +685,40 @@
     <t>Molynes United</t>
   </si>
   <si>
+    <t>Dunbeholden</t>
+  </si>
+  <si>
+    <t>Racing United</t>
+  </si>
+  <si>
+    <t>Tivoli Gardens</t>
+  </si>
+  <si>
+    <t>Arnett Gardens</t>
+  </si>
+  <si>
+    <t>Montego Bay United</t>
+  </si>
+  <si>
     <t>Harbour View</t>
   </si>
   <si>
-    <t>Montego Bay United</t>
-  </si>
-  <si>
-    <t>Arnett Gardens</t>
-  </si>
-  <si>
-    <t>Racing United</t>
-  </si>
-  <si>
-    <t>Dunbeholden</t>
-  </si>
-  <si>
-    <t>Tivoli Gardens</t>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Al Salt</t>
+  </si>
+  <si>
+    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>Sama Al Sarhan</t>
   </si>
   <si>
+    <t>Al Faisaly</t>
+  </si>
+  <si>
     <t>LA Galaxy II</t>
-  </si>
-  <si>
-    <t>USM Alger</t>
-  </si>
-  <si>
-    <t>Al Salt</t>
-  </si>
-  <si>
-    <t>Al Faisaly</t>
-  </si>
-  <si>
-    <t>Al Buqa'a</t>
   </si>
   <si>
     <t>El Paso Locomotive</t>
@@ -1523,124 +1523,124 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="T3">
         <v>2.39</v>
       </c>
       <c r="U3">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="X3">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y3">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Z3">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA3">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC3">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AD3">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="AE3">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AF3">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AG3">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AH3">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AI3">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AJ3">
+        <v>1.16</v>
+      </c>
+      <c r="AK3">
+        <v>1.75</v>
+      </c>
+      <c r="AL3">
+        <v>1.97</v>
+      </c>
+      <c r="AM3">
+        <v>1.21</v>
+      </c>
+      <c r="AN3">
+        <v>2.41</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
         <v>1.19</v>
       </c>
-      <c r="AK3">
-        <v>1.52</v>
-      </c>
-      <c r="AL3">
-        <v>2.37</v>
-      </c>
-      <c r="AM3">
-        <v>1.23</v>
-      </c>
-      <c r="AN3">
+      <c r="AQ3">
+        <v>1.44</v>
+      </c>
+      <c r="AR3">
+        <v>1.72</v>
+      </c>
+      <c r="AS3">
         <v>2.14</v>
       </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
+      <c r="AT3">
+        <v>2.86</v>
+      </c>
+      <c r="AU3">
+        <v>3.68</v>
+      </c>
+      <c r="AV3">
+        <v>2.55</v>
+      </c>
+      <c r="AW3">
+        <v>1.97</v>
+      </c>
+      <c r="AX3">
+        <v>1.62</v>
+      </c>
+      <c r="AY3">
+        <v>1.38</v>
+      </c>
+      <c r="AZ3">
+        <v>1.32</v>
+      </c>
+      <c r="BA3">
+        <v>3.6</v>
+      </c>
+      <c r="BB3">
+        <v>1.16</v>
+      </c>
+      <c r="BC3">
+        <v>1.97</v>
+      </c>
+      <c r="BD3">
+        <v>4.3</v>
+      </c>
+      <c r="BE3">
+        <v>1.77</v>
+      </c>
+      <c r="BF3">
         <v>1.17</v>
-      </c>
-      <c r="AQ3">
-        <v>1.38</v>
-      </c>
-      <c r="AR3">
-        <v>1.68</v>
-      </c>
-      <c r="AS3">
-        <v>2.09</v>
-      </c>
-      <c r="AT3">
-        <v>2.6</v>
-      </c>
-      <c r="AU3">
-        <v>3.92</v>
-      </c>
-      <c r="AV3">
-        <v>2.7</v>
-      </c>
-      <c r="AW3">
-        <v>2.05</v>
-      </c>
-      <c r="AX3">
-        <v>1.67</v>
-      </c>
-      <c r="AY3">
-        <v>1.42</v>
-      </c>
-      <c r="AZ3">
-        <v>1.47</v>
-      </c>
-      <c r="BA3">
-        <v>2.85</v>
-      </c>
-      <c r="BB3">
-        <v>1.12</v>
-      </c>
-      <c r="BC3">
-        <v>1.73</v>
-      </c>
-      <c r="BD3">
-        <v>4.95</v>
-      </c>
-      <c r="BE3">
-        <v>1.99</v>
-      </c>
-      <c r="BF3">
-        <v>1.27</v>
       </c>
       <c r="BG3">
         <v>0</v>
@@ -1708,124 +1708,124 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="T4">
         <v>2.39</v>
       </c>
       <c r="U4">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="V4">
+        <v>1.23</v>
+      </c>
+      <c r="W4">
+        <v>3.52</v>
+      </c>
+      <c r="X4">
+        <v>2.21</v>
+      </c>
+      <c r="Y4">
+        <v>1.61</v>
+      </c>
+      <c r="Z4">
+        <v>4.8</v>
+      </c>
+      <c r="AA4">
+        <v>1.12</v>
+      </c>
+      <c r="AB4">
+        <v>1.01</v>
+      </c>
+      <c r="AC4">
+        <v>1.15</v>
+      </c>
+      <c r="AD4">
+        <v>4.8</v>
+      </c>
+      <c r="AE4">
+        <v>1.52</v>
+      </c>
+      <c r="AF4">
+        <v>2.35</v>
+      </c>
+      <c r="AG4">
+        <v>2.3</v>
+      </c>
+      <c r="AH4">
+        <v>1.61</v>
+      </c>
+      <c r="AI4">
+        <v>3.8</v>
+      </c>
+      <c r="AJ4">
+        <v>1.19</v>
+      </c>
+      <c r="AK4">
+        <v>1.52</v>
+      </c>
+      <c r="AL4">
+        <v>2.37</v>
+      </c>
+      <c r="AM4">
+        <v>1.23</v>
+      </c>
+      <c r="AN4">
+        <v>2.14</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>1.17</v>
+      </c>
+      <c r="AQ4">
+        <v>1.38</v>
+      </c>
+      <c r="AR4">
+        <v>1.68</v>
+      </c>
+      <c r="AS4">
+        <v>2.09</v>
+      </c>
+      <c r="AT4">
+        <v>2.6</v>
+      </c>
+      <c r="AU4">
+        <v>3.92</v>
+      </c>
+      <c r="AV4">
+        <v>2.7</v>
+      </c>
+      <c r="AW4">
+        <v>2.05</v>
+      </c>
+      <c r="AX4">
+        <v>1.67</v>
+      </c>
+      <c r="AY4">
+        <v>1.42</v>
+      </c>
+      <c r="AZ4">
+        <v>1.47</v>
+      </c>
+      <c r="BA4">
+        <v>2.85</v>
+      </c>
+      <c r="BB4">
+        <v>1.12</v>
+      </c>
+      <c r="BC4">
+        <v>1.73</v>
+      </c>
+      <c r="BD4">
+        <v>4.95</v>
+      </c>
+      <c r="BE4">
+        <v>1.99</v>
+      </c>
+      <c r="BF4">
         <v>1.27</v>
-      </c>
-      <c r="W4">
-        <v>3.35</v>
-      </c>
-      <c r="X4">
-        <v>2.47</v>
-      </c>
-      <c r="Y4">
-        <v>1.47</v>
-      </c>
-      <c r="Z4">
-        <v>5.9</v>
-      </c>
-      <c r="AA4">
-        <v>1.07</v>
-      </c>
-      <c r="AB4">
-        <v>1.03</v>
-      </c>
-      <c r="AC4">
-        <v>1.2</v>
-      </c>
-      <c r="AD4">
-        <v>3.98</v>
-      </c>
-      <c r="AE4">
-        <v>1.74</v>
-      </c>
-      <c r="AF4">
-        <v>2.12</v>
-      </c>
-      <c r="AG4">
-        <v>2.7</v>
-      </c>
-      <c r="AH4">
-        <v>1.43</v>
-      </c>
-      <c r="AI4">
-        <v>4.7</v>
-      </c>
-      <c r="AJ4">
-        <v>1.16</v>
-      </c>
-      <c r="AK4">
-        <v>1.75</v>
-      </c>
-      <c r="AL4">
-        <v>1.97</v>
-      </c>
-      <c r="AM4">
-        <v>1.21</v>
-      </c>
-      <c r="AN4">
-        <v>2.41</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>1.19</v>
-      </c>
-      <c r="AQ4">
-        <v>1.44</v>
-      </c>
-      <c r="AR4">
-        <v>1.72</v>
-      </c>
-      <c r="AS4">
-        <v>2.14</v>
-      </c>
-      <c r="AT4">
-        <v>2.86</v>
-      </c>
-      <c r="AU4">
-        <v>3.68</v>
-      </c>
-      <c r="AV4">
-        <v>2.55</v>
-      </c>
-      <c r="AW4">
-        <v>1.97</v>
-      </c>
-      <c r="AX4">
-        <v>1.62</v>
-      </c>
-      <c r="AY4">
-        <v>1.38</v>
-      </c>
-      <c r="AZ4">
-        <v>1.32</v>
-      </c>
-      <c r="BA4">
-        <v>3.6</v>
-      </c>
-      <c r="BB4">
-        <v>1.16</v>
-      </c>
-      <c r="BC4">
-        <v>1.97</v>
-      </c>
-      <c r="BD4">
-        <v>4.3</v>
-      </c>
-      <c r="BE4">
-        <v>1.77</v>
-      </c>
-      <c r="BF4">
-        <v>1.17</v>
       </c>
       <c r="BG4">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>113</v>
@@ -1884,133 +1884,133 @@
         <v>237</v>
       </c>
       <c r="P5">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL5">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AO5">
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR5">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT5">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU5">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="AV5">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW5">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY5">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ5">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BE5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG5">
         <v>0</v>
@@ -2030,10 +2030,10 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
         <v>114</v>
@@ -2069,133 +2069,133 @@
         <v>237</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AO6">
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG6">
         <v>0</v>
@@ -2633,70 +2633,70 @@
         <v>0</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AO9">
         <v>0</v>
@@ -2738,19 +2738,19 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG9">
         <v>0</v>
@@ -3188,70 +3188,70 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="U12">
+        <v>2.95</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>2.43</v>
+      </c>
+      <c r="Y12">
+        <v>1.43</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>1.22</v>
+      </c>
+      <c r="AD12">
         <v>3.6</v>
       </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>2.55</v>
-      </c>
-      <c r="Y12">
-        <v>1.38</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>1.25</v>
-      </c>
-      <c r="AD12">
-        <v>3.35</v>
-      </c>
       <c r="AE12">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF12">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG12">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AH12">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI12">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AJ12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK12">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AL12">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AM12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AN12">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3296,13 +3296,13 @@
         <v>0</v>
       </c>
       <c r="BC12">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BD12">
         <v>0</v>
       </c>
       <c r="BE12">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="BF12">
         <v>0</v>
@@ -3558,13 +3558,13 @@
         <v>0</v>
       </c>
       <c r="S14">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3588,40 +3588,40 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>0</v>
@@ -3666,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD14">
         <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF14">
         <v>0</v>
@@ -3695,10 +3695,10 @@
         <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>123</v>
@@ -3880,10 +3880,10 @@
         <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>124</v>
@@ -3919,34 +3919,34 @@
         <v>237</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="T16">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U16">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X16">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3958,40 +3958,40 @@
         <v>0</v>
       </c>
       <c r="AC16">
+        <v>1.33</v>
+      </c>
+      <c r="AD16">
+        <v>2.88</v>
+      </c>
+      <c r="AE16">
+        <v>2.06</v>
+      </c>
+      <c r="AF16">
+        <v>1.63</v>
+      </c>
+      <c r="AG16">
+        <v>3.6</v>
+      </c>
+      <c r="AH16">
         <v>1.22</v>
       </c>
-      <c r="AD16">
-        <v>3.6</v>
-      </c>
-      <c r="AE16">
-        <v>1.72</v>
-      </c>
-      <c r="AF16">
-        <v>1.93</v>
-      </c>
-      <c r="AG16">
-        <v>2.75</v>
-      </c>
-      <c r="AH16">
-        <v>1.35</v>
-      </c>
       <c r="AI16">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL16">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AM16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN16">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AO16">
         <v>0</v>
@@ -4036,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="BD16">
         <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF16">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
@@ -4113,13 +4113,13 @@
         <v>0</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4128,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -4143,40 +4143,40 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO17">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         <v>0</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD17">
         <v>0</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF17">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>126</v>
@@ -4298,13 +4298,13 @@
         <v>0</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -4313,10 +4313,10 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -4328,40 +4328,40 @@
         <v>0</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO18">
         <v>0</v>
@@ -4406,13 +4406,13 @@
         <v>0</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD18">
         <v>0</v>
       </c>
       <c r="BE18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF18">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
         <v>127</v>
@@ -4474,28 +4474,28 @@
         <v>237</v>
       </c>
       <c r="P19">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X19">
         <v>0</v>
@@ -4513,22 +4513,22 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AH19">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -4537,16 +4537,16 @@
         <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL19">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <v>0</v>
@@ -4591,13 +4591,13 @@
         <v>0</v>
       </c>
       <c r="BC19">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF19">
         <v>0</v>
@@ -4853,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -4868,10 +4868,10 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4883,40 +4883,40 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO21">
         <v>0</v>
@@ -4961,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF21">
         <v>0</v>
@@ -5029,79 +5029,79 @@
         <v>237</v>
       </c>
       <c r="P22">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="T22">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="U22">
-        <v>4.27</v>
+        <v>2.99</v>
       </c>
       <c r="V22">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="X22">
-        <v>3.22</v>
+        <v>2.72</v>
       </c>
       <c r="Y22">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="Z22">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB22">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC22">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AD22">
-        <v>2.62</v>
+        <v>3.68</v>
       </c>
       <c r="AE22">
-        <v>2.29</v>
+        <v>1.76</v>
       </c>
       <c r="AF22">
+        <v>2.02</v>
+      </c>
+      <c r="AG22">
+        <v>2.7</v>
+      </c>
+      <c r="AH22">
+        <v>1.36</v>
+      </c>
+      <c r="AI22">
+        <v>5.12</v>
+      </c>
+      <c r="AJ22">
+        <v>1.11</v>
+      </c>
+      <c r="AK22">
         <v>1.59</v>
       </c>
-      <c r="AG22">
-        <v>3.98</v>
-      </c>
-      <c r="AH22">
-        <v>1.17</v>
-      </c>
-      <c r="AI22">
-        <v>8</v>
-      </c>
-      <c r="AJ22">
-        <v>1.02</v>
-      </c>
-      <c r="AK22">
-        <v>1.93</v>
-      </c>
       <c r="AL22">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="AM22">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AN22">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AO22">
         <v>0</v>
@@ -5143,19 +5143,19 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BC22">
-        <v>2.39</v>
+        <v>1.98</v>
       </c>
       <c r="BD22">
-        <v>3.16</v>
+        <v>4.3</v>
       </c>
       <c r="BE22">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="BF22">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="BG22">
         <v>0</v>
@@ -5223,13 +5223,13 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y23">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -5253,40 +5253,40 @@
         <v>0</v>
       </c>
       <c r="AC23">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD23">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK23">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL23">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
@@ -5331,13 +5331,13 @@
         <v>0</v>
       </c>
       <c r="BC23">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF23">
         <v>0</v>
@@ -5360,7 +5360,7 @@
         <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
         <v>109</v>
@@ -5408,13 +5408,13 @@
         <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -5423,10 +5423,10 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -5438,40 +5438,40 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO24">
         <v>0</v>
@@ -5516,13 +5516,13 @@
         <v>0</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF24">
         <v>0</v>
@@ -5584,133 +5584,133 @@
         <v>237</v>
       </c>
       <c r="P25">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q25">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="S25">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="T25">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="U25">
-        <v>2.99</v>
+        <v>4.27</v>
       </c>
       <c r="V25">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="W25">
-        <v>3.05</v>
+        <v>2.34</v>
       </c>
       <c r="X25">
-        <v>2.72</v>
+        <v>3.22</v>
       </c>
       <c r="Y25">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="AA25">
+        <v>1.03</v>
+      </c>
+      <c r="AB25">
+        <v>1.05</v>
+      </c>
+      <c r="AC25">
+        <v>1.38</v>
+      </c>
+      <c r="AD25">
+        <v>2.62</v>
+      </c>
+      <c r="AE25">
+        <v>2.29</v>
+      </c>
+      <c r="AF25">
+        <v>1.59</v>
+      </c>
+      <c r="AG25">
+        <v>3.98</v>
+      </c>
+      <c r="AH25">
+        <v>1.17</v>
+      </c>
+      <c r="AI25">
+        <v>8</v>
+      </c>
+      <c r="AJ25">
+        <v>1.02</v>
+      </c>
+      <c r="AK25">
+        <v>1.93</v>
+      </c>
+      <c r="AL25">
+        <v>1.78</v>
+      </c>
+      <c r="AM25">
+        <v>1.36</v>
+      </c>
+      <c r="AN25">
+        <v>1.62</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>0</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>1.3</v>
+      </c>
+      <c r="BC25">
+        <v>2.39</v>
+      </c>
+      <c r="BD25">
+        <v>3.16</v>
+      </c>
+      <c r="BE25">
+        <v>1.5</v>
+      </c>
+      <c r="BF25">
         <v>1.09</v>
-      </c>
-      <c r="AB25">
-        <v>1.01</v>
-      </c>
-      <c r="AC25">
-        <v>1.22</v>
-      </c>
-      <c r="AD25">
-        <v>3.68</v>
-      </c>
-      <c r="AE25">
-        <v>1.76</v>
-      </c>
-      <c r="AF25">
-        <v>2.02</v>
-      </c>
-      <c r="AG25">
-        <v>2.7</v>
-      </c>
-      <c r="AH25">
-        <v>1.36</v>
-      </c>
-      <c r="AI25">
-        <v>5.12</v>
-      </c>
-      <c r="AJ25">
-        <v>1.11</v>
-      </c>
-      <c r="AK25">
-        <v>1.59</v>
-      </c>
-      <c r="AL25">
-        <v>2.21</v>
-      </c>
-      <c r="AM25">
-        <v>1.27</v>
-      </c>
-      <c r="AN25">
-        <v>1.45</v>
-      </c>
-      <c r="AO25">
-        <v>0</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.18</v>
-      </c>
-      <c r="BC25">
-        <v>1.98</v>
-      </c>
-      <c r="BD25">
-        <v>4.3</v>
-      </c>
-      <c r="BE25">
-        <v>1.76</v>
-      </c>
-      <c r="BF25">
-        <v>1.2</v>
       </c>
       <c r="BG25">
         <v>0</v>
@@ -5915,7 +5915,7 @@
         <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" t="s">
         <v>109</v>
@@ -5954,79 +5954,79 @@
         <v>237</v>
       </c>
       <c r="P27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AO27">
         <v>0</v>
@@ -6068,19 +6068,19 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG27">
         <v>0</v>
@@ -6100,10 +6100,10 @@
         <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>136</v>
@@ -6139,133 +6139,133 @@
         <v>237</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S28">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="T28">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="U28">
-        <v>4.8</v>
+        <v>5.47</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X28">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Y28">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AD28">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="AE28">
         <v>1.54</v>
       </c>
       <c r="AF28">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AG28">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AH28">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AI28">
-        <v>4</v>
+        <v>3.74</v>
       </c>
       <c r="AJ28">
+        <v>1.23</v>
+      </c>
+      <c r="AK28">
+        <v>1.63</v>
+      </c>
+      <c r="AL28">
+        <v>2.14</v>
+      </c>
+      <c r="AM28">
         <v>1.18</v>
       </c>
-      <c r="AK28">
-        <v>1.62</v>
-      </c>
-      <c r="AL28">
-        <v>2.12</v>
-      </c>
-      <c r="AM28">
-        <v>1.16</v>
-      </c>
       <c r="AN28">
-        <v>2.12</v>
+        <v>2.49</v>
       </c>
       <c r="AO28">
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC28">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE28">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG28">
         <v>0</v>
@@ -6285,10 +6285,10 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E29" t="s">
         <v>137</v>
@@ -6324,133 +6324,133 @@
         <v>237</v>
       </c>
       <c r="P29">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q29">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="R29">
-        <v>4.99</v>
+        <v>4</v>
       </c>
       <c r="S29">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="T29">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="U29">
-        <v>5.47</v>
+        <v>4.7</v>
       </c>
       <c r="V29">
+        <v>1.3</v>
+      </c>
+      <c r="W29">
+        <v>3.16</v>
+      </c>
+      <c r="X29">
+        <v>2.54</v>
+      </c>
+      <c r="Y29">
+        <v>1.49</v>
+      </c>
+      <c r="Z29">
+        <v>5.7</v>
+      </c>
+      <c r="AA29">
+        <v>1.09</v>
+      </c>
+      <c r="AB29">
+        <v>1.03</v>
+      </c>
+      <c r="AC29">
+        <v>1.17</v>
+      </c>
+      <c r="AD29">
+        <v>4</v>
+      </c>
+      <c r="AE29">
+        <v>1.7</v>
+      </c>
+      <c r="AF29">
+        <v>2.09</v>
+      </c>
+      <c r="AG29">
+        <v>2.62</v>
+      </c>
+      <c r="AH29">
+        <v>1.38</v>
+      </c>
+      <c r="AI29">
+        <v>4.92</v>
+      </c>
+      <c r="AJ29">
+        <v>1.11</v>
+      </c>
+      <c r="AK29">
+        <v>1.64</v>
+      </c>
+      <c r="AL29">
+        <v>2.13</v>
+      </c>
+      <c r="AM29">
         <v>1.24</v>
       </c>
-      <c r="W29">
-        <v>3.44</v>
-      </c>
-      <c r="X29">
-        <v>2.21</v>
-      </c>
-      <c r="Y29">
-        <v>1.61</v>
-      </c>
-      <c r="Z29">
-        <v>4.7</v>
-      </c>
-      <c r="AA29">
-        <v>1.13</v>
-      </c>
-      <c r="AB29">
-        <v>1.01</v>
-      </c>
-      <c r="AC29">
-        <v>1.2</v>
-      </c>
-      <c r="AD29">
-        <v>4.65</v>
-      </c>
-      <c r="AE29">
-        <v>1.54</v>
-      </c>
-      <c r="AF29">
-        <v>2.33</v>
-      </c>
-      <c r="AG29">
-        <v>2.31</v>
-      </c>
-      <c r="AH29">
-        <v>1.58</v>
-      </c>
-      <c r="AI29">
-        <v>3.74</v>
-      </c>
-      <c r="AJ29">
-        <v>1.23</v>
-      </c>
-      <c r="AK29">
-        <v>1.63</v>
-      </c>
-      <c r="AL29">
-        <v>2.14</v>
-      </c>
-      <c r="AM29">
+      <c r="AN29">
+        <v>1.99</v>
+      </c>
+      <c r="AO29">
+        <v>0</v>
+      </c>
+      <c r="AP29">
+        <v>0</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29">
+        <v>0</v>
+      </c>
+      <c r="AV29">
+        <v>0</v>
+      </c>
+      <c r="AW29">
+        <v>0</v>
+      </c>
+      <c r="AX29">
+        <v>0</v>
+      </c>
+      <c r="AY29">
+        <v>0</v>
+      </c>
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+      <c r="BA29">
+        <v>0</v>
+      </c>
+      <c r="BB29">
         <v>1.18</v>
       </c>
-      <c r="AN29">
-        <v>2.49</v>
-      </c>
-      <c r="AO29">
-        <v>0</v>
-      </c>
-      <c r="AP29">
-        <v>1.08</v>
-      </c>
-      <c r="AQ29">
-        <v>1.42</v>
-      </c>
-      <c r="AR29">
-        <v>1.46</v>
-      </c>
-      <c r="AS29">
-        <v>2.08</v>
-      </c>
-      <c r="AT29">
-        <v>2.63</v>
-      </c>
-      <c r="AU29">
-        <v>5.27</v>
-      </c>
-      <c r="AV29">
-        <v>2.63</v>
-      </c>
-      <c r="AW29">
-        <v>2.02</v>
-      </c>
-      <c r="AX29">
-        <v>1.93</v>
-      </c>
-      <c r="AY29">
-        <v>1.42</v>
-      </c>
-      <c r="AZ29">
-        <v>1.24</v>
-      </c>
-      <c r="BA29">
-        <v>2.88</v>
-      </c>
-      <c r="BB29">
-        <v>1.13</v>
-      </c>
       <c r="BC29">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="BD29">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="BE29">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="BF29">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="BG29">
         <v>0</v>
@@ -6470,10 +6470,10 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E30" t="s">
         <v>138</v>
@@ -6509,133 +6509,133 @@
         <v>237</v>
       </c>
       <c r="P30">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="R30">
-        <v>7.38</v>
+        <v>2.2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO30">
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG30">
         <v>0</v>
@@ -6655,10 +6655,10 @@
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E31" t="s">
         <v>139</v>
@@ -6694,133 +6694,133 @@
         <v>237</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>3.44</v>
+        <v>1.58</v>
       </c>
       <c r="T31">
-        <v>2.13</v>
+        <v>2.88</v>
       </c>
       <c r="U31">
-        <v>2.85</v>
+        <v>7.5</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="Y31">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="Z31">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AD31">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AE31">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AF31">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AG31">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AH31">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI31">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="AJ31">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AL31">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AN31">
-        <v>1.37</v>
+        <v>3.3</v>
       </c>
       <c r="AO31">
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>1.87</v>
+        <v>1.63</v>
       </c>
       <c r="BD31">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="BF31">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG31">
         <v>0</v>
@@ -6840,7 +6840,7 @@
         <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
         <v>108</v>
@@ -6879,22 +6879,22 @@
         <v>237</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="S32">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V32">
         <v>0</v>
@@ -6903,10 +6903,10 @@
         <v>0</v>
       </c>
       <c r="X32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -6918,40 +6918,40 @@
         <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>0</v>
@@ -6996,13 +6996,13 @@
         <v>0</v>
       </c>
       <c r="BC32">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD32">
         <v>0</v>
       </c>
       <c r="BE32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32">
         <v>0</v>
@@ -7025,7 +7025,7 @@
         <v>71</v>
       </c>
       <c r="C33" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
         <v>109</v>
@@ -7210,7 +7210,7 @@
         <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
         <v>109</v>
@@ -7580,10 +7580,10 @@
         <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
         <v>144</v>
@@ -7619,133 +7619,133 @@
         <v>237</v>
       </c>
       <c r="P36">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH36">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI36">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL36">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AM36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO36">
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ36">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR36">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AS36">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="AT36">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AU36">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AV36">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW36">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AX36">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY36">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ36">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BA36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC36">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD36">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="BE36">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF36">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG36">
         <v>0</v>
@@ -7765,10 +7765,10 @@
         <v>72</v>
       </c>
       <c r="C37" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
         <v>145</v>
@@ -7804,133 +7804,133 @@
         <v>237</v>
       </c>
       <c r="P37">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R37">
-        <v>2.49</v>
+        <v>1.75</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC37">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AD37">
-        <v>3.45</v>
+        <v>4.95</v>
       </c>
       <c r="AE37">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AF37">
-        <v>1.87</v>
+        <v>2.41</v>
       </c>
       <c r="AG37">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="AH37">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="AI37">
-        <v>5.1</v>
+        <v>3.69</v>
       </c>
       <c r="AJ37">
+        <v>1.21</v>
+      </c>
+      <c r="AK37">
+        <v>1.47</v>
+      </c>
+      <c r="AL37">
+        <v>2.48</v>
+      </c>
+      <c r="AM37">
+        <v>1.22</v>
+      </c>
+      <c r="AN37">
+        <v>1.22</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>1.27</v>
+      </c>
+      <c r="AQ37">
+        <v>1.54</v>
+      </c>
+      <c r="AR37">
+        <v>2.19</v>
+      </c>
+      <c r="AS37">
+        <v>2.44</v>
+      </c>
+      <c r="AT37">
+        <v>3.33</v>
+      </c>
+      <c r="AU37">
+        <v>3.16</v>
+      </c>
+      <c r="AV37">
+        <v>2.28</v>
+      </c>
+      <c r="AW37">
+        <v>1.8</v>
+      </c>
+      <c r="AX37">
+        <v>1.47</v>
+      </c>
+      <c r="AY37">
+        <v>1.24</v>
+      </c>
+      <c r="AZ37">
+        <v>2.16</v>
+      </c>
+      <c r="BA37">
+        <v>2.05</v>
+      </c>
+      <c r="BB37">
         <v>1.11</v>
       </c>
-      <c r="AK37">
-        <v>1.63</v>
-      </c>
-      <c r="AL37">
-        <v>2.1</v>
-      </c>
-      <c r="AM37">
-        <v>1.23</v>
-      </c>
-      <c r="AN37">
-        <v>1.32</v>
-      </c>
-      <c r="AO37">
-        <v>0</v>
-      </c>
-      <c r="AP37">
-        <v>0</v>
-      </c>
-      <c r="AQ37">
-        <v>0</v>
-      </c>
-      <c r="AR37">
-        <v>0</v>
-      </c>
-      <c r="AS37">
-        <v>0</v>
-      </c>
-      <c r="AT37">
-        <v>0</v>
-      </c>
-      <c r="AU37">
-        <v>0</v>
-      </c>
-      <c r="AV37">
-        <v>0</v>
-      </c>
-      <c r="AW37">
-        <v>0</v>
-      </c>
-      <c r="AX37">
-        <v>0</v>
-      </c>
-      <c r="AY37">
-        <v>0</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>0</v>
-      </c>
       <c r="BC37">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD37">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="BE37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG37">
         <v>0</v>
@@ -7950,7 +7950,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
         <v>108</v>
@@ -7989,13 +7989,13 @@
         <v>237</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -8028,40 +8028,40 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO38">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E39" t="s">
         <v>147</v>
@@ -8174,133 +8174,133 @@
         <v>237</v>
       </c>
       <c r="P39">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AO39">
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR39">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT39">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU39">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV39">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW39">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX39">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY39">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ39">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA39">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC39">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="BD39">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BE39">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF39">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG39">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>72</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E40" t="s">
         <v>148</v>
@@ -8359,133 +8359,133 @@
         <v>237</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO40">
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG40">
         <v>0</v>
@@ -8544,118 +8544,118 @@
         <v>237</v>
       </c>
       <c r="P41">
-        <v>1.44</v>
+        <v>1.95</v>
       </c>
       <c r="Q41">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R41">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="S41">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="T41">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="U41">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="X41">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA41">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC41">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AD41">
         <v>2.66</v>
       </c>
       <c r="AE41">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AF41">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AH41">
         <v>1.16</v>
       </c>
       <c r="AI41">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AJ41">
         <v>1.01</v>
       </c>
       <c r="AK41">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AL41">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AM41">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AN41">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="AO41">
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AQ41">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AR41">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="AS41">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU41">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AV41">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AW41">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AX41">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ41">
-        <v>1.28</v>
+        <v>1.79</v>
       </c>
       <c r="BA41">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="BB41">
         <v>1.28</v>
@@ -8664,13 +8664,13 @@
         <v>2.41</v>
       </c>
       <c r="BD41">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="BE41">
         <v>1.47</v>
       </c>
       <c r="BF41">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BG41">
         <v>0</v>
@@ -8729,133 +8729,133 @@
         <v>237</v>
       </c>
       <c r="P42">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="Q42">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R42">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="S42">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="T42">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U42">
-        <v>4</v>
+        <v>4.39</v>
       </c>
       <c r="V42">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="X42">
+        <v>4.2</v>
+      </c>
+      <c r="Y42">
+        <v>1.15</v>
+      </c>
+      <c r="Z42">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA42">
+        <v>1.01</v>
+      </c>
+      <c r="AB42">
+        <v>1.08</v>
+      </c>
+      <c r="AC42">
+        <v>1.66</v>
+      </c>
+      <c r="AD42">
+        <v>2.09</v>
+      </c>
+      <c r="AE42">
+        <v>3.04</v>
+      </c>
+      <c r="AF42">
+        <v>1.29</v>
+      </c>
+      <c r="AG42">
+        <v>6.75</v>
+      </c>
+      <c r="AH42">
+        <v>1.04</v>
+      </c>
+      <c r="AI42">
+        <v>11</v>
+      </c>
+      <c r="AJ42">
+        <v>1.02</v>
+      </c>
+      <c r="AK42">
+        <v>2.4</v>
+      </c>
+      <c r="AL42">
+        <v>1.5</v>
+      </c>
+      <c r="AM42">
+        <v>1.33</v>
+      </c>
+      <c r="AN42">
+        <v>1.5</v>
+      </c>
+      <c r="AO42">
+        <v>0</v>
+      </c>
+      <c r="AP42">
+        <v>1.34</v>
+      </c>
+      <c r="AQ42">
+        <v>1.58</v>
+      </c>
+      <c r="AR42">
+        <v>1.94</v>
+      </c>
+      <c r="AS42">
+        <v>2.48</v>
+      </c>
+      <c r="AT42">
         <v>3.25</v>
       </c>
-      <c r="Y42">
-        <v>1.27</v>
-      </c>
-      <c r="Z42">
-        <v>9</v>
-      </c>
-      <c r="AA42">
-        <v>1</v>
-      </c>
-      <c r="AB42">
-        <v>1.04</v>
-      </c>
-      <c r="AC42">
-        <v>1.42</v>
-      </c>
-      <c r="AD42">
-        <v>2.66</v>
-      </c>
-      <c r="AE42">
-        <v>2.27</v>
-      </c>
-      <c r="AF42">
-        <v>1.56</v>
-      </c>
-      <c r="AG42">
-        <v>4.15</v>
-      </c>
-      <c r="AH42">
-        <v>1.16</v>
-      </c>
-      <c r="AI42">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AJ42">
+      <c r="AU42">
+        <v>2.95</v>
+      </c>
+      <c r="AV42">
+        <v>2.2</v>
+      </c>
+      <c r="AW42">
+        <v>1.75</v>
+      </c>
+      <c r="AX42">
+        <v>1.47</v>
+      </c>
+      <c r="AY42">
+        <v>1.29</v>
+      </c>
+      <c r="AZ42">
+        <v>1.8</v>
+      </c>
+      <c r="BA42">
+        <v>2.18</v>
+      </c>
+      <c r="BB42">
+        <v>1.43</v>
+      </c>
+      <c r="BC42">
+        <v>3.18</v>
+      </c>
+      <c r="BD42">
+        <v>2.53</v>
+      </c>
+      <c r="BE42">
+        <v>1.28</v>
+      </c>
+      <c r="BF42">
         <v>1.01</v>
-      </c>
-      <c r="AK42">
-        <v>1.95</v>
-      </c>
-      <c r="AL42">
-        <v>1.73</v>
-      </c>
-      <c r="AM42">
-        <v>1.3</v>
-      </c>
-      <c r="AN42">
-        <v>1.68</v>
-      </c>
-      <c r="AO42">
-        <v>0</v>
-      </c>
-      <c r="AP42">
-        <v>1.27</v>
-      </c>
-      <c r="AQ42">
-        <v>1.47</v>
-      </c>
-      <c r="AR42">
-        <v>1.77</v>
-      </c>
-      <c r="AS42">
-        <v>2.2</v>
-      </c>
-      <c r="AT42">
-        <v>2.85</v>
-      </c>
-      <c r="AU42">
-        <v>3.3</v>
-      </c>
-      <c r="AV42">
-        <v>2.45</v>
-      </c>
-      <c r="AW42">
-        <v>1.92</v>
-      </c>
-      <c r="AX42">
-        <v>1.58</v>
-      </c>
-      <c r="AY42">
-        <v>1.36</v>
-      </c>
-      <c r="AZ42">
-        <v>1.79</v>
-      </c>
-      <c r="BA42">
-        <v>2.16</v>
-      </c>
-      <c r="BB42">
-        <v>1.28</v>
-      </c>
-      <c r="BC42">
-        <v>2.41</v>
-      </c>
-      <c r="BD42">
-        <v>3.18</v>
-      </c>
-      <c r="BE42">
-        <v>1.47</v>
-      </c>
-      <c r="BF42">
-        <v>1.07</v>
       </c>
       <c r="BG42">
         <v>0</v>
@@ -8914,133 +8914,133 @@
         <v>237</v>
       </c>
       <c r="P43">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="Q43">
+        <v>2.95</v>
+      </c>
+      <c r="R43">
         <v>2.75</v>
       </c>
-      <c r="R43">
-        <v>3.1</v>
-      </c>
       <c r="S43">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="U43">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W43">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X43">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z43">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB43">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC43">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AD43">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AE43">
-        <v>3.04</v>
+        <v>2.62</v>
       </c>
       <c r="AF43">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AH43">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ43">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK43">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM43">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN43">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO43">
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ43">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR43">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS43">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT43">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU43">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV43">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW43">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AX43">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY43">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ43">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BA43">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB43">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BC43">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD43">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="BE43">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG43">
         <v>0</v>
@@ -9099,133 +9099,133 @@
         <v>237</v>
       </c>
       <c r="P44">
-        <v>2.53</v>
+        <v>1.44</v>
       </c>
       <c r="Q44">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="R44">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE44">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO44">
         <v>0</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT44">
         <v>0</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY44">
         <v>0</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG44">
         <v>0</v>
@@ -11501,7 +11501,7 @@
         <v>-1</v>
       </c>
       <c r="O57" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D58" t="s">
         <v>109</v>
@@ -11659,7 +11659,7 @@
         <v>166</v>
       </c>
       <c r="F58" t="s">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -11838,13 +11838,13 @@
         <v>104</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
         <v>167</v>
       </c>
       <c r="F59" t="s">
-        <v>230</v>
+        <v>154</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12020,7 +12020,7 @@
         <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D60" t="s">
         <v>109</v>
@@ -12056,7 +12056,7 @@
         <v>-1</v>
       </c>
       <c r="O60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P60">
         <v>0</v>
@@ -12205,7 +12205,7 @@
         <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -12390,7 +12390,7 @@
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D62" t="s">
         <v>109</v>
@@ -12575,10 +12575,10 @@
         <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
         <v>171</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>5.13</v>
+        <v>4.2</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="X3" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="BD3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2</v>
+        <v>5.13</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
         <v>1.03</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>5.74</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.75</v>
       </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.31</v>
+        <v>5.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="X8" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI8" t="n">
-        <v>6.65</v>
+        <v>5.45</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
         <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>4.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U9" t="n">
-        <v>5.5</v>
+        <v>2.31</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI9" t="n">
-        <v>5.45</v>
+        <v>6.65</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AM9" t="n">
         <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.4</v>
+        <v>1.21</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,22 +2574,22 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
         <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="S11" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
         <v>1.41</v>
@@ -2613,16 +2613,16 @@
         <v>1.02</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
         <v>3.6</v>
@@ -2631,7 +2631,7 @@
         <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>1.08</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2780,13 +2780,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2977,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,10 +2992,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -3007,40 +3007,40 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,28 +3165,28 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -3204,22 +3204,22 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -3228,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,35 +3559,35 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.38</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
@@ -3598,91 +3598,91 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.52</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,13 +3765,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
         <v>1.23</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3962,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3977,10 +3977,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL21" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH21" t="n">
+      <c r="AM21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.17</v>
       </c>
-      <c r="AI21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC21" t="n">
-        <v>2.39</v>
+        <v>1.76</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.16</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL22" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AM22" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI24" t="n">
         <v>4</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.92</v>
-      </c>
       <c r="AJ24" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X26" t="n">
-        <v>2.17</v>
+        <v>2.72</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK26" t="n">
         <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S27" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="T27" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="U27" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X27" t="n">
-        <v>2.15</v>
+        <v>3.16</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AE27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5.47</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.75</v>
+        <v>1.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="S30" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.35</v>
+        <v>2.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>3.09</v>
       </c>
       <c r="R37" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC37" t="n">
         <v>2.38</v>
       </c>
-      <c r="U37" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA37" t="n">
+      <c r="BD37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BF37" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="S40" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="T40" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="U40" t="n">
-        <v>2.8</v>
+        <v>2.19</v>
       </c>
       <c r="V40" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="W40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF40" t="n">
         <v>2.5</v>
       </c>
-      <c r="X40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG40" t="n">
-        <v>3.86</v>
+        <v>2.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.9</v>
+        <v>3.28</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AW40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC40" t="n">
         <v>1.73</v>
       </c>
-      <c r="AX40" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY40" t="n">
+      <c r="BD40" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BF40" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,37 +8484,37 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R41" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>4.39</v>
+        <v>7.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="W41" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="X41" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA41" t="n">
         <v>1.01</v>
@@ -8523,94 +8523,94 @@
         <v>1.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="AE41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BD41" t="n">
         <v>2.9</v>
       </c>
-      <c r="AF41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB41" t="n">
+      <c r="BE41" t="n">
         <v>1.44</v>
       </c>
-      <c r="BC41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF41" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R42" t="n">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="S42" t="n">
         <v>3.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U42" t="n">
-        <v>3.5</v>
+        <v>4.34</v>
       </c>
       <c r="V42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL42" t="n">
         <v>1.53</v>
       </c>
-      <c r="W42" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE42" t="n">
+      <c r="AM42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BE42" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8878,22 +8878,22 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="S43" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T43" t="n">
         <v>2.05</v>
       </c>
       <c r="U43" t="n">
-        <v>4.92</v>
+        <v>4.81</v>
       </c>
       <c r="V43" t="n">
         <v>1.48</v>
@@ -8902,40 +8902,40 @@
         <v>2.38</v>
       </c>
       <c r="X43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AA43" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB43" t="n">
         <v>1.08</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG43" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI43" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ43" t="n">
         <v>1.05</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.42</v>
+        <v>2.41</v>
       </c>
       <c r="Q44" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT44" t="n">
         <v>3.75</v>
       </c>
-      <c r="R44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X44" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF44" t="n">
+      <c r="AU44" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW44" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG44" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AX44" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="BA44" t="n">
-        <v>3.95</v>
+        <v>2.23</v>
       </c>
       <c r="BB44" t="n">
         <v>1.36</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.92</v>
+        <v>6.69</v>
       </c>
       <c r="R46" t="n">
-        <v>8.550000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="S46" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="T46" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="U46" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="X46" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB46" t="n">
         <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AN46" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9553,7 +9553,7 @@
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS46" t="n">
         <v>0</v>
@@ -9568,7 +9568,7 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
@@ -9577,25 +9577,25 @@
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,137 +9662,137 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>2.83</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="R47" t="n">
-        <v>1.3</v>
+        <v>2.01</v>
       </c>
       <c r="S47" t="n">
-        <v>7.06</v>
+        <v>3.2</v>
       </c>
       <c r="T47" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="U47" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="V47" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI47" t="n">
         <v>4</v>
       </c>
-      <c r="X47" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA47" t="n">
+      <c r="AJ47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
         <v>1.17</v>
       </c>
-      <c r="AB47" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BC47" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,137 +9859,137 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R3" t="n">
-        <v>4.2</v>
+        <v>5.13</v>
       </c>
       <c r="S3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF3" t="n">
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>5.74</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.75</v>
       </c>
-      <c r="BD3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>5.13</v>
+        <v>4.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB4" t="n">
         <v>1.03</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AJ4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AQ4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="BD4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>4.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>4.65</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.31</v>
+        <v>5.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI9" t="n">
-        <v>6.65</v>
+        <v>5.45</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM9" t="n">
         <v>1.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,34 +3165,34 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U15" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3413,16 +3413,16 @@
         <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH15" t="n">
         <v>1.35</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK15" t="n">
         <v>1.58</v>
@@ -3431,10 +3431,10 @@
         <v>2.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,34 +3953,34 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3992,40 +3992,40 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AI18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,13 +4070,13 @@
         <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="R21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U21" t="n">
-        <v>5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
         <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X24" t="n">
-        <v>2.17</v>
+        <v>3.16</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.25</v>
+        <v>2.75</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.33</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="AI24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,80 +5529,80 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD26" t="n">
         <v>3.4</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AE26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.46</v>
       </c>
-      <c r="Z26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R27" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF27" t="n">
         <v>2.05</v>
       </c>
-      <c r="U27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="AG27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z27" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="AN27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD27" t="n">
         <v>4</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="BE27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5932,13 +5932,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5947,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.35</v>
       </c>
-      <c r="Q30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.59</v>
+        <v>1.58</v>
       </c>
       <c r="T31" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="U31" t="n">
-        <v>2.73</v>
+        <v>7.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AD31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.34</v>
+        <v>3.3</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="R36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC36" t="n">
         <v>2.38</v>
       </c>
-      <c r="S36" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.03</v>
-      </c>
       <c r="BD36" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="Q40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD40" t="n">
         <v>3.9</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W40" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>5.05</v>
-      </c>
       <c r="BE40" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R41" t="n">
-        <v>6.7</v>
+        <v>3.1</v>
       </c>
       <c r="S41" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U41" t="n">
-        <v>7.5</v>
+        <v>4.34</v>
       </c>
       <c r="V41" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="W41" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="X41" t="n">
-        <v>3.18</v>
+        <v>3.85</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA41" t="n">
         <v>1.01</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AI41" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF41" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.38</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R42" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="T42" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>4.34</v>
+        <v>7.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="W42" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="X42" t="n">
-        <v>3.85</v>
+        <v>3.18</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA42" t="n">
         <v>1.01</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="AE42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BD42" t="n">
         <v>2.9</v>
       </c>
-      <c r="AF42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB42" t="n">
+      <c r="BE42" t="n">
         <v>1.44</v>
       </c>
-      <c r="BC42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF42" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="S43" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="T43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK43" t="n">
         <v>2.05</v>
       </c>
-      <c r="U43" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W43" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AL43" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
         <v>1.36</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AR43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ43" t="n">
         <v>1.77</v>
       </c>
-      <c r="AS43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY43" t="n">
+      <c r="BA43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB43" t="n">
         <v>1.36</v>
       </c>
-      <c r="AZ43" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC43" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="BD43" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="S44" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="T44" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="U44" t="n">
-        <v>3.5</v>
+        <v>4.81</v>
       </c>
       <c r="V44" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="W44" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="X44" t="n">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG44" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI44" t="n">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AM44" t="n">
         <v>1.36</v>
       </c>
       <c r="AN44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE44" t="n">
         <v>1.44</v>
       </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BF44" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.69</v>
+        <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>10.7</v>
+        <v>8.5</v>
       </c>
       <c r="S46" t="n">
         <v>1.67</v>
@@ -9484,13 +9484,13 @@
         <v>2.63</v>
       </c>
       <c r="U46" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="V46" t="n">
         <v>1.15</v>
       </c>
       <c r="W46" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="X46" t="n">
         <v>1.99</v>
@@ -9514,28 +9514,28 @@
         <v>5.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AF46" t="n">
         <v>2.7</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="n">
         <v>1.67</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AJ46" t="n">
         <v>1.29</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AM46" t="n">
         <v>1.11</v>
@@ -9547,52 +9547,52 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ46" t="n">
         <v>1.33</v>
       </c>
       <c r="BA46" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB46" t="n">
         <v>1.14</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BD46" t="n">
         <v>4.8</v>
       </c>
       <c r="BE46" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BF46" t="n">
         <v>1.3</v>
@@ -10060,40 +10060,40 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="S49" t="n">
         <v>2.09</v>
       </c>
       <c r="T49" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="U49" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="V49" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W49" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="X49" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB49" t="n">
         <v>1.01</v>
@@ -10105,88 +10105,88 @@
         <v>8.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF49" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AG49" t="n">
         <v>1.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AK49" t="n">
         <v>1.25</v>
       </c>
       <c r="AL49" t="n">
-        <v>4.01</v>
+        <v>3.6</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AU49" t="n">
-        <v>4.55</v>
+        <v>4.23</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AZ49" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="BD49" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13418,10 +13418,10 @@
         <v>3.27</v>
       </c>
       <c r="S66" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="T66" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="U66" t="n">
         <v>3.6</v>
@@ -13433,7 +13433,7 @@
         <v>2.86</v>
       </c>
       <c r="X66" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="Y66" t="n">
         <v>1.38</v>
@@ -13445,25 +13445,25 @@
         <v>1.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC66" t="n">
         <v>1.24</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI66" t="n">
         <v>6</v>
@@ -13472,7 +13472,7 @@
         <v>1.08</v>
       </c>
       <c r="AK66" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AL66" t="n">
         <v>1.92</v>

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Chennaiyin</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.23</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>4.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3174,13 +3174,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,10 +3189,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3204,40 +3204,40 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,13 +3282,13 @@
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,13 +3371,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3401,40 +3401,40 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3479,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3765,13 +3765,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U17" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3780,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3795,40 +3795,40 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4159,13 +4159,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4174,10 +4174,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -4189,40 +4189,40 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -4583,40 +4583,40 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.12</v>
+        <v>1.38</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BD21" t="n">
         <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="BF21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,37 +4741,37 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="X22" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
         <v>1.09</v>
@@ -4780,40 +4780,40 @@
         <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5371,40 +5371,40 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.48</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U27" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.72</v>
+        <v>2.17</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="Z27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
         <v>1.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="BD27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5932,13 +5932,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5947,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5962,40 +5962,40 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.54</v>
+        <v>1.89</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.21</v>
+        <v>3.15</v>
       </c>
       <c r="R29" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="S29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
         <v>1.91</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U29" t="n">
-        <v>5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE29" t="n">
+      <c r="AL29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.5</v>
       </c>
-      <c r="AF29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="AF30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG30" t="n">
         <v>2.08</v>
       </c>
-      <c r="AG30" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AH30" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S31" t="n">
-        <v>1.58</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X31" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>2</v>
-      </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="U36" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W36" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="X36" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="Y36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH36" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB36" t="n">
+      <c r="AI36" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AK36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="R40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC40" t="n">
         <v>2.38</v>
       </c>
-      <c r="S40" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="T40" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W40" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>2.03</v>
-      </c>
       <c r="BD40" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R41" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="S41" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
         <v>1.85</v>
       </c>
       <c r="U41" t="n">
-        <v>4.34</v>
+        <v>3.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="W41" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="X41" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.14</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF41" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.06</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R43" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="S43" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="T43" t="n">
         <v>1.85</v>
       </c>
       <c r="U43" t="n">
-        <v>3.5</v>
+        <v>4.34</v>
       </c>
       <c r="V43" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="W43" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="X43" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE43" t="n">
+      <c r="AK43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD43" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>2.8</v>
-      </c>
       <c r="BE43" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">

--- a/jogos_2026-05-06.xlsx
+++ b/jogos_2026-05-06.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>5.13</v>
+        <v>4.2</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="W3" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="X3" t="n">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="n">
         <v>1.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
         <v>1.15</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AQ3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1.75</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="BD3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R4" t="n">
-        <v>4.2</v>
+        <v>5.13</v>
       </c>
       <c r="S4" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>3.52</v>
+        <v>3.35</v>
       </c>
       <c r="X4" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB4" t="n">
         <v>1.03</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.15</v>
       </c>
-      <c r="AD4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF4" t="n">
+      <c r="AK4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>5.74</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE4" t="n">
         <v>1.75</v>
       </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z6" t="n">
-        <v>0